--- a/doc/equip/Equip.xlsx
+++ b/doc/equip/Equip.xlsx
@@ -2573,7 +2573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="true">
+  <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AE583"/>
@@ -4347,7 +4347,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="n">
         <v>162</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="n">
         <v>356</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="n">
         <v>90</v>
       </c>
@@ -4476,7 +4476,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="n">
         <v>50</v>
       </c>
@@ -4517,7 +4517,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="n">
         <v>123</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="n">
         <v>357</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="n">
         <v>463</v>
       </c>
@@ -4652,7 +4652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="n">
         <v>520</v>
       </c>
@@ -4696,7 +4696,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="n">
         <v>6</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="n">
         <v>234</v>
       </c>
@@ -4778,7 +4778,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="n">
         <v>303</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="n">
         <v>555</v>
       </c>
@@ -4872,7 +4872,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="n">
         <v>5</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="n">
         <v>12</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="n">
         <v>134</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="n">
         <v>235</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="n">
         <v>518</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="n">
         <v>407</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="n">
         <v>11</v>
       </c>
@@ -5177,7 +5177,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="n">
         <v>77</v>
       </c>
@@ -5224,7 +5224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="n">
         <v>247</v>
       </c>
@@ -5268,7 +5268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="n">
         <v>310</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="n">
         <v>536</v>
       </c>
@@ -5362,7 +5362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="n">
         <v>340</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="n">
         <v>537</v>
       </c>
@@ -5453,7 +5453,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="n">
         <v>360</v>
       </c>
@@ -5500,7 +5500,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="n">
         <v>341</v>
       </c>
@@ -5547,7 +5547,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="n">
         <v>535</v>
       </c>
@@ -5588,7 +5588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="n">
         <v>361</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="n">
         <v>65</v>
       </c>
@@ -5676,7 +5676,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="n">
         <v>387</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="n">
         <v>139</v>
       </c>
@@ -5764,7 +5764,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="n">
         <v>4</v>
       </c>
@@ -5805,7 +5805,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="n">
         <v>119</v>
       </c>
@@ -5846,7 +5846,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="n">
         <v>4102</v>
       </c>
@@ -5887,7 +5887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="n">
         <v>359</v>
       </c>
@@ -5937,7 +5937,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="n">
         <v>399</v>
       </c>
@@ -5984,7 +5984,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="n">
         <v>534</v>
       </c>
@@ -6028,7 +6028,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="n">
         <v>282</v>
       </c>
@@ -6072,7 +6072,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="n">
         <v>386</v>
       </c>
@@ -6119,7 +6119,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="n">
         <v>529</v>
       </c>
@@ -6169,7 +6169,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="n">
         <v>294</v>
       </c>
@@ -6216,7 +6216,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="n">
         <v>63</v>
       </c>
@@ -6263,7 +6263,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="n">
         <v>295</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="n">
         <v>362</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="n">
         <v>266</v>
       </c>
@@ -6407,7 +6407,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="n">
         <v>4101</v>
       </c>
@@ -6454,7 +6454,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="n">
         <v>3</v>
       </c>
@@ -6495,7 +6495,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="n">
         <v>296</v>
       </c>
@@ -6545,7 +6545,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="n">
         <v>267</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="n">
         <v>122</v>
       </c>
@@ -6639,7 +6639,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="n">
         <v>455</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="n">
         <v>470</v>
       </c>
@@ -6730,7 +6730,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="n">
         <v>308</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="n">
         <v>363</v>
       </c>
@@ -6830,7 +6830,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="n">
         <v>366</v>
       </c>
@@ -6880,7 +6880,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="n">
         <v>379</v>
       </c>
@@ -6927,7 +6927,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="n">
         <v>380</v>
       </c>
@@ -6974,7 +6974,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="n">
         <v>397</v>
       </c>
@@ -7018,7 +7018,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="n">
         <v>398</v>
       </c>
@@ -7062,7 +7062,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="n">
         <v>553</v>
       </c>
@@ -7109,7 +7109,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="n">
         <v>533</v>
       </c>
@@ -7156,7 +7156,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="n">
         <v>297</v>
       </c>
@@ -7197,7 +7197,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="n">
         <v>2</v>
       </c>
@@ -7238,7 +7238,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="n">
         <v>293</v>
       </c>
@@ -7282,7 +7282,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="n">
         <v>4099</v>
       </c>
@@ -7323,7 +7323,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="n">
         <v>78</v>
       </c>
@@ -7367,7 +7367,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="n">
         <v>284</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="n">
         <v>393</v>
       </c>
@@ -7458,7 +7458,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="n">
         <v>4100</v>
       </c>
@@ -7499,7 +7499,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="n">
         <v>394</v>
       </c>
@@ -7543,7 +7543,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="n">
         <v>313</v>
       </c>
@@ -7587,7 +7587,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="n">
         <v>382</v>
       </c>
@@ -7637,7 +7637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="n">
         <v>91</v>
       </c>
@@ -7684,7 +7684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="n">
         <v>229</v>
       </c>
@@ -7731,7 +7731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="n">
         <v>509</v>
       </c>
@@ -7781,7 +7781,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="n">
         <v>1</v>
       </c>
@@ -7819,7 +7819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="n">
         <v>48</v>
       </c>
@@ -7857,7 +7857,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="n">
         <v>280</v>
       </c>
@@ -7907,7 +7907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="n">
         <v>147</v>
       </c>
@@ -7951,7 +7951,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="n">
         <v>365</v>
       </c>
@@ -7983,7 +7983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="n">
         <v>116</v>
       </c>
@@ -8015,7 +8015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="n">
         <v>36</v>
       </c>
@@ -8047,7 +8047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="n">
         <v>467</v>
       </c>
@@ -8091,7 +8091,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="n">
         <v>464</v>
       </c>
@@ -8138,7 +8138,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="n">
         <v>358</v>
       </c>
@@ -8185,7 +8185,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="n">
         <v>10</v>
       </c>
@@ -8226,7 +8226,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="n">
         <v>160</v>
       </c>
@@ -8270,7 +8270,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="n">
         <v>130</v>
       </c>
@@ -8317,7 +8317,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="n">
         <v>172</v>
       </c>
@@ -8364,7 +8364,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="n">
         <v>524</v>
       </c>
@@ -8414,7 +8414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="n">
         <v>66</v>
       </c>
@@ -8455,7 +8455,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="n">
         <v>135</v>
       </c>
@@ -8499,7 +8499,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="n">
         <v>220</v>
       </c>
@@ -8546,7 +8546,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="n">
         <v>430</v>
       </c>
@@ -8593,7 +8593,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="n">
         <v>556</v>
       </c>
@@ -8640,7 +8640,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="n">
         <v>71</v>
       </c>
@@ -8681,7 +8681,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="n">
         <v>275</v>
       </c>
@@ -8819,7 +8819,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="n">
         <v>513</v>
       </c>
@@ -8845,7 +8845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="n">
         <v>42</v>
       </c>
@@ -8868,7 +8868,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="n">
         <v>74</v>
       </c>
@@ -8894,7 +8894,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="n">
         <v>136</v>
       </c>
@@ -8929,7 +8929,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="n">
         <v>145</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="n">
         <v>146</v>
       </c>
@@ -8981,7 +8981,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="n">
         <v>174</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="n">
         <v>402</v>
       </c>
@@ -9080,7 +9080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="n">
         <v>33</v>
       </c>
@@ -9109,7 +9109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="0" t="n">
         <v>13</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="0" t="n">
         <v>191</v>
       </c>
@@ -9167,7 +9167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="n">
         <v>477</v>
       </c>
@@ -9214,7 +9214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="0" t="n">
         <v>4098</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="n">
         <v>43</v>
       </c>
@@ -9263,7 +9263,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="0" t="n">
         <v>101</v>
       </c>
@@ -9286,7 +9286,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="0" t="n">
         <v>408</v>
       </c>
@@ -9327,7 +9327,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="n">
         <v>68</v>
       </c>
@@ -9356,7 +9356,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="0" t="n">
         <v>304</v>
       </c>
@@ -9394,7 +9394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="0" t="n">
         <v>120</v>
       </c>
@@ -9423,7 +9423,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="0" t="n">
         <v>440</v>
       </c>
@@ -9452,7 +9452,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="0" t="n">
         <v>442</v>
       </c>
@@ -9484,7 +9484,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="0" t="n">
         <v>496</v>
       </c>
@@ -9510,7 +9510,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="0" t="n">
         <v>511</v>
       </c>
@@ -9539,7 +9539,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="n">
         <v>37</v>
       </c>
@@ -9568,7 +9568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="0" t="n">
         <v>166</v>
       </c>
@@ -9597,7 +9597,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="0" t="n">
         <v>46</v>
       </c>
@@ -9629,7 +9629,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="0" t="n">
         <v>72</v>
       </c>
@@ -9661,7 +9661,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="0" t="n">
         <v>73</v>
       </c>
@@ -9693,7 +9693,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="0" t="n">
         <v>258</v>
       </c>
@@ -9731,7 +9731,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="0" t="n">
         <v>510</v>
       </c>
@@ -9766,7 +9766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="0" t="n">
         <v>38</v>
       </c>
@@ -9795,7 +9795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="0" t="n">
         <v>44</v>
       </c>
@@ -9821,7 +9821,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="0" t="n">
         <v>64</v>
       </c>
@@ -9862,7 +9862,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="0" t="n">
         <v>92</v>
       </c>
@@ -9891,7 +9891,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="0" t="n">
         <v>121</v>
       </c>
@@ -9920,7 +9920,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="0" t="n">
         <v>173</v>
       </c>
@@ -10002,7 +10002,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="0" t="n">
         <v>367</v>
       </c>
@@ -10049,7 +10049,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="0" t="n">
         <v>401</v>
       </c>
@@ -10090,7 +10090,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="0" t="n">
         <v>500</v>
       </c>
@@ -10119,7 +10119,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="0" t="n">
         <v>95</v>
       </c>
@@ -10151,7 +10151,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="0" t="n">
         <v>108</v>
       </c>
@@ -10192,7 +10192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="0" t="n">
         <v>178</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="0" t="n">
         <v>414</v>
       </c>
@@ -10271,7 +10271,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="0" t="n">
         <v>14</v>
       </c>
@@ -10297,7 +10297,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="0" t="n">
         <v>19</v>
       </c>
@@ -10329,7 +10329,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="0" t="n">
         <v>39</v>
       </c>
@@ -10358,7 +10358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="0" t="n">
         <v>40</v>
       </c>
@@ -10387,7 +10387,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="0" t="n">
         <v>49</v>
       </c>
@@ -10416,7 +10416,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="0" t="n">
         <v>163</v>
       </c>
@@ -10463,7 +10463,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="0" t="n">
         <v>168</v>
       </c>
@@ -10504,7 +10504,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="0" t="n">
         <v>197</v>
       </c>
@@ -10542,7 +10542,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="0" t="n">
         <v>242</v>
       </c>
@@ -10583,7 +10583,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="0" t="n">
         <v>260</v>
       </c>
@@ -10621,7 +10621,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="0" t="n">
         <v>471</v>
       </c>
@@ -10659,7 +10659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="0" t="n">
         <v>16</v>
       </c>
@@ -10694,7 +10694,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="0" t="n">
         <v>115</v>
       </c>
@@ -10738,7 +10738,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="0" t="n">
         <v>125</v>
       </c>
@@ -10773,7 +10773,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="0" t="n">
         <v>129</v>
       </c>
@@ -10811,7 +10811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="0" t="n">
         <v>164</v>
       </c>
@@ -10849,7 +10849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="0" t="n">
         <v>194</v>
       </c>
@@ -10899,7 +10899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="0" t="n">
         <v>196</v>
       </c>
@@ -10940,7 +10940,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="0" t="n">
         <v>226</v>
       </c>
@@ -10966,7 +10966,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="0" t="n">
         <v>370</v>
       </c>
@@ -11004,7 +11004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="0" t="n">
         <v>371</v>
       </c>
@@ -11048,7 +11048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="0" t="n">
         <v>431</v>
       </c>
@@ -11092,7 +11092,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="0" t="n">
         <v>436</v>
       </c>
@@ -11127,7 +11127,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="0" t="n">
         <v>505</v>
       </c>
@@ -11156,7 +11156,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="0" t="n">
         <v>542</v>
       </c>
@@ -11194,7 +11194,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="0" t="n">
         <v>41</v>
       </c>
@@ -11220,7 +11220,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="0" t="n">
         <v>84</v>
       </c>
@@ -11252,7 +11252,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="0" t="n">
         <v>102</v>
       </c>
@@ -11287,7 +11287,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="0" t="n">
         <v>140</v>
       </c>
@@ -11316,7 +11316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="0" t="n">
         <v>193</v>
       </c>
@@ -11345,7 +11345,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="0" t="n">
         <v>248</v>
       </c>
@@ -11383,7 +11383,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="0" t="n">
         <v>250</v>
       </c>
@@ -11424,7 +11424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="0" t="n">
         <v>283</v>
       </c>
@@ -11503,7 +11503,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="0" t="n">
         <v>314</v>
       </c>
@@ -11591,7 +11591,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="0" t="n">
         <v>494</v>
       </c>
@@ -11620,7 +11620,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="0" t="n">
         <v>497</v>
       </c>
@@ -11646,7 +11646,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="0" t="n">
         <v>515</v>
       </c>
@@ -11681,7 +11681,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="0" t="n">
         <v>522</v>
       </c>
@@ -11722,7 +11722,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="0" t="n">
         <v>523</v>
       </c>
@@ -11766,7 +11766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="0" t="n">
         <v>538</v>
       </c>
@@ -11810,7 +11810,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="0" t="n">
         <v>15</v>
       </c>
@@ -11839,7 +11839,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="0" t="n">
         <v>23</v>
       </c>
@@ -11871,7 +11871,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="0" t="n">
         <v>86</v>
       </c>
@@ -11897,7 +11897,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="0" t="n">
         <v>171</v>
       </c>
@@ -11941,7 +11941,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="0" t="n">
         <v>195</v>
       </c>
@@ -12035,7 +12035,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="0" t="n">
         <v>400</v>
       </c>
@@ -12070,7 +12070,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="0" t="n">
         <v>541</v>
       </c>
@@ -12117,7 +12117,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="0" t="n">
         <v>559</v>
       </c>
@@ -12164,7 +12164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="0" t="n">
         <v>20</v>
       </c>
@@ -12193,7 +12193,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="0" t="n">
         <v>25</v>
       </c>
@@ -12234,7 +12234,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="0" t="n">
         <v>34</v>
       </c>
@@ -12263,7 +12263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="0" t="n">
         <v>59</v>
       </c>
@@ -12304,7 +12304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="0" t="n">
         <v>132</v>
       </c>
@@ -12339,7 +12339,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="0" t="n">
         <v>198</v>
       </c>
@@ -12380,7 +12380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="0" t="n">
         <v>230</v>
       </c>
@@ -12406,7 +12406,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="0" t="n">
         <v>249</v>
       </c>
@@ -12453,7 +12453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="0" t="n">
         <v>259</v>
       </c>
@@ -12494,7 +12494,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="0" t="n">
         <v>301</v>
       </c>
@@ -12523,7 +12523,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="0" t="n">
         <v>368</v>
       </c>
@@ -12567,7 +12567,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="0" t="n">
         <v>369</v>
       </c>
@@ -12614,7 +12614,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="0" t="n">
         <v>405</v>
       </c>
@@ -12655,7 +12655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="0" t="n">
         <v>423</v>
       </c>
@@ -12699,7 +12699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="0" t="n">
         <v>478</v>
       </c>
@@ -12755,7 +12755,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="0" t="n">
         <v>539</v>
       </c>
@@ -12799,7 +12799,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="0" t="n">
         <v>30</v>
       </c>
@@ -12831,7 +12831,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="0" t="n">
         <v>35</v>
       </c>
@@ -12860,7 +12860,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="0" t="n">
         <v>142</v>
       </c>
@@ -12901,7 +12901,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="0" t="n">
         <v>143</v>
       </c>
@@ -12948,7 +12948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="0" t="n">
         <v>150</v>
       </c>
@@ -12974,7 +12974,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="0" t="n">
         <v>158</v>
       </c>
@@ -13012,7 +13012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="0" t="n">
         <v>169</v>
       </c>
@@ -13053,7 +13053,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="0" t="n">
         <v>184</v>
       </c>
@@ -13091,7 +13091,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="0" t="n">
         <v>203</v>
       </c>
@@ -13123,7 +13123,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="259" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="0" t="n">
         <v>204</v>
       </c>
@@ -13155,7 +13155,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="0" t="n">
         <v>213</v>
       </c>
@@ -13187,7 +13187,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="0" t="n">
         <v>214</v>
       </c>
@@ -13222,7 +13222,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="262" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="0" t="n">
         <v>221</v>
       </c>
@@ -13254,7 +13254,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="263" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="0" t="n">
         <v>251</v>
       </c>
@@ -13386,7 +13386,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="0" t="n">
         <v>416</v>
       </c>
@@ -13427,7 +13427,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="0" t="n">
         <v>449</v>
       </c>
@@ -13456,7 +13456,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="268" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="0" t="n">
         <v>457</v>
       </c>
@@ -13491,7 +13491,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="0" t="n">
         <v>459</v>
       </c>
@@ -13535,7 +13535,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="0" t="n">
         <v>461</v>
       </c>
@@ -13573,7 +13573,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="0" t="n">
         <v>479</v>
       </c>
@@ -13620,7 +13620,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="272" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="0" t="n">
         <v>480</v>
       </c>
@@ -13655,7 +13655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="273" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="0" t="n">
         <v>481</v>
       </c>
@@ -13699,7 +13699,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="0" t="n">
         <v>482</v>
       </c>
@@ -13734,7 +13734,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="0" t="n">
         <v>495</v>
       </c>
@@ -13766,7 +13766,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="0" t="n">
         <v>498</v>
       </c>
@@ -13792,7 +13792,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="0" t="n">
         <v>499</v>
       </c>
@@ -13821,7 +13821,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="0" t="n">
         <v>501</v>
       </c>
@@ -13850,7 +13850,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="0" t="n">
         <v>519</v>
       </c>
@@ -13888,7 +13888,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="0" t="n">
         <v>527</v>
       </c>
@@ -13926,7 +13926,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="0" t="n">
         <v>4103</v>
       </c>
@@ -13955,7 +13955,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="282" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="0" t="n">
         <v>21</v>
       </c>
@@ -13984,7 +13984,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="0" t="n">
         <v>27</v>
       </c>
@@ -14016,7 +14016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="0" t="n">
         <v>61</v>
       </c>
@@ -14051,7 +14051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="0" t="n">
         <v>69</v>
       </c>
@@ -14083,7 +14083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="0" t="n">
         <v>75</v>
       </c>
@@ -14109,7 +14109,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="287" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="0" t="n">
         <v>93</v>
       </c>
@@ -14156,7 +14156,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="288" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="0" t="n">
         <v>96</v>
       </c>
@@ -14197,7 +14197,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="0" t="n">
         <v>97</v>
       </c>
@@ -14244,7 +14244,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="0" t="n">
         <v>98</v>
       </c>
@@ -14285,7 +14285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="0" t="n">
         <v>99</v>
       </c>
@@ -14329,7 +14329,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="292" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="0" t="n">
         <v>138</v>
       </c>
@@ -14367,7 +14367,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="293" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="0" t="n">
         <v>155</v>
       </c>
@@ -14408,7 +14408,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="294" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="0" t="n">
         <v>165</v>
       </c>
@@ -14446,7 +14446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="0" t="n">
         <v>167</v>
       </c>
@@ -14475,7 +14475,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="296" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="0" t="n">
         <v>181</v>
       </c>
@@ -14507,7 +14507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="0" t="n">
         <v>205</v>
       </c>
@@ -14548,7 +14548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="0" t="n">
         <v>215</v>
       </c>
@@ -14586,7 +14586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="299" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="0" t="n">
         <v>216</v>
       </c>
@@ -14627,7 +14627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="0" t="n">
         <v>225</v>
       </c>
@@ -14671,7 +14671,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="301" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="301" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="0" t="n">
         <v>227</v>
       </c>
@@ -14697,7 +14697,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="0" t="n">
         <v>228</v>
       </c>
@@ -14732,7 +14732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="0" t="n">
         <v>233</v>
       </c>
@@ -14779,7 +14779,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="304" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="0" t="n">
         <v>238</v>
       </c>
@@ -14820,7 +14820,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="0" t="n">
         <v>252</v>
       </c>
@@ -14864,7 +14864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="306" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="0" t="n">
         <v>256</v>
       </c>
@@ -14905,7 +14905,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="307" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="307" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="0" t="n">
         <v>261</v>
       </c>
@@ -14940,7 +14940,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="308" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="0" t="n">
         <v>268</v>
       </c>
@@ -14972,7 +14972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="309" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="0" t="n">
         <v>277</v>
       </c>
@@ -15022,7 +15022,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="310" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="310" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="0" t="n">
         <v>285</v>
       </c>
@@ -15057,7 +15057,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="311" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="0" t="n">
         <v>311</v>
       </c>
@@ -15092,7 +15092,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="312" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="0" t="n">
         <v>312</v>
       </c>
@@ -15133,7 +15133,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="313" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="0" t="n">
         <v>315</v>
       </c>
@@ -15180,7 +15180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="314" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="0" t="n">
         <v>316</v>
       </c>
@@ -15224,7 +15224,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="315" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="0" t="n">
         <v>350</v>
       </c>
@@ -15259,7 +15259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="0" t="n">
         <v>355</v>
       </c>
@@ -15294,7 +15294,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="317" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="0" t="n">
         <v>383</v>
       </c>
@@ -15326,7 +15326,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="318" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="0" t="n">
         <v>391</v>
       </c>
@@ -15367,7 +15367,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="319" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="319" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="0" t="n">
         <v>392</v>
       </c>
@@ -15417,7 +15417,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="320" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="0" t="n">
         <v>415</v>
       </c>
@@ -15455,7 +15455,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="321" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="0" t="n">
         <v>417</v>
       </c>
@@ -15496,7 +15496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="322" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="322" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="0" t="n">
         <v>418</v>
       </c>
@@ -15537,7 +15537,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="323" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="0" t="n">
         <v>424</v>
       </c>
@@ -15575,7 +15575,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="324" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="0" t="n">
         <v>432</v>
       </c>
@@ -15616,7 +15616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="325" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="325" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="0" t="n">
         <v>433</v>
       </c>
@@ -15663,7 +15663,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="326" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="326" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="0" t="n">
         <v>434</v>
       </c>
@@ -15701,7 +15701,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="327" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="327" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="0" t="n">
         <v>435</v>
       </c>
@@ -15745,7 +15745,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="328" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="328" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="0" t="n">
         <v>439</v>
       </c>
@@ -15780,7 +15780,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="329" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="329" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="0" t="n">
         <v>445</v>
       </c>
@@ -15818,7 +15818,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="330" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="330" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="0" t="n">
         <v>514</v>
       </c>
@@ -15853,7 +15853,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="331" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="331" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="0" t="n">
         <v>543</v>
       </c>
@@ -15900,7 +15900,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="332" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="332" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="0" t="n">
         <v>544</v>
       </c>
@@ -15950,7 +15950,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="333" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="333" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="0" t="n">
         <v>560</v>
       </c>
@@ -15988,7 +15988,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="334" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="334" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="0" t="n">
         <v>17</v>
       </c>
@@ -16023,7 +16023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="335" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="0" t="n">
         <v>24</v>
       </c>
@@ -16055,7 +16055,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="336" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="336" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="0" t="n">
         <v>26</v>
       </c>
@@ -16096,7 +16096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="337" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="0" t="n">
         <v>28</v>
       </c>
@@ -16125,7 +16125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="338" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="338" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="0" t="n">
         <v>31</v>
       </c>
@@ -16154,7 +16154,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="339" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="339" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="0" t="n">
         <v>32</v>
       </c>
@@ -16186,7 +16186,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="340" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="0" t="n">
         <v>45</v>
       </c>
@@ -16212,7 +16212,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="341" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="341" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="0" t="n">
         <v>47</v>
       </c>
@@ -16244,7 +16244,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="342" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="0" t="n">
         <v>55</v>
       </c>
@@ -16276,7 +16276,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="343" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="343" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="0" t="n">
         <v>62</v>
       </c>
@@ -16320,7 +16320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="344" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="0" t="n">
         <v>70</v>
       </c>
@@ -16355,7 +16355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="345" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="345" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="0" t="n">
         <v>82</v>
       </c>
@@ -16393,7 +16393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="346" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="346" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="0" t="n">
         <v>87</v>
       </c>
@@ -16422,7 +16422,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="347" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="347" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="0" t="n">
         <v>89</v>
       </c>
@@ -16457,7 +16457,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="348" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="0" t="n">
         <v>107</v>
       </c>
@@ -16492,7 +16492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="349" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="0" t="n">
         <v>118</v>
       </c>
@@ -16530,7 +16530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="350" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="0" t="n">
         <v>126</v>
       </c>
@@ -16565,7 +16565,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="351" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="351" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="0" t="n">
         <v>131</v>
       </c>
@@ -16638,7 +16638,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="353" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="0" t="n">
         <v>175</v>
       </c>
@@ -16673,7 +16673,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="354" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="0" t="n">
         <v>176</v>
       </c>
@@ -16708,7 +16708,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="355" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="0" t="n">
         <v>177</v>
       </c>
@@ -16746,7 +16746,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="356" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="356" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="0" t="n">
         <v>180</v>
       </c>
@@ -16787,7 +16787,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="357" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="357" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="0" t="n">
         <v>186</v>
       </c>
@@ -16831,7 +16831,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="358" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="0" t="n">
         <v>188</v>
       </c>
@@ -16869,7 +16869,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="359" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="359" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="0" t="n">
         <v>189</v>
       </c>
@@ -16904,7 +16904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="360" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="360" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="0" t="n">
         <v>201</v>
       </c>
@@ -16942,7 +16942,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="361" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="361" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="0" t="n">
         <v>210</v>
       </c>
@@ -16983,7 +16983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="362" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="0" t="n">
         <v>217</v>
       </c>
@@ -17018,7 +17018,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="363" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="363" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="0" t="n">
         <v>241</v>
       </c>
@@ -17044,7 +17044,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="364" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="0" t="n">
         <v>243</v>
       </c>
@@ -17085,7 +17085,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="365" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="365" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="0" t="n">
         <v>253</v>
       </c>
@@ -17126,7 +17126,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="366" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="0" t="n">
         <v>254</v>
       </c>
@@ -17170,7 +17170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="367" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="0" t="n">
         <v>278</v>
       </c>
@@ -17208,7 +17208,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="368" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="368" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="0" t="n">
         <v>279</v>
       </c>
@@ -17252,7 +17252,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="369" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="369" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="0" t="n">
         <v>286</v>
       </c>
@@ -17287,7 +17287,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="370" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="370" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="0" t="n">
         <v>307</v>
       </c>
@@ -17334,7 +17334,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="371" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="371" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="0" t="n">
         <v>324</v>
       </c>
@@ -17369,7 +17369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="372" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="0" t="n">
         <v>344</v>
       </c>
@@ -17410,7 +17410,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="373" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="0" t="n">
         <v>346</v>
       </c>
@@ -17442,7 +17442,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="374" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="374" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="0" t="n">
         <v>376</v>
       </c>
@@ -17524,7 +17524,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="376" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="376" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="0" t="n">
         <v>395</v>
       </c>
@@ -17562,7 +17562,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="377" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="377" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="0" t="n">
         <v>406</v>
       </c>
@@ -17603,7 +17603,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="378" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="378" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="0" t="n">
         <v>409</v>
       </c>
@@ -17641,7 +17641,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="379" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="379" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="0" t="n">
         <v>412</v>
       </c>
@@ -17685,7 +17685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="380" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="0" t="n">
         <v>413</v>
       </c>
@@ -17717,7 +17717,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="381" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="381" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="0" t="n">
         <v>419</v>
       </c>
@@ -17764,7 +17764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="382" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="382" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="0" t="n">
         <v>420</v>
       </c>
@@ -17814,7 +17814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="383" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="0" t="n">
         <v>441</v>
       </c>
@@ -17846,7 +17846,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="384" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="384" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="0" t="n">
         <v>443</v>
       </c>
@@ -17878,7 +17878,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="385" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="385" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="0" t="n">
         <v>446</v>
       </c>
@@ -17916,7 +17916,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="386" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="386" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="0" t="n">
         <v>469</v>
       </c>
@@ -17957,7 +17957,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="387" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="387" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="0" t="n">
         <v>489</v>
       </c>
@@ -17998,7 +17998,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="388" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="0" t="n">
         <v>512</v>
       </c>
@@ -18030,7 +18030,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="389" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="0" t="n">
         <v>531</v>
       </c>
@@ -18059,7 +18059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="0" t="n">
         <v>532</v>
       </c>
@@ -18085,7 +18085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="391" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="0" t="n">
         <v>4097</v>
       </c>
@@ -18120,7 +18120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="392" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="0" t="n">
         <v>22</v>
       </c>
@@ -18152,7 +18152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="393" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="393" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="0" t="n">
         <v>29</v>
       </c>
@@ -18181,7 +18181,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="394" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="394" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="0" t="n">
         <v>51</v>
       </c>
@@ -18210,7 +18210,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="395" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="395" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="0" t="n">
         <v>54</v>
       </c>
@@ -18242,7 +18242,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="396" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="396" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="0" t="n">
         <v>57</v>
       </c>
@@ -18277,7 +18277,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="397" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="397" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="0" t="n">
         <v>58</v>
       </c>
@@ -18306,7 +18306,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="398" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="398" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="0" t="n">
         <v>79</v>
       </c>
@@ -18350,7 +18350,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="399" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="399" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="0" t="n">
         <v>85</v>
       </c>
@@ -18382,7 +18382,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="400" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="400" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="0" t="n">
         <v>106</v>
       </c>
@@ -18417,7 +18417,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="401" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="0" t="n">
         <v>111</v>
       </c>
@@ -18458,7 +18458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="402" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="402" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="0" t="n">
         <v>112</v>
       </c>
@@ -18499,7 +18499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="403" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="0" t="n">
         <v>124</v>
       </c>
@@ -18537,7 +18537,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="404" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="404" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="0" t="n">
         <v>127</v>
       </c>
@@ -18572,7 +18572,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="405" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="405" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="0" t="n">
         <v>149</v>
       </c>
@@ -18607,7 +18607,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="406" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="406" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="0" t="n">
         <v>152</v>
       </c>
@@ -18648,7 +18648,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="407" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="0" t="n">
         <v>153</v>
       </c>
@@ -18689,7 +18689,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="408" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="408" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="0" t="n">
         <v>156</v>
       </c>
@@ -18730,7 +18730,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="409" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="409" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="0" t="n">
         <v>159</v>
       </c>
@@ -18765,7 +18765,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="410" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="410" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="0" t="n">
         <v>170</v>
       </c>
@@ -18812,7 +18812,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="411" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="0" t="n">
         <v>182</v>
       </c>
@@ -18853,7 +18853,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="412" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="412" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="0" t="n">
         <v>185</v>
       </c>
@@ -18888,7 +18888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="413" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="413" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="0" t="n">
         <v>187</v>
       </c>
@@ -18932,7 +18932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="414" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="414" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="0" t="n">
         <v>202</v>
       </c>
@@ -18970,7 +18970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="415" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="415" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="0" t="n">
         <v>206</v>
       </c>
@@ -19011,7 +19011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="0" t="n">
         <v>207</v>
       </c>
@@ -19055,7 +19055,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="417" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="417" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="0" t="n">
         <v>209</v>
       </c>
@@ -19081,7 +19081,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="418" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="418" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="0" t="n">
         <v>211</v>
       </c>
@@ -19119,7 +19119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="419" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="0" t="n">
         <v>212</v>
       </c>
@@ -19154,7 +19154,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="420" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="420" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="0" t="n">
         <v>218</v>
       </c>
@@ -19189,7 +19189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="421" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="421" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="0" t="n">
         <v>222</v>
       </c>
@@ -19227,7 +19227,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="422" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="422" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="0" t="n">
         <v>223</v>
       </c>
@@ -19271,7 +19271,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="423" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="423" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="0" t="n">
         <v>239</v>
       </c>
@@ -19315,7 +19315,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="424" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="424" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="0" t="n">
         <v>244</v>
       </c>
@@ -19359,7 +19359,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="425" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="425" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="0" t="n">
         <v>262</v>
       </c>
@@ -19394,7 +19394,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="426" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="426" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="0" t="n">
         <v>263</v>
       </c>
@@ -19435,7 +19435,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="427" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="0" t="n">
         <v>264</v>
       </c>
@@ -19476,7 +19476,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="428" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="428" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="0" t="n">
         <v>265</v>
       </c>
@@ -19517,7 +19517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="429" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="0" t="n">
         <v>269</v>
       </c>
@@ -19552,7 +19552,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="430" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="0" t="n">
         <v>272</v>
       </c>
@@ -19587,7 +19587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="431" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="0" t="n">
         <v>287</v>
       </c>
@@ -19613,7 +19613,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="432" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="432" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="0" t="n">
         <v>291</v>
       </c>
@@ -19657,7 +19657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="433" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="0" t="n">
         <v>305</v>
       </c>
@@ -19701,7 +19701,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="434" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="434" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="0" t="n">
         <v>309</v>
       </c>
@@ -19733,7 +19733,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="435" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="435" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="0" t="n">
         <v>325</v>
       </c>
@@ -19771,7 +19771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="436" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="436" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="0" t="n">
         <v>345</v>
       </c>
@@ -19812,7 +19812,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="437" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="437" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="0" t="n">
         <v>347</v>
       </c>
@@ -19844,7 +19844,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="438" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="438" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="0" t="n">
         <v>348</v>
       </c>
@@ -19876,7 +19876,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="439" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="0" t="n">
         <v>353</v>
       </c>
@@ -19917,7 +19917,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="440" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="440" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="0" t="n">
         <v>354</v>
       </c>
@@ -19958,7 +19958,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="441" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="441" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="0" t="n">
         <v>372</v>
       </c>
@@ -19996,7 +19996,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="442" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="0" t="n">
         <v>388</v>
       </c>
@@ -20043,7 +20043,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="443" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="443" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="0" t="n">
         <v>403</v>
       </c>
@@ -20087,7 +20087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="444" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="0" t="n">
         <v>404</v>
       </c>
@@ -20134,7 +20134,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="445" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="0" t="n">
         <v>421</v>
       </c>
@@ -20184,7 +20184,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="446" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="446" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="0" t="n">
         <v>425</v>
       </c>
@@ -20222,7 +20222,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="447" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="447" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="0" t="n">
         <v>452</v>
       </c>
@@ -20260,7 +20260,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="448" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="448" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="0" t="n">
         <v>453</v>
       </c>
@@ -20307,7 +20307,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="449" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="449" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="0" t="n">
         <v>456</v>
       </c>
@@ -20354,7 +20354,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="450" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="450" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="0" t="n">
         <v>460</v>
       </c>
@@ -20398,7 +20398,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="451" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="451" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="0" t="n">
         <v>473</v>
       </c>
@@ -20442,7 +20442,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="452" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="452" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="0" t="n">
         <v>474</v>
       </c>
@@ -20489,7 +20489,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="453" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="453" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="0" t="n">
         <v>488</v>
       </c>
@@ -20524,7 +20524,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="454" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="454" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="0" t="n">
         <v>492</v>
       </c>
@@ -20565,7 +20565,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="455" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="455" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="0" t="n">
         <v>493</v>
       </c>
@@ -20612,7 +20612,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="456" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="456" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="0" t="n">
         <v>516</v>
       </c>
@@ -20653,7 +20653,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="457" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="457" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="0" t="n">
         <v>521</v>
       </c>
@@ -20697,7 +20697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="458" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="0" t="n">
         <v>525</v>
       </c>
@@ -20732,7 +20732,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="459" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="459" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="0" t="n">
         <v>528</v>
       </c>
@@ -20779,7 +20779,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="460" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="460" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="0" t="n">
         <v>554</v>
       </c>
@@ -20814,7 +20814,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="461" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="461" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="0" t="n">
         <v>18</v>
       </c>
@@ -20852,7 +20852,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="462" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="462" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="0" t="n">
         <v>60</v>
       </c>
@@ -20887,7 +20887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="463" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="463" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="0" t="n">
         <v>83</v>
       </c>
@@ -20925,7 +20925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="464" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="464" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="0" t="n">
         <v>88</v>
       </c>
@@ -20957,7 +20957,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="465" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="465" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="0" t="n">
         <v>94</v>
       </c>
@@ -21004,7 +21004,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="466" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="466" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="0" t="n">
         <v>100</v>
       </c>
@@ -21051,7 +21051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="467" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="467" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="0" t="n">
         <v>109</v>
       </c>
@@ -21089,7 +21089,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="468" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="468" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="0" t="n">
         <v>144</v>
       </c>
@@ -21136,7 +21136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="469" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="469" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="0" t="n">
         <v>148</v>
       </c>
@@ -21177,7 +21177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="470" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="0" t="n">
         <v>151</v>
       </c>
@@ -21215,7 +21215,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="471" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="471" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="0" t="n">
         <v>208</v>
       </c>
@@ -21259,7 +21259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="472" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="472" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="0" t="n">
         <v>224</v>
       </c>
@@ -21303,7 +21303,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="473" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="473" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="0" t="n">
         <v>255</v>
       </c>
@@ -21347,7 +21347,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="474" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="474" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="0" t="n">
         <v>270</v>
       </c>
@@ -21388,7 +21388,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="475" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="475" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="0" t="n">
         <v>271</v>
       </c>
@@ -21426,7 +21426,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="476" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="476" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="0" t="n">
         <v>273</v>
       </c>
@@ -21461,7 +21461,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="477" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="477" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="0" t="n">
         <v>274</v>
       </c>
@@ -21496,7 +21496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="478" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="478" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="0" t="n">
         <v>288</v>
       </c>
@@ -21528,7 +21528,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="479" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="479" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="0" t="n">
         <v>292</v>
       </c>
@@ -21578,7 +21578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="480" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="480" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="0" t="n">
         <v>302</v>
       </c>
@@ -21622,7 +21622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="481" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="481" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="0" t="n">
         <v>306</v>
       </c>
@@ -21672,7 +21672,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="482" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="482" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="0" t="n">
         <v>317</v>
       </c>
@@ -21707,7 +21707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="483" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="483" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="0" t="n">
         <v>319</v>
       </c>
@@ -21754,7 +21754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="484" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="484" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="0" t="n">
         <v>320</v>
       </c>
@@ -21795,7 +21795,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="485" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="485" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="0" t="n">
         <v>333</v>
       </c>
@@ -21833,7 +21833,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="486" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="486" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="0" t="n">
         <v>334</v>
       </c>
@@ -21874,7 +21874,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="487" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="487" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="0" t="n">
         <v>349</v>
       </c>
@@ -21906,7 +21906,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="488" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="488" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="0" t="n">
         <v>351</v>
       </c>
@@ -21938,7 +21938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="489" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="0" t="n">
         <v>364</v>
       </c>
@@ -21970,7 +21970,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="490" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="490" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="0" t="n">
         <v>373</v>
       </c>
@@ -22014,7 +22014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="491" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="491" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="0" t="n">
         <v>374</v>
       </c>
@@ -22061,7 +22061,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="492" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="492" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="0" t="n">
         <v>375</v>
       </c>
@@ -22096,7 +22096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="493" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="493" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="0" t="n">
         <v>384</v>
       </c>
@@ -22190,7 +22190,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="495" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="495" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="0" t="n">
         <v>410</v>
       </c>
@@ -22225,7 +22225,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="496" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="496" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="0" t="n">
         <v>411</v>
       </c>
@@ -22260,7 +22260,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="497" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="497" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="0" t="n">
         <v>422</v>
       </c>
@@ -22301,7 +22301,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="498" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="498" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="0" t="n">
         <v>438</v>
       </c>
@@ -22339,7 +22339,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="499" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="499" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="0" t="n">
         <v>450</v>
       </c>
@@ -22374,7 +22374,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="500" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="500" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="0" t="n">
         <v>451</v>
       </c>
@@ -22412,7 +22412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="501" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="501" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="0" t="n">
         <v>458</v>
       </c>
@@ -22453,7 +22453,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="502" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="502" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="0" t="n">
         <v>475</v>
       </c>
@@ -22500,7 +22500,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="503" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="503" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="0" t="n">
         <v>476</v>
       </c>
@@ -22547,7 +22547,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="504" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="504" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="0" t="n">
         <v>486</v>
       </c>
@@ -22588,7 +22588,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="505" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="505" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="0" t="n">
         <v>491</v>
       </c>
@@ -22635,7 +22635,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="506" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="506" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="0" t="n">
         <v>504</v>
       </c>
@@ -22682,7 +22682,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="507" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="507" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="0" t="n">
         <v>506</v>
       </c>
@@ -22723,7 +22723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="508" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="508" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="0" t="n">
         <v>550</v>
       </c>
@@ -22761,7 +22761,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="509" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="509" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="0" t="n">
         <v>561</v>
       </c>
@@ -22808,7 +22808,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="510" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="510" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="0" t="n">
         <v>53</v>
       </c>
@@ -22837,7 +22837,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="511" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="511" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="0" t="n">
         <v>80</v>
       </c>
@@ -22878,7 +22878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="512" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="512" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="0" t="n">
         <v>81</v>
       </c>
@@ -22922,7 +22922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="513" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="513" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="0" t="n">
         <v>113</v>
       </c>
@@ -22963,7 +22963,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="514" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="514" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="0" t="n">
         <v>141</v>
       </c>
@@ -22992,7 +22992,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="515" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="515" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="0" t="n">
         <v>154</v>
       </c>
@@ -23092,7 +23092,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="517" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="517" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="0" t="n">
         <v>199</v>
       </c>
@@ -23136,7 +23136,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="518" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="518" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="0" t="n">
         <v>219</v>
       </c>
@@ -23171,7 +23171,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="519" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="519" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="0" t="n">
         <v>237</v>
       </c>
@@ -23218,7 +23218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="520" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="520" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="0" t="n">
         <v>257</v>
       </c>
@@ -23265,7 +23265,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="521" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="521" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="0" t="n">
         <v>396</v>
       </c>
@@ -23300,7 +23300,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="522" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="522" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="0" t="n">
         <v>437</v>
       </c>
@@ -23335,7 +23335,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="523" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="523" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="0" t="n">
         <v>444</v>
       </c>
@@ -23382,7 +23382,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="524" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="524" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="0" t="n">
         <v>447</v>
       </c>
@@ -23423,7 +23423,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="525" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="525" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="0" t="n">
         <v>454</v>
       </c>
@@ -23473,7 +23473,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="526" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="526" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="0" t="n">
         <v>484</v>
       </c>
@@ -23520,7 +23520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="527" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="527" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="0" t="n">
         <v>485</v>
       </c>
@@ -23555,7 +23555,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="528" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="528" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="0" t="n">
         <v>526</v>
       </c>
@@ -23593,7 +23593,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="529" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="529" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="0" t="n">
         <v>540</v>
       </c>
@@ -23634,7 +23634,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="530" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="530" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="0" t="n">
         <v>551</v>
       </c>
@@ -23672,7 +23672,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="531" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="531" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="0" t="n">
         <v>52</v>
       </c>
@@ -23710,7 +23710,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="532" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="532" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="0" t="n">
         <v>110</v>
       </c>
@@ -23748,7 +23748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="533" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="533" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="0" t="n">
         <v>157</v>
       </c>
@@ -23789,7 +23789,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="534" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="534" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="0" t="n">
         <v>200</v>
       </c>
@@ -23830,7 +23830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="535" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="535" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="0" t="n">
         <v>240</v>
       </c>
@@ -23865,7 +23865,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="536" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="536" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="0" t="n">
         <v>326</v>
       </c>
@@ -23906,7 +23906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="537" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="537" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="0" t="n">
         <v>336</v>
       </c>
@@ -23944,7 +23944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="538" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="538" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="0" t="n">
         <v>342</v>
       </c>
@@ -23988,7 +23988,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="539" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="539" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="0" t="n">
         <v>352</v>
       </c>
@@ -24020,7 +24020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="540" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="540" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="0" t="n">
         <v>389</v>
       </c>
@@ -24070,7 +24070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="541" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="541" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="0" t="n">
         <v>466</v>
       </c>
@@ -24117,7 +24117,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="542" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="542" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="0" t="n">
         <v>487</v>
       </c>
@@ -24164,7 +24164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="543" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="543" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="0" t="n">
         <v>179</v>
       </c>
@@ -24193,7 +24193,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="544" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="544" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="0" t="n">
         <v>322</v>
       </c>
@@ -24243,7 +24243,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="545" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="545" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="0" t="n">
         <v>338</v>
       </c>
@@ -24290,7 +24290,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="546" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="546" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="0" t="n">
         <v>339</v>
       </c>
@@ -24337,7 +24337,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="547" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="547" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="0" t="n">
         <v>343</v>
       </c>
@@ -24384,7 +24384,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="548" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="548" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="0" t="n">
         <v>483</v>
       </c>
@@ -24422,7 +24422,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="549" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="549" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="0" t="n">
         <v>490</v>
       </c>
@@ -24466,7 +24466,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="550" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="550" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="0" t="n">
         <v>517</v>
       </c>
@@ -24504,7 +24504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="551" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="551" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="0" t="n">
         <v>545</v>
       </c>
@@ -24551,7 +24551,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="552" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="552" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="0" t="n">
         <v>546</v>
       </c>
@@ -24586,7 +24586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="553" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="553" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="0" t="n">
         <v>549</v>
       </c>
@@ -24627,7 +24627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="554" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="554" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A554" s="0" t="n">
         <v>552</v>
       </c>
@@ -24671,7 +24671,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="555" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="555" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="0" t="n">
         <v>557</v>
       </c>
@@ -24715,7 +24715,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="556" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="556" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="0" t="n">
         <v>323</v>
       </c>
@@ -24765,7 +24765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="557" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="557" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="0" t="n">
         <v>56</v>
       </c>
@@ -24794,7 +24794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="558" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="558" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="0" t="n">
         <v>558</v>
       </c>
@@ -24838,7 +24838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="559" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="559" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="0" t="n">
         <v>377</v>
       </c>
@@ -24876,7 +24876,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="560" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="560" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A560" s="0" t="n">
         <v>472</v>
       </c>
@@ -24911,7 +24911,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="561" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="561" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A561" s="0" t="n">
         <v>327</v>
       </c>
@@ -24949,7 +24949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="562" customFormat="false" ht="17.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="562" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A562" s="0" t="n">
         <v>378</v>
       </c>
@@ -24978,7 +24978,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="563" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="563" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A563" s="0" t="n">
         <v>16384</v>
       </c>
@@ -24992,7 +24992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="564" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A564" s="0" t="n">
         <v>16389</v>
       </c>
@@ -25006,7 +25006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="565" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A565" s="0" t="n">
         <v>16390</v>
       </c>
@@ -25020,7 +25020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="566" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="566" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A566" s="0" t="n">
         <v>16391</v>
       </c>
@@ -25034,7 +25034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="567" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A567" s="0" t="n">
         <v>16392</v>
       </c>
@@ -25048,7 +25048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="568" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A568" s="0" t="n">
         <v>16393</v>
       </c>
@@ -25062,7 +25062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="569" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A569" s="0" t="n">
         <v>16394</v>
       </c>
@@ -25076,7 +25076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="570" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A570" s="0" t="n">
         <v>16396</v>
       </c>
@@ -25090,7 +25090,7 @@
         <v>16394</v>
       </c>
     </row>
-    <row r="571" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="571" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A571" s="0" t="n">
         <v>16401</v>
       </c>
@@ -25104,7 +25104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="572" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A572" s="0" t="n">
         <v>16402</v>
       </c>
@@ -25118,7 +25118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="573" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A573" s="0" t="n">
         <v>16404</v>
       </c>
@@ -25132,7 +25132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="574" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A574" s="0" t="n">
         <v>16415</v>
       </c>
@@ -25146,7 +25146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="575" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A575" s="0" t="n">
         <v>16427</v>
       </c>
@@ -25160,7 +25160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="576" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A576" s="0" t="n">
         <v>16438</v>
       </c>
@@ -25174,7 +25174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="577" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A577" s="0" t="n">
         <v>16439</v>
       </c>
@@ -25188,7 +25188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="578" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A578" s="0" t="n">
         <v>16440</v>
       </c>
@@ -25202,7 +25202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="579" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A579" s="0" t="n">
         <v>16445</v>
       </c>
@@ -25216,7 +25216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="580" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A580" s="0" t="n">
         <v>16446</v>
       </c>
@@ -25230,7 +25230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="581" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A581" s="0" t="n">
         <v>16461</v>
       </c>
@@ -25244,7 +25244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="582" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A582" s="0" t="n">
         <v>16469</v>
       </c>
@@ -25258,7 +25258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="583" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A583" s="0" t="n">
         <v>16470</v>
       </c>
@@ -25274,11 +25274,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:AE583">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="大口径主砲"/>
-      </filters>
-    </filterColumn>
     <sortState ref="A3:AE583">
       <sortCondition ref="M3:M583" descending="1" customList=""/>
     </sortState>

--- a/doc/equip/Equip.xlsx
+++ b/doc/equip/Equip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuoMuoRuoProject\doc\equip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58DE5BF2-93A4-4123-99E9-26280A33F290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CB8BDA-76C9-4FC9-AC7C-9E93FF53E32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/doc/equip/Equip.xlsx
+++ b/doc/equip/Equip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuoMuoRuoProject\doc\equip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CB8BDA-76C9-4FC9-AC7C-9E93FF53E32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D933B8DE-A77B-4CD1-BBB4-930A9429E1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/doc/equip/Equip.xlsx
+++ b/doc/equip/Equip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuoMuoRuoProject\doc\equip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A90BAC-0B0B-4B98-91A6-471DAEE6EA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5AA8D3-E676-451C-94D1-A6AB9C89CB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2553,6 +2553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AE583"/>
   <sheetFormatPr defaultColWidth="10.06640625" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2772,7 +2773,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2810,7 +2811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2851,7 +2852,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2892,7 +2893,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2933,7 +2934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2974,7 +2975,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3012,7 +3013,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3050,7 +3051,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3088,7 +3089,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3126,7 +3127,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3167,7 +3168,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3205,7 +3206,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -3246,7 +3247,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3272,7 +3273,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3298,7 +3299,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -3327,7 +3328,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3362,7 +3363,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3397,7 +3398,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
@@ -3435,7 +3436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
@@ -3467,7 +3468,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
@@ -3496,7 +3497,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
@@ -3525,7 +3526,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
@@ -3557,7 +3558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
@@ -3589,7 +3590,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
@@ -3621,7 +3622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -3662,7 +3663,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -3703,7 +3704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
@@ -3735,7 +3736,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
@@ -3764,7 +3765,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
@@ -3793,7 +3794,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
@@ -3825,7 +3826,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>31</v>
       </c>
@@ -3854,7 +3855,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>32</v>
       </c>
@@ -3886,7 +3887,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>33</v>
       </c>
@@ -3915,7 +3916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>34</v>
       </c>
@@ -3944,7 +3945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>35</v>
       </c>
@@ -3973,7 +3974,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>36</v>
       </c>
@@ -4005,7 +4006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>37</v>
       </c>
@@ -4034,7 +4035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>38</v>
       </c>
@@ -4063,7 +4064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>39</v>
       </c>
@@ -4092,7 +4093,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>40</v>
       </c>
@@ -4121,7 +4122,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>41</v>
       </c>
@@ -4147,7 +4148,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>42</v>
       </c>
@@ -4170,7 +4171,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>43</v>
       </c>
@@ -4193,7 +4194,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>44</v>
       </c>
@@ -4219,7 +4220,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>45</v>
       </c>
@@ -4245,7 +4246,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>46</v>
       </c>
@@ -4277,7 +4278,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>47</v>
       </c>
@@ -4309,7 +4310,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>48</v>
       </c>
@@ -4347,7 +4348,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>49</v>
       </c>
@@ -4376,7 +4377,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>50</v>
       </c>
@@ -4417,7 +4418,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>51</v>
       </c>
@@ -4446,7 +4447,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>52</v>
       </c>
@@ -4484,7 +4485,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>53</v>
       </c>
@@ -4513,7 +4514,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>54</v>
       </c>
@@ -4545,7 +4546,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>55</v>
       </c>
@@ -4577,7 +4578,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>56</v>
       </c>
@@ -4606,7 +4607,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>57</v>
       </c>
@@ -4641,7 +4642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>58</v>
       </c>
@@ -4670,7 +4671,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>59</v>
       </c>
@@ -4711,7 +4712,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>60</v>
       </c>
@@ -4746,7 +4747,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>61</v>
       </c>
@@ -4781,7 +4782,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>62</v>
       </c>
@@ -4825,7 +4826,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>63</v>
       </c>
@@ -4872,7 +4873,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>64</v>
       </c>
@@ -4913,7 +4914,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>65</v>
       </c>
@@ -4954,7 +4955,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>66</v>
       </c>
@@ -4995,7 +4996,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5024,7 +5025,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5056,7 +5057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5091,7 +5092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5132,7 +5133,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5164,7 +5165,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5196,7 +5197,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5222,7 +5223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5248,7 +5249,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5292,7 +5293,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5339,7 +5340,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5383,7 +5384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5427,7 +5428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5468,7 +5469,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5512,7 +5513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5550,7 +5551,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5588,7 +5589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5620,7 +5621,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5652,7 +5653,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5678,7 +5679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5707,7 +5708,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5739,7 +5740,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5774,7 +5775,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="91" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5815,7 +5816,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5862,7 +5863,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5891,7 +5892,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5938,7 +5939,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5985,7 +5986,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -6017,7 +6018,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="97" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -6058,7 +6059,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -6105,7 +6106,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -6146,7 +6147,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -6190,7 +6191,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -6237,7 +6238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -6260,7 +6261,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="103" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -6295,7 +6296,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -6336,7 +6337,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -6383,7 +6384,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -6424,7 +6425,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -6459,7 +6460,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -6494,7 +6495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -6535,7 +6536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -6573,7 +6574,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -6611,7 +6612,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -6652,7 +6653,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -6693,7 +6694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -6734,7 +6735,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -6775,7 +6776,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -6819,7 +6820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -6851,7 +6852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -6895,7 +6896,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="119" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -6933,7 +6934,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -6974,7 +6975,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -7003,7 +7004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -7032,7 +7033,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -7079,7 +7080,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="124" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -7123,7 +7124,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -7161,7 +7162,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="126" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -7196,7 +7197,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="127" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -7231,7 +7232,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -7266,7 +7267,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="129" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -7310,7 +7311,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="130" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -7348,7 +7349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -7395,7 +7396,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="132" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -7424,7 +7425,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -7459,7 +7460,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="134" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -7503,7 +7504,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="135" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>134</v>
       </c>
@@ -7550,7 +7551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>135</v>
       </c>
@@ -7594,7 +7595,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="137" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>136</v>
       </c>
@@ -7629,7 +7630,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="138" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -7673,7 +7674,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="139" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -7711,7 +7712,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="140" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -7752,7 +7753,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -7781,7 +7782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -7810,7 +7811,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="143" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -7851,7 +7852,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="144" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -7898,7 +7899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -7945,7 +7946,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -7971,7 +7972,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="147" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -7997,7 +7998,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="148" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>147</v>
       </c>
@@ -8041,7 +8042,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -8082,7 +8083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -8117,7 +8118,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="151" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -8143,7 +8144,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="152" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -8181,7 +8182,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -8222,7 +8223,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="154" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>153</v>
       </c>
@@ -8263,7 +8264,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -8310,7 +8311,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="156" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -8351,7 +8352,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="157" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -8392,7 +8393,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -8433,7 +8434,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -8471,7 +8472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>159</v>
       </c>
@@ -8506,7 +8507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>160</v>
       </c>
@@ -8550,7 +8551,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="162" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>161</v>
       </c>
@@ -8594,7 +8595,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="163" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>162</v>
       </c>
@@ -8638,7 +8639,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="164" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>163</v>
       </c>
@@ -8685,7 +8686,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>164</v>
       </c>
@@ -8723,7 +8724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>165</v>
       </c>
@@ -8761,7 +8762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>166</v>
       </c>
@@ -8790,7 +8791,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>167</v>
       </c>
@@ -8819,7 +8820,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="169" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>168</v>
       </c>
@@ -8860,7 +8861,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="170" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>169</v>
       </c>
@@ -8901,7 +8902,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="171" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>170</v>
       </c>
@@ -8948,7 +8949,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="172" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>171</v>
       </c>
@@ -8992,7 +8993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>172</v>
       </c>
@@ -9039,7 +9040,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="174" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>173</v>
       </c>
@@ -9080,7 +9081,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="175" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>174</v>
       </c>
@@ -9109,7 +9110,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="176" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>175</v>
       </c>
@@ -9144,7 +9145,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>176</v>
       </c>
@@ -9179,7 +9180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="178" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>177</v>
       </c>
@@ -9217,7 +9218,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>178</v>
       </c>
@@ -9255,7 +9256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>179</v>
       </c>
@@ -9284,7 +9285,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="181" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>180</v>
       </c>
@@ -9325,7 +9326,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>181</v>
       </c>
@@ -9357,7 +9358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>182</v>
       </c>
@@ -9398,7 +9399,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>183</v>
       </c>
@@ -9451,7 +9452,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="185" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>184</v>
       </c>
@@ -9489,7 +9490,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>185</v>
       </c>
@@ -9524,7 +9525,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>186</v>
       </c>
@@ -9568,7 +9569,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="188" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>187</v>
       </c>
@@ -9612,7 +9613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>188</v>
       </c>
@@ -9650,7 +9651,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="190" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>189</v>
       </c>
@@ -9685,7 +9686,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="191" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>190</v>
       </c>
@@ -9729,7 +9730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="192" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>191</v>
       </c>
@@ -9761,7 +9762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>192</v>
       </c>
@@ -9802,7 +9803,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="194" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>193</v>
       </c>
@@ -9831,7 +9832,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="195" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -9881,7 +9882,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>195</v>
       </c>
@@ -9928,7 +9929,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>196</v>
       </c>
@@ -9969,7 +9970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>197</v>
       </c>
@@ -10007,7 +10008,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>198</v>
       </c>
@@ -10048,7 +10049,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>199</v>
       </c>
@@ -10092,7 +10093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>200</v>
       </c>
@@ -10133,7 +10134,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>201</v>
       </c>
@@ -10171,7 +10172,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="203" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>202</v>
       </c>
@@ -10209,7 +10210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>203</v>
       </c>
@@ -10241,7 +10242,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="205" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>204</v>
       </c>
@@ -10273,7 +10274,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="206" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>205</v>
       </c>
@@ -10314,7 +10315,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>206</v>
       </c>
@@ -10355,7 +10356,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>207</v>
       </c>
@@ -10399,7 +10400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>208</v>
       </c>
@@ -10443,7 +10444,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>209</v>
       </c>
@@ -10469,7 +10470,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="211" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>210</v>
       </c>
@@ -10510,7 +10511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>211</v>
       </c>
@@ -10548,7 +10549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>212</v>
       </c>
@@ -10583,7 +10584,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="214" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>213</v>
       </c>
@@ -10615,7 +10616,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="215" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>214</v>
       </c>
@@ -10650,7 +10651,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="216" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>215</v>
       </c>
@@ -10688,7 +10689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>216</v>
       </c>
@@ -10729,7 +10730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>217</v>
       </c>
@@ -10764,7 +10765,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="219" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>218</v>
       </c>
@@ -10799,7 +10800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>219</v>
       </c>
@@ -10834,7 +10835,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>220</v>
       </c>
@@ -10881,7 +10882,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="222" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>221</v>
       </c>
@@ -10913,7 +10914,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="223" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>222</v>
       </c>
@@ -10951,7 +10952,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="224" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>223</v>
       </c>
@@ -10995,7 +10996,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>224</v>
       </c>
@@ -11039,7 +11040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="226" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>225</v>
       </c>
@@ -11083,7 +11084,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="227" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>226</v>
       </c>
@@ -11109,7 +11110,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="228" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>227</v>
       </c>
@@ -11135,7 +11136,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="229" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>228</v>
       </c>
@@ -11170,7 +11171,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>229</v>
       </c>
@@ -11217,7 +11218,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>230</v>
       </c>
@@ -11243,7 +11244,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="232" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>231</v>
       </c>
@@ -11290,7 +11291,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="233" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>232</v>
       </c>
@@ -11337,7 +11338,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="234" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>233</v>
       </c>
@@ -11384,7 +11385,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="235" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>234</v>
       </c>
@@ -11428,7 +11429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>235</v>
       </c>
@@ -11475,7 +11476,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="237" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>236</v>
       </c>
@@ -11519,7 +11520,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="238" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>237</v>
       </c>
@@ -11566,7 +11567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>238</v>
       </c>
@@ -11607,7 +11608,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="240" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>239</v>
       </c>
@@ -11651,7 +11652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="241" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>240</v>
       </c>
@@ -11686,7 +11687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>241</v>
       </c>
@@ -11712,7 +11713,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="243" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>242</v>
       </c>
@@ -11753,7 +11754,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>243</v>
       </c>
@@ -11794,7 +11795,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>244</v>
       </c>
@@ -11838,7 +11839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>245</v>
       </c>
@@ -11882,7 +11883,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="247" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>246</v>
       </c>
@@ -11926,7 +11927,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="248" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>247</v>
       </c>
@@ -11970,7 +11971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>248</v>
       </c>
@@ -12008,7 +12009,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>249</v>
       </c>
@@ -12055,7 +12056,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="251" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>250</v>
       </c>
@@ -12096,7 +12097,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>251</v>
       </c>
@@ -12134,7 +12135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>252</v>
       </c>
@@ -12178,7 +12179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>253</v>
       </c>
@@ -12219,7 +12220,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>254</v>
       </c>
@@ -12263,7 +12264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>255</v>
       </c>
@@ -12307,7 +12308,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>256</v>
       </c>
@@ -12348,7 +12349,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="258" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>257</v>
       </c>
@@ -12395,7 +12396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="259" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>258</v>
       </c>
@@ -12433,7 +12434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="260" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>259</v>
       </c>
@@ -12474,7 +12475,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="261" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>260</v>
       </c>
@@ -12512,7 +12513,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="262" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>261</v>
       </c>
@@ -12547,7 +12548,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="263" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>262</v>
       </c>
@@ -12582,7 +12583,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="264" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>263</v>
       </c>
@@ -12623,7 +12624,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>264</v>
       </c>
@@ -12664,7 +12665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>265</v>
       </c>
@@ -12705,7 +12706,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>266</v>
       </c>
@@ -12752,7 +12753,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="268" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>267</v>
       </c>
@@ -12799,7 +12800,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="269" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>268</v>
       </c>
@@ -12831,7 +12832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>269</v>
       </c>
@@ -12866,7 +12867,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="271" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>270</v>
       </c>
@@ -12907,7 +12908,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="272" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>271</v>
       </c>
@@ -12945,7 +12946,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="273" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>272</v>
       </c>
@@ -12980,7 +12981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>273</v>
       </c>
@@ -13015,7 +13016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="275" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>274</v>
       </c>
@@ -13050,7 +13051,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="276" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>275</v>
       </c>
@@ -13100,7 +13101,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="277" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>276</v>
       </c>
@@ -13144,7 +13145,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="278" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>277</v>
       </c>
@@ -13194,7 +13195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="279" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>278</v>
       </c>
@@ -13232,7 +13233,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="280" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>279</v>
       </c>
@@ -13276,7 +13277,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="281" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>280</v>
       </c>
@@ -13326,7 +13327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>281</v>
       </c>
@@ -13373,7 +13374,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="283" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>282</v>
       </c>
@@ -13417,7 +13418,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="284" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>283</v>
       </c>
@@ -13452,7 +13453,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="285" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>284</v>
       </c>
@@ -13499,7 +13500,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="286" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>285</v>
       </c>
@@ -13534,7 +13535,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="287" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>286</v>
       </c>
@@ -13569,7 +13570,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="288" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>287</v>
       </c>
@@ -13595,7 +13596,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="289" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>288</v>
       </c>
@@ -13627,7 +13628,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="290" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>289</v>
       </c>
@@ -13674,7 +13675,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="291" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>290</v>
       </c>
@@ -13718,7 +13719,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="292" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>291</v>
       </c>
@@ -13762,7 +13763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>292</v>
       </c>
@@ -13812,7 +13813,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="294" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>293</v>
       </c>
@@ -13856,7 +13857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="295" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>294</v>
       </c>
@@ -13903,7 +13904,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="296" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>295</v>
       </c>
@@ -13953,7 +13954,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="297" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>296</v>
       </c>
@@ -14003,7 +14004,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="298" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>297</v>
       </c>
@@ -14044,7 +14045,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="299" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>298</v>
       </c>
@@ -14085,7 +14086,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="300" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>299</v>
       </c>
@@ -14129,7 +14130,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="301" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>300</v>
       </c>
@@ -14179,7 +14180,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="302" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>301</v>
       </c>
@@ -14208,7 +14209,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="303" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>302</v>
       </c>
@@ -14252,7 +14253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>303</v>
       </c>
@@ -14299,7 +14300,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="305" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>304</v>
       </c>
@@ -14337,7 +14338,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="306" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>305</v>
       </c>
@@ -14381,7 +14382,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>306</v>
       </c>
@@ -14431,7 +14432,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="308" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>307</v>
       </c>
@@ -14478,7 +14479,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="309" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>308</v>
       </c>
@@ -14528,7 +14529,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="310" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>309</v>
       </c>
@@ -14560,7 +14561,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="311" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>310</v>
       </c>
@@ -14607,7 +14608,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="312" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>311</v>
       </c>
@@ -14642,7 +14643,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="313" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>312</v>
       </c>
@@ -14683,7 +14684,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="314" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>313</v>
       </c>
@@ -14727,7 +14728,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="315" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>314</v>
       </c>
@@ -14768,7 +14769,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="316" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>315</v>
       </c>
@@ -14815,7 +14816,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>316</v>
       </c>
@@ -14859,7 +14860,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>317</v>
       </c>
@@ -14894,7 +14895,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="319" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>318</v>
       </c>
@@ -14941,7 +14942,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="320" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>319</v>
       </c>
@@ -14988,7 +14989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="321" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>320</v>
       </c>
@@ -15029,7 +15030,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="322" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>322</v>
       </c>
@@ -15079,7 +15080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="323" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>323</v>
       </c>
@@ -15129,7 +15130,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="324" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>324</v>
       </c>
@@ -15164,7 +15165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>325</v>
       </c>
@@ -15202,7 +15203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>326</v>
       </c>
@@ -15243,7 +15244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>327</v>
       </c>
@@ -15281,7 +15282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="328" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>328</v>
       </c>
@@ -15328,7 +15329,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="329" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>329</v>
       </c>
@@ -15375,7 +15376,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="330" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>330</v>
       </c>
@@ -15419,7 +15420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="331" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>331</v>
       </c>
@@ -15466,7 +15467,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="332" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>332</v>
       </c>
@@ -15513,7 +15514,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="333" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>333</v>
       </c>
@@ -15551,7 +15552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>334</v>
       </c>
@@ -15592,7 +15593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>336</v>
       </c>
@@ -15630,7 +15631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="336" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>338</v>
       </c>
@@ -15677,7 +15678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="337" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>339</v>
       </c>
@@ -15724,7 +15725,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="338" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>340</v>
       </c>
@@ -15771,7 +15772,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="339" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>341</v>
       </c>
@@ -15818,7 +15819,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="340" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>342</v>
       </c>
@@ -15862,7 +15863,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="341" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>343</v>
       </c>
@@ -15909,7 +15910,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="342" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>344</v>
       </c>
@@ -15950,7 +15951,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>345</v>
       </c>
@@ -15991,7 +15992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>346</v>
       </c>
@@ -16023,7 +16024,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="345" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>347</v>
       </c>
@@ -16055,7 +16056,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="346" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>348</v>
       </c>
@@ -16087,7 +16088,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="347" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>349</v>
       </c>
@@ -16119,7 +16120,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="348" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>350</v>
       </c>
@@ -16154,7 +16155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>351</v>
       </c>
@@ -16186,7 +16187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>352</v>
       </c>
@@ -16218,7 +16219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>353</v>
       </c>
@@ -16259,7 +16260,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="352" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>354</v>
       </c>
@@ -16300,7 +16301,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="353" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>355</v>
       </c>
@@ -16335,7 +16336,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="354" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>356</v>
       </c>
@@ -16379,7 +16380,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="355" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>357</v>
       </c>
@@ -16423,7 +16424,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="356" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>358</v>
       </c>
@@ -16470,7 +16471,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="357" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>359</v>
       </c>
@@ -16520,7 +16521,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="358" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>360</v>
       </c>
@@ -16567,7 +16568,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="359" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>361</v>
       </c>
@@ -16614,7 +16615,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="360" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>362</v>
       </c>
@@ -16661,7 +16662,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="361" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>363</v>
       </c>
@@ -16711,7 +16712,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="362" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>364</v>
       </c>
@@ -16743,7 +16744,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="363" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>365</v>
       </c>
@@ -16775,7 +16776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="364" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>366</v>
       </c>
@@ -16825,7 +16826,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="365" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>367</v>
       </c>
@@ -16872,7 +16873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="366" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>368</v>
       </c>
@@ -16916,7 +16917,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="367" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>369</v>
       </c>
@@ -16963,7 +16964,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="368" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>370</v>
       </c>
@@ -17001,7 +17002,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="369" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>371</v>
       </c>
@@ -17045,7 +17046,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="370" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>372</v>
       </c>
@@ -17083,7 +17084,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="371" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>373</v>
       </c>
@@ -17127,7 +17128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="372" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>374</v>
       </c>
@@ -17174,7 +17175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>375</v>
       </c>
@@ -17209,7 +17210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="374" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>376</v>
       </c>
@@ -17247,7 +17248,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="375" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>377</v>
       </c>
@@ -17285,7 +17286,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="376" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>378</v>
       </c>
@@ -17314,7 +17315,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="377" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>379</v>
       </c>
@@ -17361,7 +17362,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="378" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>380</v>
       </c>
@@ -17408,7 +17409,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="379" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>381</v>
       </c>
@@ -17452,7 +17453,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="380" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>382</v>
       </c>
@@ -17502,7 +17503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>383</v>
       </c>
@@ -17534,7 +17535,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="382" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>384</v>
       </c>
@@ -17575,7 +17576,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="383" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>385</v>
       </c>
@@ -17619,7 +17620,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="384" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>386</v>
       </c>
@@ -17666,7 +17667,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="385" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>387</v>
       </c>
@@ -17713,7 +17714,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="386" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>388</v>
       </c>
@@ -17760,7 +17761,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="387" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>389</v>
       </c>
@@ -17810,7 +17811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>390</v>
       </c>
@@ -17863,7 +17864,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="389" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>391</v>
       </c>
@@ -17904,7 +17905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="390" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>392</v>
       </c>
@@ -17954,7 +17955,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="391" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>393</v>
       </c>
@@ -17998,7 +17999,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="392" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>394</v>
       </c>
@@ -18042,7 +18043,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="393" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>395</v>
       </c>
@@ -18080,7 +18081,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="394" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>396</v>
       </c>
@@ -18115,7 +18116,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="395" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>397</v>
       </c>
@@ -18159,7 +18160,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="396" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>398</v>
       </c>
@@ -18203,7 +18204,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="397" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>399</v>
       </c>
@@ -18250,7 +18251,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="398" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>400</v>
       </c>
@@ -18285,7 +18286,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="399" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>401</v>
       </c>
@@ -18326,7 +18327,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="400" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>402</v>
       </c>
@@ -18352,7 +18353,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="401" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>403</v>
       </c>
@@ -18396,7 +18397,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="402" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>404</v>
       </c>
@@ -18443,7 +18444,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>405</v>
       </c>
@@ -18484,7 +18485,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="404" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>406</v>
       </c>
@@ -18525,7 +18526,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="405" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>407</v>
       </c>
@@ -18572,7 +18573,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="406" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>408</v>
       </c>
@@ -18613,7 +18614,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="407" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>409</v>
       </c>
@@ -18651,7 +18652,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="408" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>410</v>
       </c>
@@ -18686,7 +18687,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="409" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>411</v>
       </c>
@@ -18721,7 +18722,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="410" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>412</v>
       </c>
@@ -18765,7 +18766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>413</v>
       </c>
@@ -18797,7 +18798,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="412" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>414</v>
       </c>
@@ -18838,7 +18839,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="413" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>415</v>
       </c>
@@ -18876,7 +18877,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="414" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>416</v>
       </c>
@@ -18917,7 +18918,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="415" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>417</v>
       </c>
@@ -18958,7 +18959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>418</v>
       </c>
@@ -18999,7 +19000,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="417" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>419</v>
       </c>
@@ -19046,7 +19047,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="418" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>420</v>
       </c>
@@ -19096,7 +19097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="419" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>421</v>
       </c>
@@ -19146,7 +19147,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="420" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>422</v>
       </c>
@@ -19187,7 +19188,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="421" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>423</v>
       </c>
@@ -19231,7 +19232,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="422" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>424</v>
       </c>
@@ -19269,7 +19270,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="423" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>425</v>
       </c>
@@ -19307,7 +19308,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="424" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>426</v>
       </c>
@@ -19354,7 +19355,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="425" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>427</v>
       </c>
@@ -19398,7 +19399,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="426" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>428</v>
       </c>
@@ -19442,7 +19443,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="427" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>429</v>
       </c>
@@ -19486,7 +19487,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="428" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>430</v>
       </c>
@@ -19533,7 +19534,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="429" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>431</v>
       </c>
@@ -19577,7 +19578,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="430" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>432</v>
       </c>
@@ -19618,7 +19619,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="431" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>433</v>
       </c>
@@ -19665,7 +19666,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="432" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>434</v>
       </c>
@@ -19703,7 +19704,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="433" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>435</v>
       </c>
@@ -19747,7 +19748,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="434" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>436</v>
       </c>
@@ -19782,7 +19783,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="435" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>437</v>
       </c>
@@ -19817,7 +19818,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="436" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>438</v>
       </c>
@@ -19855,7 +19856,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="437" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>439</v>
       </c>
@@ -19890,7 +19891,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="438" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>440</v>
       </c>
@@ -19919,7 +19920,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="439" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>441</v>
       </c>
@@ -19951,7 +19952,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="440" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>442</v>
       </c>
@@ -19983,7 +19984,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="441" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>443</v>
       </c>
@@ -20015,7 +20016,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="442" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>444</v>
       </c>
@@ -20062,7 +20063,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>445</v>
       </c>
@@ -20100,7 +20101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="444" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>446</v>
       </c>
@@ -20138,7 +20139,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="445" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>447</v>
       </c>
@@ -20179,7 +20180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="446" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>449</v>
       </c>
@@ -20208,7 +20209,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="447" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>450</v>
       </c>
@@ -20243,7 +20244,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="448" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>451</v>
       </c>
@@ -20281,7 +20282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="449" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>452</v>
       </c>
@@ -20319,7 +20320,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="450" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>453</v>
       </c>
@@ -20366,7 +20367,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="451" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>454</v>
       </c>
@@ -20416,7 +20417,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="452" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>455</v>
       </c>
@@ -20457,7 +20458,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>456</v>
       </c>
@@ -20504,7 +20505,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="454" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>457</v>
       </c>
@@ -20539,7 +20540,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="455" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>458</v>
       </c>
@@ -20580,7 +20581,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="456" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>459</v>
       </c>
@@ -20624,7 +20625,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="457" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>460</v>
       </c>
@@ -20668,7 +20669,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="458" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>461</v>
       </c>
@@ -20706,7 +20707,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="459" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>463</v>
       </c>
@@ -20753,7 +20754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>464</v>
       </c>
@@ -20800,7 +20801,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="461" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>465</v>
       </c>
@@ -20847,7 +20848,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="462" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>466</v>
       </c>
@@ -20894,7 +20895,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="463" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>467</v>
       </c>
@@ -20938,7 +20939,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="464" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>468</v>
       </c>
@@ -20982,7 +20983,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="465" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>469</v>
       </c>
@@ -21023,7 +21024,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="466" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>470</v>
       </c>
@@ -21073,7 +21074,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="467" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>471</v>
       </c>
@@ -21111,7 +21112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="468" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>472</v>
       </c>
@@ -21146,7 +21147,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="469" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>473</v>
       </c>
@@ -21190,7 +21191,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="470" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>474</v>
       </c>
@@ -21237,7 +21238,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="471" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>475</v>
       </c>
@@ -21284,7 +21285,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="472" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>476</v>
       </c>
@@ -21331,7 +21332,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="473" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>477</v>
       </c>
@@ -21378,7 +21379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="474" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>478</v>
       </c>
@@ -21434,7 +21435,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="475" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>479</v>
       </c>
@@ -21481,7 +21482,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="476" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>480</v>
       </c>
@@ -21516,7 +21517,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="477" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>481</v>
       </c>
@@ -21560,7 +21561,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="478" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>482</v>
       </c>
@@ -21595,7 +21596,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="479" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>483</v>
       </c>
@@ -21633,7 +21634,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="480" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>484</v>
       </c>
@@ -21680,7 +21681,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="481" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>485</v>
       </c>
@@ -21715,7 +21716,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="482" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>486</v>
       </c>
@@ -21756,7 +21757,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="483" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>487</v>
       </c>
@@ -21803,7 +21804,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="484" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>488</v>
       </c>
@@ -21838,7 +21839,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="485" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>489</v>
       </c>
@@ -21879,7 +21880,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="486" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>490</v>
       </c>
@@ -21923,7 +21924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="487" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>491</v>
       </c>
@@ -21970,7 +21971,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="488" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>492</v>
       </c>
@@ -22011,7 +22012,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="489" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>493</v>
       </c>
@@ -22058,7 +22059,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="490" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>494</v>
       </c>
@@ -22087,7 +22088,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="491" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>495</v>
       </c>
@@ -22119,7 +22120,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="492" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>496</v>
       </c>
@@ -22145,7 +22146,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="493" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>497</v>
       </c>
@@ -22171,7 +22172,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="494" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>498</v>
       </c>
@@ -22197,7 +22198,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="495" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>499</v>
       </c>
@@ -22226,7 +22227,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="496" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>500</v>
       </c>
@@ -22255,7 +22256,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="497" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>501</v>
       </c>
@@ -22284,7 +22285,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="498" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>502</v>
       </c>
@@ -22334,7 +22335,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="499" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>503</v>
       </c>
@@ -22381,7 +22382,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="500" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>504</v>
       </c>
@@ -22428,7 +22429,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="501" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>505</v>
       </c>
@@ -22457,7 +22458,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="502" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>506</v>
       </c>
@@ -22498,7 +22499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="503" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>507</v>
       </c>
@@ -22545,7 +22546,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="504" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>508</v>
       </c>
@@ -22586,7 +22587,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="505" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>509</v>
       </c>
@@ -22636,7 +22637,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="506" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>510</v>
       </c>
@@ -22671,7 +22672,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="507" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>511</v>
       </c>
@@ -22700,7 +22701,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="508" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>512</v>
       </c>
@@ -22732,7 +22733,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="509" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>513</v>
       </c>
@@ -22758,7 +22759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>514</v>
       </c>
@@ -22793,7 +22794,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="511" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>515</v>
       </c>
@@ -22828,7 +22829,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="512" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>516</v>
       </c>
@@ -22869,7 +22870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="513" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>517</v>
       </c>
@@ -22907,7 +22908,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="514" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>518</v>
       </c>
@@ -22951,7 +22952,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="515" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>519</v>
       </c>
@@ -22989,7 +22990,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="516" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516">
         <v>520</v>
       </c>
@@ -23033,7 +23034,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="517" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>521</v>
       </c>
@@ -23077,7 +23078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="518" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>522</v>
       </c>
@@ -23118,7 +23119,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="519" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>523</v>
       </c>
@@ -23162,7 +23163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="520" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>524</v>
       </c>
@@ -23212,7 +23213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>525</v>
       </c>
@@ -23247,7 +23248,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="522" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>526</v>
       </c>
@@ -23285,7 +23286,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="523" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>527</v>
       </c>
@@ -23323,7 +23324,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="524" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>528</v>
       </c>
@@ -23370,7 +23371,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="525" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>529</v>
       </c>
@@ -23420,7 +23421,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="526" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>530</v>
       </c>
@@ -23467,7 +23468,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="527" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>531</v>
       </c>
@@ -23496,7 +23497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>532</v>
       </c>
@@ -23522,7 +23523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>533</v>
       </c>
@@ -23569,7 +23570,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="530" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>534</v>
       </c>
@@ -23613,7 +23614,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="531" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>535</v>
       </c>
@@ -23654,7 +23655,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="532" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>536</v>
       </c>
@@ -23701,7 +23702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="533" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>537</v>
       </c>
@@ -23745,7 +23746,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="534" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>538</v>
       </c>
@@ -23789,7 +23790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="535" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>539</v>
       </c>
@@ -23833,7 +23834,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="536" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>540</v>
       </c>
@@ -23874,7 +23875,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="537" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>541</v>
       </c>
@@ -23921,7 +23922,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="538" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>542</v>
       </c>
@@ -23959,7 +23960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="539" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>543</v>
       </c>
@@ -24006,7 +24007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="540" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>544</v>
       </c>
@@ -24056,7 +24057,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="541" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>545</v>
       </c>
@@ -24103,7 +24104,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="542" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542">
         <v>546</v>
       </c>
@@ -24138,7 +24139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="543" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>549</v>
       </c>
@@ -24179,7 +24180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="544" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544">
         <v>550</v>
       </c>
@@ -24217,7 +24218,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="545" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545">
         <v>551</v>
       </c>
@@ -24255,7 +24256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="546" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546">
         <v>552</v>
       </c>
@@ -24299,7 +24300,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="547" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547">
         <v>553</v>
       </c>
@@ -24346,7 +24347,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="548" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548">
         <v>554</v>
       </c>
@@ -24381,7 +24382,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="549" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549">
         <v>555</v>
       </c>
@@ -24428,7 +24429,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="550" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550">
         <v>556</v>
       </c>
@@ -24475,7 +24476,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="551" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>557</v>
       </c>
@@ -24519,7 +24520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="552" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>558</v>
       </c>
@@ -24563,7 +24564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="553" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553">
         <v>559</v>
       </c>
@@ -24610,7 +24611,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="554" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>560</v>
       </c>
@@ -24648,7 +24649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="555" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>561</v>
       </c>
@@ -24695,7 +24696,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="556" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>4097</v>
       </c>
@@ -24730,7 +24731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="557" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557">
         <v>4098</v>
       </c>
@@ -24756,7 +24757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="558" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>4099</v>
       </c>
@@ -24797,7 +24798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="559" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>4100</v>
       </c>
@@ -24838,7 +24839,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="560" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>4101</v>
       </c>
@@ -24885,7 +24886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="561" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>4102</v>
       </c>
@@ -24926,7 +24927,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="562" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>4103</v>
       </c>
@@ -25251,6 +25252,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:AE583" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Virtual-precondition"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AE583">
       <sortCondition ref="A2:A583"/>
     </sortState>

--- a/doc/equip/Equip.xlsx
+++ b/doc/equip/Equip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuoMuoRuoProject\doc\equip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5AA8D3-E676-451C-94D1-A6AB9C89CB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202039A5-AF35-49EC-99A9-D998585A7445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2553,7 +2553,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AE583"/>
   <sheetFormatPr defaultColWidth="10.06640625" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2773,7 +2772,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2811,7 +2810,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2852,7 +2851,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2893,7 +2892,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2934,7 +2933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2975,7 +2974,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3013,7 +3012,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3051,7 +3050,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3089,7 +3088,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3127,7 +3126,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3168,7 +3167,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3206,7 +3205,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -3247,7 +3246,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3273,7 +3272,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3299,7 +3298,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -3328,7 +3327,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3363,7 +3362,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3398,7 +3397,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
@@ -3436,7 +3435,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
@@ -3468,7 +3467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
@@ -3497,7 +3496,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
@@ -3526,7 +3525,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
@@ -3558,7 +3557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
@@ -3590,7 +3589,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
@@ -3622,7 +3621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -3663,7 +3662,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -3704,7 +3703,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
@@ -3736,7 +3735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
@@ -3765,7 +3764,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
@@ -3794,7 +3793,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
@@ -3826,7 +3825,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>31</v>
       </c>
@@ -3855,7 +3854,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>32</v>
       </c>
@@ -3887,7 +3886,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>33</v>
       </c>
@@ -3916,7 +3915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>34</v>
       </c>
@@ -3945,7 +3944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>35</v>
       </c>
@@ -3974,7 +3973,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>36</v>
       </c>
@@ -4006,7 +4005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>37</v>
       </c>
@@ -4035,7 +4034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>38</v>
       </c>
@@ -4064,7 +4063,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>39</v>
       </c>
@@ -4093,7 +4092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>40</v>
       </c>
@@ -4122,7 +4121,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>41</v>
       </c>
@@ -4148,7 +4147,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>42</v>
       </c>
@@ -4171,7 +4170,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="45" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>43</v>
       </c>
@@ -4194,7 +4193,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="46" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>44</v>
       </c>
@@ -4220,7 +4219,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>45</v>
       </c>
@@ -4246,7 +4245,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="48" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>46</v>
       </c>
@@ -4278,7 +4277,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>47</v>
       </c>
@@ -4310,7 +4309,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>48</v>
       </c>
@@ -4348,7 +4347,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>49</v>
       </c>
@@ -4377,7 +4376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>50</v>
       </c>
@@ -4418,7 +4417,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>51</v>
       </c>
@@ -4447,7 +4446,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>52</v>
       </c>
@@ -4485,7 +4484,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>53</v>
       </c>
@@ -4514,7 +4513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>54</v>
       </c>
@@ -4546,7 +4545,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>55</v>
       </c>
@@ -4578,7 +4577,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>56</v>
       </c>
@@ -4607,7 +4606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>57</v>
       </c>
@@ -4642,7 +4641,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>58</v>
       </c>
@@ -4671,7 +4670,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>59</v>
       </c>
@@ -4712,7 +4711,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>60</v>
       </c>
@@ -4747,7 +4746,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>61</v>
       </c>
@@ -4782,7 +4781,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>62</v>
       </c>
@@ -4826,7 +4825,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>63</v>
       </c>
@@ -4873,7 +4872,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>64</v>
       </c>
@@ -4914,7 +4913,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>65</v>
       </c>
@@ -4955,7 +4954,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>66</v>
       </c>
@@ -4996,7 +4995,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5025,7 +5024,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5057,7 +5056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5092,7 +5091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5133,7 +5132,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5165,7 +5164,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="74" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5197,7 +5196,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="75" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5223,7 +5222,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5249,7 +5248,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="77" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5293,7 +5292,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5340,7 +5339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5384,7 +5383,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5428,7 +5427,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5469,7 +5468,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5513,7 +5512,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5551,7 +5550,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5589,7 +5588,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5621,7 +5620,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5653,7 +5652,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5679,7 +5678,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5708,7 +5707,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5740,7 +5739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5775,7 +5774,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="91" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5816,7 +5815,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5863,7 +5862,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5892,7 +5891,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5939,7 +5938,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5986,7 +5985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -6018,7 +6017,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="97" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -6059,7 +6058,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -6106,7 +6105,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -6147,7 +6146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -6191,7 +6190,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -6238,7 +6237,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -6261,7 +6260,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="103" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -6296,7 +6295,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -6337,7 +6336,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -6384,7 +6383,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -6425,7 +6424,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -6460,7 +6459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -6495,7 +6494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -6536,7 +6535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -6574,7 +6573,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -6612,7 +6611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -6653,7 +6652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -6694,7 +6693,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -6735,7 +6734,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -6776,7 +6775,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -6820,7 +6819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -6852,7 +6851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -6896,7 +6895,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="119" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -6934,7 +6933,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -6975,7 +6974,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -7004,7 +7003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -7033,7 +7032,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -7080,7 +7079,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="124" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -7124,7 +7123,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -7162,7 +7161,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="126" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -7197,7 +7196,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="127" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -7232,7 +7231,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -7267,7 +7266,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="129" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -7311,7 +7310,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="130" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -7349,7 +7348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -7396,7 +7395,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="132" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -7425,7 +7424,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -7460,7 +7459,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="134" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -7504,7 +7503,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="135" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>134</v>
       </c>
@@ -7551,7 +7550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>135</v>
       </c>
@@ -7595,7 +7594,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="137" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>136</v>
       </c>
@@ -7630,7 +7629,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="138" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -7674,7 +7673,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="139" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -7712,7 +7711,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="140" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -7753,7 +7752,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -7782,7 +7781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -7811,7 +7810,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="143" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -7852,7 +7851,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="144" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -7899,7 +7898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -7946,7 +7945,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -7972,7 +7971,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="147" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -7998,7 +7997,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="148" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>147</v>
       </c>
@@ -8042,7 +8041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -8083,7 +8082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -8118,7 +8117,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="151" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -8144,7 +8143,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="152" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -8182,7 +8181,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -8223,7 +8222,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="154" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>153</v>
       </c>
@@ -8264,7 +8263,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -8311,7 +8310,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="156" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -8352,7 +8351,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="157" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -8393,7 +8392,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -8434,7 +8433,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -8472,7 +8471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>159</v>
       </c>
@@ -8507,7 +8506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>160</v>
       </c>
@@ -8551,7 +8550,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="162" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>161</v>
       </c>
@@ -8595,7 +8594,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="163" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>162</v>
       </c>
@@ -8639,7 +8638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="164" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>163</v>
       </c>
@@ -8686,7 +8685,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>164</v>
       </c>
@@ -8724,7 +8723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>165</v>
       </c>
@@ -8762,7 +8761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>166</v>
       </c>
@@ -8791,7 +8790,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>167</v>
       </c>
@@ -8820,7 +8819,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="169" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>168</v>
       </c>
@@ -8861,7 +8860,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="170" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>169</v>
       </c>
@@ -8902,7 +8901,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="171" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>170</v>
       </c>
@@ -8949,7 +8948,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="172" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>171</v>
       </c>
@@ -8993,7 +8992,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>172</v>
       </c>
@@ -9040,7 +9039,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="174" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>173</v>
       </c>
@@ -9081,7 +9080,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="175" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>174</v>
       </c>
@@ -9110,7 +9109,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="176" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>175</v>
       </c>
@@ -9145,7 +9144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>176</v>
       </c>
@@ -9180,7 +9179,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="178" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>177</v>
       </c>
@@ -9218,7 +9217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>178</v>
       </c>
@@ -9256,7 +9255,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>179</v>
       </c>
@@ -9285,7 +9284,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="181" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>180</v>
       </c>
@@ -9326,7 +9325,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>181</v>
       </c>
@@ -9358,7 +9357,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>182</v>
       </c>
@@ -9399,7 +9398,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>183</v>
       </c>
@@ -9452,7 +9451,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="185" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>184</v>
       </c>
@@ -9490,7 +9489,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>185</v>
       </c>
@@ -9525,7 +9524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>186</v>
       </c>
@@ -9569,7 +9568,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="188" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>187</v>
       </c>
@@ -9613,7 +9612,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>188</v>
       </c>
@@ -9651,7 +9650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="190" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>189</v>
       </c>
@@ -9686,7 +9685,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="191" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>190</v>
       </c>
@@ -9730,7 +9729,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="192" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>191</v>
       </c>
@@ -9762,7 +9761,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>192</v>
       </c>
@@ -9803,7 +9802,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="194" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>193</v>
       </c>
@@ -9832,7 +9831,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="195" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -9882,7 +9881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>195</v>
       </c>
@@ -9929,7 +9928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>196</v>
       </c>
@@ -9970,7 +9969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>197</v>
       </c>
@@ -10008,7 +10007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>198</v>
       </c>
@@ -10049,7 +10048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>199</v>
       </c>
@@ -10093,7 +10092,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>200</v>
       </c>
@@ -10134,7 +10133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>201</v>
       </c>
@@ -10172,7 +10171,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="203" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>202</v>
       </c>
@@ -10210,7 +10209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>203</v>
       </c>
@@ -10242,7 +10241,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="205" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>204</v>
       </c>
@@ -10274,7 +10273,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="206" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>205</v>
       </c>
@@ -10315,7 +10314,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>206</v>
       </c>
@@ -10356,7 +10355,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>207</v>
       </c>
@@ -10400,7 +10399,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>208</v>
       </c>
@@ -10444,7 +10443,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>209</v>
       </c>
@@ -10470,7 +10469,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="211" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>210</v>
       </c>
@@ -10511,7 +10510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>211</v>
       </c>
@@ -10549,7 +10548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>212</v>
       </c>
@@ -10584,7 +10583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="214" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>213</v>
       </c>
@@ -10616,7 +10615,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="215" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>214</v>
       </c>
@@ -10651,7 +10650,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="216" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>215</v>
       </c>
@@ -10689,7 +10688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>216</v>
       </c>
@@ -10730,7 +10729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>217</v>
       </c>
@@ -10765,7 +10764,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="219" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>218</v>
       </c>
@@ -10800,7 +10799,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>219</v>
       </c>
@@ -10835,7 +10834,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>220</v>
       </c>
@@ -10882,7 +10881,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="222" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>221</v>
       </c>
@@ -10914,7 +10913,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="223" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>222</v>
       </c>
@@ -10952,7 +10951,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="224" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>223</v>
       </c>
@@ -10996,7 +10995,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>224</v>
       </c>
@@ -11040,7 +11039,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="226" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>225</v>
       </c>
@@ -11084,7 +11083,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="227" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>226</v>
       </c>
@@ -11110,7 +11109,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="228" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>227</v>
       </c>
@@ -11136,7 +11135,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="229" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>228</v>
       </c>
@@ -11171,7 +11170,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>229</v>
       </c>
@@ -11218,7 +11217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>230</v>
       </c>
@@ -11244,7 +11243,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="232" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>231</v>
       </c>
@@ -11291,7 +11290,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="233" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>232</v>
       </c>
@@ -11338,7 +11337,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="234" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>233</v>
       </c>
@@ -11385,7 +11384,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="235" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>234</v>
       </c>
@@ -11429,7 +11428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>235</v>
       </c>
@@ -11476,7 +11475,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="237" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>236</v>
       </c>
@@ -11520,7 +11519,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="238" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>237</v>
       </c>
@@ -11567,7 +11566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>238</v>
       </c>
@@ -11608,7 +11607,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="240" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>239</v>
       </c>
@@ -11652,7 +11651,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="241" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>240</v>
       </c>
@@ -11687,7 +11686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>241</v>
       </c>
@@ -11713,7 +11712,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="243" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>242</v>
       </c>
@@ -11754,7 +11753,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>243</v>
       </c>
@@ -11795,7 +11794,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>244</v>
       </c>
@@ -11839,7 +11838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>245</v>
       </c>
@@ -11883,7 +11882,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="247" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>246</v>
       </c>
@@ -11927,7 +11926,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="248" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>247</v>
       </c>
@@ -11971,7 +11970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>248</v>
       </c>
@@ -12009,7 +12008,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>249</v>
       </c>
@@ -12056,7 +12055,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="251" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>250</v>
       </c>
@@ -12097,7 +12096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>251</v>
       </c>
@@ -12135,7 +12134,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>252</v>
       </c>
@@ -12179,7 +12178,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>253</v>
       </c>
@@ -12220,7 +12219,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>254</v>
       </c>
@@ -12264,7 +12263,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>255</v>
       </c>
@@ -12308,7 +12307,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>256</v>
       </c>
@@ -12349,7 +12348,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="258" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>257</v>
       </c>
@@ -12396,7 +12395,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="259" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>258</v>
       </c>
@@ -12434,7 +12433,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="260" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>259</v>
       </c>
@@ -12475,7 +12474,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="261" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>260</v>
       </c>
@@ -12513,7 +12512,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="262" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>261</v>
       </c>
@@ -12548,7 +12547,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="263" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>262</v>
       </c>
@@ -12583,7 +12582,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="264" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>263</v>
       </c>
@@ -12624,7 +12623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>264</v>
       </c>
@@ -12665,7 +12664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>265</v>
       </c>
@@ -12706,7 +12705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>266</v>
       </c>
@@ -12753,7 +12752,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="268" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>267</v>
       </c>
@@ -12800,7 +12799,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="269" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>268</v>
       </c>
@@ -12832,7 +12831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>269</v>
       </c>
@@ -12867,7 +12866,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="271" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>270</v>
       </c>
@@ -12908,7 +12907,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="272" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>271</v>
       </c>
@@ -12946,7 +12945,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="273" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>272</v>
       </c>
@@ -12981,7 +12980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>273</v>
       </c>
@@ -13016,7 +13015,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="275" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>274</v>
       </c>
@@ -13051,7 +13050,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="276" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>275</v>
       </c>
@@ -13101,7 +13100,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="277" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>276</v>
       </c>
@@ -13145,7 +13144,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="278" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>277</v>
       </c>
@@ -13195,7 +13194,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="279" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>278</v>
       </c>
@@ -13233,7 +13232,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="280" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>279</v>
       </c>
@@ -13277,7 +13276,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="281" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>280</v>
       </c>
@@ -13327,7 +13326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>281</v>
       </c>
@@ -13374,7 +13373,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="283" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>282</v>
       </c>
@@ -13418,7 +13417,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="284" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>283</v>
       </c>
@@ -13453,7 +13452,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="285" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>284</v>
       </c>
@@ -13500,7 +13499,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="286" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>285</v>
       </c>
@@ -13535,7 +13534,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="287" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>286</v>
       </c>
@@ -13570,7 +13569,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="288" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>287</v>
       </c>
@@ -13596,7 +13595,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="289" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>288</v>
       </c>
@@ -13628,7 +13627,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="290" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>289</v>
       </c>
@@ -13675,7 +13674,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="291" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>290</v>
       </c>
@@ -13719,7 +13718,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="292" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>291</v>
       </c>
@@ -13763,7 +13762,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>292</v>
       </c>
@@ -13813,7 +13812,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="294" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>293</v>
       </c>
@@ -13857,7 +13856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="295" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>294</v>
       </c>
@@ -13904,7 +13903,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="296" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>295</v>
       </c>
@@ -13954,7 +13953,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="297" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>296</v>
       </c>
@@ -14004,7 +14003,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="298" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>297</v>
       </c>
@@ -14045,7 +14044,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="299" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>298</v>
       </c>
@@ -14086,7 +14085,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="300" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>299</v>
       </c>
@@ -14130,7 +14129,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="301" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>300</v>
       </c>
@@ -14180,7 +14179,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="302" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>301</v>
       </c>
@@ -14209,7 +14208,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="303" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>302</v>
       </c>
@@ -14253,7 +14252,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>303</v>
       </c>
@@ -14300,7 +14299,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="305" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>304</v>
       </c>
@@ -14338,7 +14337,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="306" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>305</v>
       </c>
@@ -14382,7 +14381,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>306</v>
       </c>
@@ -14432,7 +14431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="308" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>307</v>
       </c>
@@ -14479,7 +14478,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="309" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>308</v>
       </c>
@@ -14529,7 +14528,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="310" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>309</v>
       </c>
@@ -14561,7 +14560,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="311" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>310</v>
       </c>
@@ -14608,7 +14607,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="312" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>311</v>
       </c>
@@ -14643,7 +14642,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="313" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>312</v>
       </c>
@@ -14684,7 +14683,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="314" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>313</v>
       </c>
@@ -14728,7 +14727,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="315" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>314</v>
       </c>
@@ -14769,7 +14768,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="316" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>315</v>
       </c>
@@ -14816,7 +14815,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>316</v>
       </c>
@@ -14860,7 +14859,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>317</v>
       </c>
@@ -14895,7 +14894,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="319" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>318</v>
       </c>
@@ -14942,7 +14941,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="320" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>319</v>
       </c>
@@ -14989,7 +14988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="321" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>320</v>
       </c>
@@ -15030,7 +15029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="322" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>322</v>
       </c>
@@ -15080,7 +15079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="323" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>323</v>
       </c>
@@ -15130,7 +15129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="324" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>324</v>
       </c>
@@ -15165,7 +15164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>325</v>
       </c>
@@ -15203,7 +15202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>326</v>
       </c>
@@ -15244,7 +15243,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>327</v>
       </c>
@@ -15282,7 +15281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="328" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>328</v>
       </c>
@@ -15329,7 +15328,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="329" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>329</v>
       </c>
@@ -15376,7 +15375,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="330" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>330</v>
       </c>
@@ -15420,7 +15419,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="331" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>331</v>
       </c>
@@ -15467,7 +15466,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="332" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>332</v>
       </c>
@@ -15514,7 +15513,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="333" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>333</v>
       </c>
@@ -15552,7 +15551,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>334</v>
       </c>
@@ -15593,7 +15592,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>336</v>
       </c>
@@ -15631,7 +15630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="336" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>338</v>
       </c>
@@ -15678,7 +15677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="337" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>339</v>
       </c>
@@ -15725,7 +15724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="338" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>340</v>
       </c>
@@ -15772,7 +15771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="339" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>341</v>
       </c>
@@ -15819,7 +15818,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="340" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>342</v>
       </c>
@@ -15863,7 +15862,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="341" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>343</v>
       </c>
@@ -15910,7 +15909,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="342" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>344</v>
       </c>
@@ -15951,7 +15950,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>345</v>
       </c>
@@ -15992,7 +15991,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>346</v>
       </c>
@@ -16024,7 +16023,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="345" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>347</v>
       </c>
@@ -16056,7 +16055,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="346" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>348</v>
       </c>
@@ -16088,7 +16087,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="347" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>349</v>
       </c>
@@ -16120,7 +16119,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="348" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>350</v>
       </c>
@@ -16155,7 +16154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>351</v>
       </c>
@@ -16187,7 +16186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>352</v>
       </c>
@@ -16219,7 +16218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>353</v>
       </c>
@@ -16260,7 +16259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="352" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>354</v>
       </c>
@@ -16301,7 +16300,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="353" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>355</v>
       </c>
@@ -16336,7 +16335,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="354" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>356</v>
       </c>
@@ -16380,7 +16379,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="355" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>357</v>
       </c>
@@ -16424,7 +16423,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="356" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>358</v>
       </c>
@@ -16471,7 +16470,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="357" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>359</v>
       </c>
@@ -16521,7 +16520,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="358" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>360</v>
       </c>
@@ -16568,7 +16567,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="359" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>361</v>
       </c>
@@ -16615,7 +16614,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="360" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>362</v>
       </c>
@@ -16662,7 +16661,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="361" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>363</v>
       </c>
@@ -16712,7 +16711,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="362" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>364</v>
       </c>
@@ -16744,7 +16743,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="363" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>365</v>
       </c>
@@ -16776,7 +16775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="364" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>366</v>
       </c>
@@ -16826,7 +16825,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="365" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>367</v>
       </c>
@@ -16873,7 +16872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="366" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>368</v>
       </c>
@@ -16917,7 +16916,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="367" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>369</v>
       </c>
@@ -16964,7 +16963,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="368" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>370</v>
       </c>
@@ -17002,7 +17001,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="369" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>371</v>
       </c>
@@ -17046,7 +17045,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="370" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>372</v>
       </c>
@@ -17084,7 +17083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="371" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>373</v>
       </c>
@@ -17128,7 +17127,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="372" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>374</v>
       </c>
@@ -17175,7 +17174,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>375</v>
       </c>
@@ -17210,7 +17209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="374" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>376</v>
       </c>
@@ -17248,7 +17247,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="375" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>377</v>
       </c>
@@ -17286,7 +17285,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="376" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>378</v>
       </c>
@@ -17315,7 +17314,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="377" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>379</v>
       </c>
@@ -17362,7 +17361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="378" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>380</v>
       </c>
@@ -17409,7 +17408,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="379" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>381</v>
       </c>
@@ -17453,7 +17452,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="380" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>382</v>
       </c>
@@ -17503,7 +17502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>383</v>
       </c>
@@ -17535,7 +17534,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="382" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>384</v>
       </c>
@@ -17576,7 +17575,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="383" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>385</v>
       </c>
@@ -17620,7 +17619,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="384" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>386</v>
       </c>
@@ -17667,7 +17666,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="385" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>387</v>
       </c>
@@ -17714,7 +17713,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="386" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>388</v>
       </c>
@@ -17761,7 +17760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="387" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>389</v>
       </c>
@@ -17811,7 +17810,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>390</v>
       </c>
@@ -17864,7 +17863,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="389" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>391</v>
       </c>
@@ -17905,7 +17904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="390" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>392</v>
       </c>
@@ -17955,7 +17954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="391" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>393</v>
       </c>
@@ -17999,7 +17998,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="392" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>394</v>
       </c>
@@ -18043,7 +18042,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="393" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>395</v>
       </c>
@@ -18081,7 +18080,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="394" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>396</v>
       </c>
@@ -18116,7 +18115,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="395" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>397</v>
       </c>
@@ -18160,7 +18159,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="396" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>398</v>
       </c>
@@ -18204,7 +18203,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="397" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>399</v>
       </c>
@@ -18251,7 +18250,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="398" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>400</v>
       </c>
@@ -18286,7 +18285,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="399" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>401</v>
       </c>
@@ -18327,7 +18326,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="400" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>402</v>
       </c>
@@ -18353,7 +18352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="401" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>403</v>
       </c>
@@ -18397,7 +18396,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="402" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>404</v>
       </c>
@@ -18444,7 +18443,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>405</v>
       </c>
@@ -18485,7 +18484,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="404" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>406</v>
       </c>
@@ -18526,7 +18525,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="405" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>407</v>
       </c>
@@ -18573,7 +18572,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="406" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>408</v>
       </c>
@@ -18614,7 +18613,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="407" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>409</v>
       </c>
@@ -18652,7 +18651,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="408" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>410</v>
       </c>
@@ -18687,7 +18686,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="409" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>411</v>
       </c>
@@ -18722,7 +18721,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="410" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>412</v>
       </c>
@@ -18766,7 +18765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>413</v>
       </c>
@@ -18798,7 +18797,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="412" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>414</v>
       </c>
@@ -18839,7 +18838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="413" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>415</v>
       </c>
@@ -18877,7 +18876,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="414" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>416</v>
       </c>
@@ -18918,7 +18917,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="415" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>417</v>
       </c>
@@ -18959,7 +18958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>418</v>
       </c>
@@ -19000,7 +18999,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="417" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>419</v>
       </c>
@@ -19047,7 +19046,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="418" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>420</v>
       </c>
@@ -19097,7 +19096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="419" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>421</v>
       </c>
@@ -19147,7 +19146,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="420" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>422</v>
       </c>
@@ -19188,7 +19187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="421" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>423</v>
       </c>
@@ -19232,7 +19231,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="422" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>424</v>
       </c>
@@ -19270,7 +19269,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="423" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>425</v>
       </c>
@@ -19308,7 +19307,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="424" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>426</v>
       </c>
@@ -19355,7 +19354,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="425" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>427</v>
       </c>
@@ -19399,7 +19398,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="426" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>428</v>
       </c>
@@ -19443,7 +19442,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="427" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>429</v>
       </c>
@@ -19487,7 +19486,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="428" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>430</v>
       </c>
@@ -19534,7 +19533,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="429" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>431</v>
       </c>
@@ -19578,7 +19577,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="430" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>432</v>
       </c>
@@ -19619,7 +19618,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="431" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>433</v>
       </c>
@@ -19666,7 +19665,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="432" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>434</v>
       </c>
@@ -19704,7 +19703,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="433" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>435</v>
       </c>
@@ -19748,7 +19747,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="434" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>436</v>
       </c>
@@ -19783,7 +19782,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="435" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>437</v>
       </c>
@@ -19818,7 +19817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="436" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>438</v>
       </c>
@@ -19856,7 +19855,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="437" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>439</v>
       </c>
@@ -19891,7 +19890,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="438" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>440</v>
       </c>
@@ -19920,7 +19919,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="439" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>441</v>
       </c>
@@ -19952,7 +19951,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="440" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>442</v>
       </c>
@@ -19984,7 +19983,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="441" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>443</v>
       </c>
@@ -20016,7 +20015,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="442" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>444</v>
       </c>
@@ -20063,7 +20062,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>445</v>
       </c>
@@ -20101,7 +20100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="444" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>446</v>
       </c>
@@ -20139,7 +20138,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="445" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>447</v>
       </c>
@@ -20180,7 +20179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="446" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>449</v>
       </c>
@@ -20209,7 +20208,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="447" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>450</v>
       </c>
@@ -20244,7 +20243,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="448" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>451</v>
       </c>
@@ -20282,7 +20281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="449" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>452</v>
       </c>
@@ -20320,7 +20319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="450" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>453</v>
       </c>
@@ -20367,7 +20366,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="451" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>454</v>
       </c>
@@ -20417,7 +20416,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="452" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>455</v>
       </c>
@@ -20458,7 +20457,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>456</v>
       </c>
@@ -20505,7 +20504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="454" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>457</v>
       </c>
@@ -20540,7 +20539,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="455" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>458</v>
       </c>
@@ -20581,7 +20580,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="456" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>459</v>
       </c>
@@ -20625,7 +20624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="457" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>460</v>
       </c>
@@ -20669,7 +20668,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="458" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>461</v>
       </c>
@@ -20707,7 +20706,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="459" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>463</v>
       </c>
@@ -20754,7 +20753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>464</v>
       </c>
@@ -20801,7 +20800,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="461" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>465</v>
       </c>
@@ -20848,7 +20847,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="462" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>466</v>
       </c>
@@ -20895,7 +20894,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="463" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>467</v>
       </c>
@@ -20939,7 +20938,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="464" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>468</v>
       </c>
@@ -20983,7 +20982,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="465" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>469</v>
       </c>
@@ -21024,7 +21023,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="466" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>470</v>
       </c>
@@ -21074,7 +21073,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="467" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>471</v>
       </c>
@@ -21112,7 +21111,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="468" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>472</v>
       </c>
@@ -21147,7 +21146,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="469" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>473</v>
       </c>
@@ -21191,7 +21190,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="470" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>474</v>
       </c>
@@ -21238,7 +21237,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="471" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>475</v>
       </c>
@@ -21285,7 +21284,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="472" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>476</v>
       </c>
@@ -21332,7 +21331,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="473" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>477</v>
       </c>
@@ -21379,7 +21378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="474" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>478</v>
       </c>
@@ -21435,7 +21434,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="475" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>479</v>
       </c>
@@ -21482,7 +21481,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="476" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>480</v>
       </c>
@@ -21517,7 +21516,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="477" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>481</v>
       </c>
@@ -21561,7 +21560,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="478" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>482</v>
       </c>
@@ -21596,7 +21595,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="479" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>483</v>
       </c>
@@ -21634,7 +21633,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="480" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>484</v>
       </c>
@@ -21681,7 +21680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="481" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>485</v>
       </c>
@@ -21716,7 +21715,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="482" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>486</v>
       </c>
@@ -21757,7 +21756,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="483" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>487</v>
       </c>
@@ -21804,7 +21803,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="484" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>488</v>
       </c>
@@ -21839,7 +21838,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="485" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>489</v>
       </c>
@@ -21880,7 +21879,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="486" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>490</v>
       </c>
@@ -21924,7 +21923,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="487" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>491</v>
       </c>
@@ -21971,7 +21970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="488" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>492</v>
       </c>
@@ -22012,7 +22011,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="489" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>493</v>
       </c>
@@ -22059,7 +22058,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="490" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>494</v>
       </c>
@@ -22088,7 +22087,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="491" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>495</v>
       </c>
@@ -22120,7 +22119,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="492" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>496</v>
       </c>
@@ -22146,7 +22145,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="493" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>497</v>
       </c>
@@ -22172,7 +22171,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="494" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>498</v>
       </c>
@@ -22198,7 +22197,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="495" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>499</v>
       </c>
@@ -22227,7 +22226,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="496" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>500</v>
       </c>
@@ -22256,7 +22255,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="497" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>501</v>
       </c>
@@ -22285,7 +22284,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="498" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>502</v>
       </c>
@@ -22335,7 +22334,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="499" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>503</v>
       </c>
@@ -22382,7 +22381,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="500" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>504</v>
       </c>
@@ -22429,7 +22428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="501" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>505</v>
       </c>
@@ -22458,7 +22457,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="502" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>506</v>
       </c>
@@ -22499,7 +22498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="503" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>507</v>
       </c>
@@ -22546,7 +22545,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="504" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>508</v>
       </c>
@@ -22587,7 +22586,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="505" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>509</v>
       </c>
@@ -22637,7 +22636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="506" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>510</v>
       </c>
@@ -22672,7 +22671,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="507" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>511</v>
       </c>
@@ -22701,7 +22700,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="508" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>512</v>
       </c>
@@ -22733,7 +22732,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="509" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>513</v>
       </c>
@@ -22759,7 +22758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>514</v>
       </c>
@@ -22794,7 +22793,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="511" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>515</v>
       </c>
@@ -22829,7 +22828,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="512" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>516</v>
       </c>
@@ -22870,7 +22869,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="513" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>517</v>
       </c>
@@ -22908,7 +22907,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="514" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>518</v>
       </c>
@@ -22952,7 +22951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="515" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>519</v>
       </c>
@@ -22990,7 +22989,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="516" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A516">
         <v>520</v>
       </c>
@@ -23034,7 +23033,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="517" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>521</v>
       </c>
@@ -23078,7 +23077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="518" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>522</v>
       </c>
@@ -23119,7 +23118,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="519" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>523</v>
       </c>
@@ -23163,7 +23162,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="520" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>524</v>
       </c>
@@ -23213,7 +23212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>525</v>
       </c>
@@ -23248,7 +23247,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="522" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>526</v>
       </c>
@@ -23286,7 +23285,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="523" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>527</v>
       </c>
@@ -23324,7 +23323,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="524" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>528</v>
       </c>
@@ -23371,7 +23370,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="525" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>529</v>
       </c>
@@ -23421,7 +23420,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="526" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>530</v>
       </c>
@@ -23468,7 +23467,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="527" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>531</v>
       </c>
@@ -23497,7 +23496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>532</v>
       </c>
@@ -23523,7 +23522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>533</v>
       </c>
@@ -23570,7 +23569,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="530" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>534</v>
       </c>
@@ -23614,7 +23613,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="531" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>535</v>
       </c>
@@ -23655,7 +23654,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="532" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>536</v>
       </c>
@@ -23702,7 +23701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="533" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>537</v>
       </c>
@@ -23746,7 +23745,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="534" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>538</v>
       </c>
@@ -23790,7 +23789,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="535" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>539</v>
       </c>
@@ -23834,7 +23833,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="536" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>540</v>
       </c>
@@ -23875,7 +23874,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="537" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>541</v>
       </c>
@@ -23922,7 +23921,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="538" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>542</v>
       </c>
@@ -23960,7 +23959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="539" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>543</v>
       </c>
@@ -24007,7 +24006,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="540" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>544</v>
       </c>
@@ -24057,7 +24056,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="541" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>545</v>
       </c>
@@ -24104,7 +24103,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="542" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A542">
         <v>546</v>
       </c>
@@ -24139,7 +24138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="543" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>549</v>
       </c>
@@ -24180,7 +24179,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="544" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A544">
         <v>550</v>
       </c>
@@ -24218,7 +24217,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="545" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A545">
         <v>551</v>
       </c>
@@ -24256,7 +24255,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="546" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A546">
         <v>552</v>
       </c>
@@ -24300,7 +24299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="547" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A547">
         <v>553</v>
       </c>
@@ -24347,7 +24346,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="548" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A548">
         <v>554</v>
       </c>
@@ -24382,7 +24381,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="549" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A549">
         <v>555</v>
       </c>
@@ -24429,7 +24428,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="550" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A550">
         <v>556</v>
       </c>
@@ -24476,7 +24475,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="551" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>557</v>
       </c>
@@ -24520,7 +24519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="552" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>558</v>
       </c>
@@ -24564,7 +24563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="553" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A553">
         <v>559</v>
       </c>
@@ -24611,7 +24610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="554" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>560</v>
       </c>
@@ -24649,7 +24648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="555" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>561</v>
       </c>
@@ -24696,7 +24695,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="556" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>4097</v>
       </c>
@@ -24731,7 +24730,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="557" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A557">
         <v>4098</v>
       </c>
@@ -24757,7 +24756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="558" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>4099</v>
       </c>
@@ -24798,7 +24797,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="559" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>4100</v>
       </c>
@@ -24839,7 +24838,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="560" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>4101</v>
       </c>
@@ -24886,7 +24885,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="561" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>4102</v>
       </c>
@@ -24927,7 +24926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="562" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>4103</v>
       </c>
@@ -25252,11 +25251,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:AE583" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Virtual-precondition"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AE583">
       <sortCondition ref="A2:A583"/>
     </sortState>

--- a/doc/equip/Equip.xlsx
+++ b/doc/equip/Equip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuoMuoRuoProject\doc\equip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202039A5-AF35-49EC-99A9-D998585A7445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6477CFE3-F7DD-432F-924D-014D71BC92EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/doc/equip/Equip.xlsx
+++ b/doc/equip/Equip.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/doc/equip/Equip.xlsx
+++ b/doc/equip/Equip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuoMuoRuoProject\doc\equip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00AD1B06-5884-4BD3-9348-C724015D5E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81491F31-AC43-4384-9B9E-D16E7DC73612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Equip" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Equip!$A$2:$AF$585</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Equip!$A$2:$AG$585</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="760">
   <si>
     <t>id</t>
   </si>
@@ -2302,6 +2302,14 @@
   </si>
   <si>
     <t>JP-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Storeprice</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>attr</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2552,7 +2560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF585"/>
+  <dimension ref="A1:AG585"/>
   <sheetFormatPr defaultColWidth="10.06640625" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.265625" customWidth="1"/>
@@ -2584,7 +2592,7 @@
     <col min="31" max="31" width="14.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2678,8 +2686,11 @@
       <c r="AF1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG1" s="1" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2776,8 +2787,11 @@
       <c r="AF2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG2" s="1" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2818,7 +2832,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2859,7 +2873,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2903,7 +2917,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2947,7 +2961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2988,7 +3002,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3029,7 +3043,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3070,7 +3084,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3111,7 +3125,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3149,7 +3163,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3193,7 +3207,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3234,7 +3248,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -3275,7 +3289,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3301,7 +3315,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3878,7 +3892,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>31</v>
       </c>
@@ -3910,7 +3924,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>32</v>
       </c>
@@ -3942,7 +3956,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>33</v>
       </c>
@@ -3974,7 +3988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>34</v>
       </c>
@@ -4006,7 +4020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>35</v>
       </c>
@@ -4038,7 +4052,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>36</v>
       </c>
@@ -4073,7 +4087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>37</v>
       </c>
@@ -4105,7 +4119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>38</v>
       </c>
@@ -4134,7 +4148,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>39</v>
       </c>
@@ -4163,7 +4177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>40</v>
       </c>
@@ -4192,7 +4206,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>41</v>
       </c>
@@ -4221,7 +4235,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>42</v>
       </c>
@@ -4243,8 +4257,11 @@
       <c r="I44">
         <v>-1</v>
       </c>
-    </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AG44">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>43</v>
       </c>
@@ -4266,8 +4283,11 @@
       <c r="I45">
         <v>-1</v>
       </c>
-    </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AG45">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>44</v>
       </c>
@@ -4296,7 +4316,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>45</v>
       </c>
@@ -4322,7 +4342,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>46</v>
       </c>
@@ -25478,7 +25498,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AF585" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:AG585" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/doc/equip/Equip.xlsx
+++ b/doc/equip/Equip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuoMuoRuoProject\doc\equip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64ACC552-A50A-4171-83B0-8B7207D5EDC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F619E1-6A28-454B-8C94-A5032096E1B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Equip!$A$2:$AH$585</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -2660,6 +2660,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2886,6 +2887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AH585"/>
   <sheetFormatPr defaultColWidth="10.06640625" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3120,7 +3122,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3164,7 +3166,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3208,7 +3210,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3255,7 +3257,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3302,7 +3304,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:34" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -3346,7 +3348,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3390,7 +3392,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3431,7 +3433,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3475,7 +3477,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3648,7 +3650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3677,7 +3679,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3706,7 +3708,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -3738,7 +3740,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3779,7 +3781,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3817,7 +3819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
@@ -3858,7 +3860,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
@@ -3896,7 +3898,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
@@ -3928,7 +3930,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
@@ -3960,7 +3962,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
@@ -3992,7 +3994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
@@ -4030,7 +4032,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
@@ -4065,7 +4067,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -4112,7 +4114,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -4159,7 +4161,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
@@ -4194,7 +4196,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
@@ -4226,7 +4228,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
@@ -4255,7 +4257,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
@@ -4290,7 +4292,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>31</v>
       </c>
@@ -4322,7 +4324,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>32</v>
       </c>
@@ -4354,7 +4356,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>33</v>
       </c>
@@ -4386,7 +4388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>34</v>
       </c>
@@ -4418,7 +4420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>35</v>
       </c>
@@ -4450,7 +4452,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>36</v>
       </c>
@@ -4485,7 +4487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>37</v>
       </c>
@@ -4517,7 +4519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>38</v>
       </c>
@@ -4546,7 +4548,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>39</v>
       </c>
@@ -4575,7 +4577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>40</v>
       </c>
@@ -4604,7 +4606,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>41</v>
       </c>
@@ -4633,7 +4635,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>42</v>
       </c>
@@ -4659,7 +4661,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>43</v>
       </c>
@@ -4685,7 +4687,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>44</v>
       </c>
@@ -4714,7 +4716,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>45</v>
       </c>
@@ -4740,7 +4742,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>46</v>
       </c>
@@ -4775,7 +4777,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>47</v>
       </c>
@@ -4807,7 +4809,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>48</v>
       </c>
@@ -4851,7 +4853,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>49</v>
       </c>
@@ -4880,7 +4882,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>50</v>
       </c>
@@ -4924,7 +4926,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>51</v>
       </c>
@@ -4953,7 +4955,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>52</v>
       </c>
@@ -4994,7 +4996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>53</v>
       </c>
@@ -5023,7 +5025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>54</v>
       </c>
@@ -5061,7 +5063,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>55</v>
       </c>
@@ -5096,7 +5098,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>56</v>
       </c>
@@ -5125,7 +5127,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>57</v>
       </c>
@@ -5163,7 +5165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>58</v>
       </c>
@@ -5195,7 +5197,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>59</v>
       </c>
@@ -5239,7 +5241,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>60</v>
       </c>
@@ -5277,7 +5279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>61</v>
       </c>
@@ -5318,7 +5320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>62</v>
       </c>
@@ -5365,7 +5367,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>63</v>
       </c>
@@ -5415,7 +5417,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>64</v>
       </c>
@@ -5459,7 +5461,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>65</v>
       </c>
@@ -5544,7 +5546,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5576,7 +5578,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5614,7 +5616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5699,7 +5701,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5731,7 +5733,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5763,7 +5765,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5789,7 +5791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5815,7 +5817,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5912,7 +5914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5956,7 +5958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6003,7 +6005,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6047,7 +6049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6094,7 +6096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6135,7 +6137,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -6176,7 +6178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -6211,7 +6213,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -6243,7 +6245,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -6269,7 +6271,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -6298,7 +6300,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -6330,7 +6332,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -6365,7 +6367,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="91" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -6409,7 +6411,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -6459,7 +6461,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -6488,7 +6490,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -6538,7 +6540,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -6588,7 +6590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -6623,7 +6625,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="97" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -6667,7 +6669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -6717,7 +6719,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -6761,7 +6763,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -6808,7 +6810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -6858,7 +6860,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -6881,7 +6883,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="103" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -6919,7 +6921,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -6960,7 +6962,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -7007,7 +7009,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -7048,7 +7050,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -7083,7 +7085,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -7118,7 +7120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -7159,7 +7161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -7200,7 +7202,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -7238,7 +7240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -7282,7 +7284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -7326,7 +7328,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -7370,7 +7372,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -7414,7 +7416,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -7461,7 +7463,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -7493,7 +7495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -7537,7 +7539,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="119" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -7575,7 +7577,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -7619,7 +7621,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -7651,7 +7653,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -7680,7 +7682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -7730,7 +7732,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="124" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -7777,7 +7779,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -7818,7 +7820,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="126" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -7856,7 +7858,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="127" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -7891,7 +7893,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -7926,7 +7928,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="129" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -7970,7 +7972,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="130" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -8058,7 +8060,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="132" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -8087,7 +8089,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -8122,7 +8124,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="134" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -8263,7 +8265,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="137" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>136</v>
       </c>
@@ -8298,7 +8300,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="138" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -8345,7 +8347,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="139" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -8386,7 +8388,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="140" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -8427,7 +8429,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -8456,7 +8458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -8485,7 +8487,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="143" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -8526,7 +8528,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="144" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -8576,7 +8578,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -8626,7 +8628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -8652,7 +8654,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="147" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -8678,7 +8680,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="148" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>147</v>
       </c>
@@ -8722,7 +8724,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -8766,7 +8768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -8801,7 +8803,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="151" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -8827,7 +8829,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="152" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -8865,7 +8867,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -8909,7 +8911,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="154" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>153</v>
       </c>
@@ -8953,7 +8955,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -9003,7 +9005,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="156" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -9047,7 +9049,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="157" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -9091,7 +9093,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -9135,7 +9137,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -9176,7 +9178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>159</v>
       </c>
@@ -9258,7 +9260,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="162" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>161</v>
       </c>
@@ -9305,7 +9307,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="163" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>162</v>
       </c>
@@ -9352,7 +9354,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="164" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>163</v>
       </c>
@@ -9402,7 +9404,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>164</v>
       </c>
@@ -9440,7 +9442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>165</v>
       </c>
@@ -9478,7 +9480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>166</v>
       </c>
@@ -9507,7 +9509,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>167</v>
       </c>
@@ -9539,7 +9541,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="169" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>168</v>
       </c>
@@ -9586,7 +9588,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="170" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>169</v>
       </c>
@@ -9630,7 +9632,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="171" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>170</v>
       </c>
@@ -9680,7 +9682,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="172" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>171</v>
       </c>
@@ -9777,7 +9779,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="174" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>173</v>
       </c>
@@ -9821,7 +9823,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="175" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>174</v>
       </c>
@@ -9853,7 +9855,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="176" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>175</v>
       </c>
@@ -9891,7 +9893,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>176</v>
       </c>
@@ -9929,7 +9931,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="178" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>177</v>
       </c>
@@ -9970,7 +9972,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>178</v>
       </c>
@@ -10011,7 +10013,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>179</v>
       </c>
@@ -10040,7 +10042,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="181" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>180</v>
       </c>
@@ -10084,7 +10086,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>181</v>
       </c>
@@ -10119,7 +10121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>182</v>
       </c>
@@ -10163,7 +10165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>183</v>
       </c>
@@ -10219,7 +10221,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="185" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>184</v>
       </c>
@@ -10260,7 +10262,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>185</v>
       </c>
@@ -10298,7 +10300,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>186</v>
       </c>
@@ -10345,7 +10347,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="188" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>187</v>
       </c>
@@ -10395,7 +10397,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>188</v>
       </c>
@@ -10436,7 +10438,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="190" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>189</v>
       </c>
@@ -10474,7 +10476,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="191" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>190</v>
       </c>
@@ -10521,7 +10523,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="192" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>191</v>
       </c>
@@ -10556,7 +10558,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>192</v>
       </c>
@@ -10600,7 +10602,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="194" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>193</v>
       </c>
@@ -10629,7 +10631,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="195" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -10682,7 +10684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>195</v>
       </c>
@@ -10735,7 +10737,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>196</v>
       </c>
@@ -10779,7 +10781,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>197</v>
       </c>
@@ -10820,7 +10822,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>198</v>
       </c>
@@ -10864,7 +10866,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>199</v>
       </c>
@@ -10908,7 +10910,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>200</v>
       </c>
@@ -10949,7 +10951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>201</v>
       </c>
@@ -10993,7 +10995,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="203" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>202</v>
       </c>
@@ -11034,7 +11036,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>203</v>
       </c>
@@ -11066,7 +11068,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="205" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>204</v>
       </c>
@@ -11098,7 +11100,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="206" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>205</v>
       </c>
@@ -11142,7 +11144,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>206</v>
       </c>
@@ -11186,7 +11188,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>207</v>
       </c>
@@ -11233,7 +11235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>208</v>
       </c>
@@ -11280,7 +11282,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>209</v>
       </c>
@@ -11309,7 +11311,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="211" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>210</v>
       </c>
@@ -11350,7 +11352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>211</v>
       </c>
@@ -11388,7 +11390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>212</v>
       </c>
@@ -11426,7 +11428,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="214" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>213</v>
       </c>
@@ -11458,7 +11460,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="215" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>214</v>
       </c>
@@ -11493,7 +11495,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="216" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>215</v>
       </c>
@@ -11531,7 +11533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>216</v>
       </c>
@@ -11572,7 +11574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>217</v>
       </c>
@@ -11607,7 +11609,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="219" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>218</v>
       </c>
@@ -11645,7 +11647,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>219</v>
       </c>
@@ -11733,7 +11735,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="222" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>221</v>
       </c>
@@ -11771,7 +11773,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="223" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>222</v>
       </c>
@@ -11812,7 +11814,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="224" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>223</v>
       </c>
@@ -11859,7 +11861,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>224</v>
       </c>
@@ -11906,7 +11908,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="226" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>225</v>
       </c>
@@ -11953,7 +11955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="227" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>226</v>
       </c>
@@ -11982,7 +11984,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="228" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>227</v>
       </c>
@@ -12008,7 +12010,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="229" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>228</v>
       </c>
@@ -12046,7 +12048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>229</v>
       </c>
@@ -12093,7 +12095,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>230</v>
       </c>
@@ -12119,7 +12121,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="232" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>231</v>
       </c>
@@ -12169,7 +12171,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="233" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>232</v>
       </c>
@@ -12219,7 +12221,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="234" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>233</v>
       </c>
@@ -12316,7 +12318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>235</v>
       </c>
@@ -12366,7 +12368,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="237" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>236</v>
       </c>
@@ -12413,7 +12415,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="238" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>237</v>
       </c>
@@ -12463,7 +12465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>238</v>
       </c>
@@ -12507,7 +12509,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="240" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>239</v>
       </c>
@@ -12554,7 +12556,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="241" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>240</v>
       </c>
@@ -12589,7 +12591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>241</v>
       </c>
@@ -12615,7 +12617,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="243" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>242</v>
       </c>
@@ -12659,7 +12661,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>243</v>
       </c>
@@ -12703,7 +12705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>244</v>
       </c>
@@ -12750,7 +12752,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>245</v>
       </c>
@@ -12797,7 +12799,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="247" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>246</v>
       </c>
@@ -12888,7 +12890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>248</v>
       </c>
@@ -12932,7 +12934,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>249</v>
       </c>
@@ -12982,7 +12984,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="251" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>250</v>
       </c>
@@ -13026,7 +13028,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>251</v>
       </c>
@@ -13067,7 +13069,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>252</v>
       </c>
@@ -13114,7 +13116,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>253</v>
       </c>
@@ -13158,7 +13160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>254</v>
       </c>
@@ -13205,7 +13207,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>255</v>
       </c>
@@ -13252,7 +13254,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>256</v>
       </c>
@@ -13296,7 +13298,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="258" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>257</v>
       </c>
@@ -13346,7 +13348,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="259" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>258</v>
       </c>
@@ -13384,7 +13386,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="260" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>259</v>
       </c>
@@ -13425,7 +13427,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="261" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>260</v>
       </c>
@@ -13463,7 +13465,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="262" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>261</v>
       </c>
@@ -13498,7 +13500,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="263" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>262</v>
       </c>
@@ -13533,7 +13535,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="264" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>263</v>
       </c>
@@ -13577,7 +13579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>264</v>
       </c>
@@ -13621,7 +13623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>265</v>
       </c>
@@ -13665,7 +13667,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>266</v>
       </c>
@@ -13712,7 +13714,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="268" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>267</v>
       </c>
@@ -13759,7 +13761,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="269" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>268</v>
       </c>
@@ -13791,7 +13793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>269</v>
       </c>
@@ -13826,7 +13828,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="271" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>270</v>
       </c>
@@ -13867,7 +13869,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="272" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>271</v>
       </c>
@@ -13905,7 +13907,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="273" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>272</v>
       </c>
@@ -13940,7 +13942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>273</v>
       </c>
@@ -13975,7 +13977,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="275" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>274</v>
       </c>
@@ -14060,7 +14062,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="277" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>276</v>
       </c>
@@ -14104,7 +14106,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="278" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>277</v>
       </c>
@@ -14154,7 +14156,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="279" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>278</v>
       </c>
@@ -14192,7 +14194,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="280" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>279</v>
       </c>
@@ -14236,7 +14238,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="281" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>280</v>
       </c>
@@ -14286,7 +14288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>281</v>
       </c>
@@ -14333,7 +14335,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="283" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>282</v>
       </c>
@@ -14377,7 +14379,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="284" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>283</v>
       </c>
@@ -14412,7 +14414,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="285" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>284</v>
       </c>
@@ -14459,7 +14461,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="286" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>285</v>
       </c>
@@ -14494,7 +14496,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="287" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>286</v>
       </c>
@@ -14529,7 +14531,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="288" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>287</v>
       </c>
@@ -14555,7 +14557,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="289" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>288</v>
       </c>
@@ -14587,7 +14589,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="290" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>289</v>
       </c>
@@ -14634,7 +14636,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="291" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>290</v>
       </c>
@@ -14678,7 +14680,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="292" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>291</v>
       </c>
@@ -14722,7 +14724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>292</v>
       </c>
@@ -14772,7 +14774,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="294" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>293</v>
       </c>
@@ -14816,7 +14818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="295" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>294</v>
       </c>
@@ -14863,7 +14865,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="296" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>295</v>
       </c>
@@ -14913,7 +14915,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="297" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>296</v>
       </c>
@@ -14963,7 +14965,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="298" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>297</v>
       </c>
@@ -15007,7 +15009,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="299" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>298</v>
       </c>
@@ -15048,7 +15050,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="300" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>299</v>
       </c>
@@ -15092,7 +15094,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="301" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>300</v>
       </c>
@@ -15142,7 +15144,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="302" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>301</v>
       </c>
@@ -15171,7 +15173,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="303" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>302</v>
       </c>
@@ -15215,7 +15217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>303</v>
       </c>
@@ -15262,7 +15264,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="305" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>304</v>
       </c>
@@ -15303,7 +15305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="306" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>305</v>
       </c>
@@ -15347,7 +15349,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>306</v>
       </c>
@@ -15397,7 +15399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="308" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>307</v>
       </c>
@@ -15444,7 +15446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="309" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>308</v>
       </c>
@@ -15494,7 +15496,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="310" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>309</v>
       </c>
@@ -15526,7 +15528,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="311" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>310</v>
       </c>
@@ -15573,7 +15575,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="312" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>311</v>
       </c>
@@ -15611,7 +15613,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="313" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>312</v>
       </c>
@@ -15652,7 +15654,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="314" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>313</v>
       </c>
@@ -15696,7 +15698,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="315" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>314</v>
       </c>
@@ -15737,7 +15739,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="316" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>315</v>
       </c>
@@ -15784,7 +15786,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>316</v>
       </c>
@@ -15828,7 +15830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>317</v>
       </c>
@@ -15863,7 +15865,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="319" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>318</v>
       </c>
@@ -15910,7 +15912,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="320" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>319</v>
       </c>
@@ -15957,7 +15959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="321" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>320</v>
       </c>
@@ -15998,7 +16000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="322" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>322</v>
       </c>
@@ -16048,7 +16050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="323" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>323</v>
       </c>
@@ -16098,7 +16100,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="324" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>324</v>
       </c>
@@ -16133,7 +16135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>325</v>
       </c>
@@ -16171,7 +16173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>326</v>
       </c>
@@ -16212,7 +16214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>327</v>
       </c>
@@ -16250,7 +16252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="328" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>328</v>
       </c>
@@ -16297,7 +16299,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="329" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>329</v>
       </c>
@@ -16344,7 +16346,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="330" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>330</v>
       </c>
@@ -16388,7 +16390,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="331" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>331</v>
       </c>
@@ -16435,7 +16437,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="332" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>332</v>
       </c>
@@ -16482,7 +16484,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="333" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>333</v>
       </c>
@@ -16520,7 +16522,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>334</v>
       </c>
@@ -16561,7 +16563,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>336</v>
       </c>
@@ -16599,7 +16601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="336" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>338</v>
       </c>
@@ -16646,7 +16648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="337" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>339</v>
       </c>
@@ -16693,7 +16695,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="338" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>340</v>
       </c>
@@ -16740,7 +16742,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="339" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>341</v>
       </c>
@@ -16787,7 +16789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="340" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>342</v>
       </c>
@@ -16834,7 +16836,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="341" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>343</v>
       </c>
@@ -16884,7 +16886,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="342" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>344</v>
       </c>
@@ -16928,7 +16930,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>345</v>
       </c>
@@ -16972,7 +16974,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>346</v>
       </c>
@@ -17004,7 +17006,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="345" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>347</v>
       </c>
@@ -17036,7 +17038,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="346" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>348</v>
       </c>
@@ -17068,7 +17070,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="347" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>349</v>
       </c>
@@ -17100,7 +17102,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="348" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>350</v>
       </c>
@@ -17138,7 +17140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>351</v>
       </c>
@@ -17173,7 +17175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>352</v>
       </c>
@@ -17208,7 +17210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>353</v>
       </c>
@@ -17252,7 +17254,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="352" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>354</v>
       </c>
@@ -17296,7 +17298,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="353" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>355</v>
       </c>
@@ -17334,7 +17336,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="354" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>356</v>
       </c>
@@ -17381,7 +17383,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="355" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>357</v>
       </c>
@@ -17478,7 +17480,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="357" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>359</v>
       </c>
@@ -17531,7 +17533,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="358" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>360</v>
       </c>
@@ -17581,7 +17583,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="359" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>361</v>
       </c>
@@ -17631,7 +17633,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="360" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>362</v>
       </c>
@@ -17681,7 +17683,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="361" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>363</v>
       </c>
@@ -17734,7 +17736,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="362" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>364</v>
       </c>
@@ -17766,7 +17768,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="363" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>365</v>
       </c>
@@ -17798,7 +17800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="364" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>366</v>
       </c>
@@ -17848,7 +17850,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="365" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>367</v>
       </c>
@@ -17898,7 +17900,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="366" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>368</v>
       </c>
@@ -17945,7 +17947,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="367" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>369</v>
       </c>
@@ -17995,7 +17997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="368" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>370</v>
       </c>
@@ -18036,7 +18038,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="369" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>371</v>
       </c>
@@ -18083,7 +18085,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="370" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>372</v>
       </c>
@@ -18124,7 +18126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="371" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>373</v>
       </c>
@@ -18171,7 +18173,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="372" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>374</v>
       </c>
@@ -18221,7 +18223,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>375</v>
       </c>
@@ -18259,7 +18261,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="374" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>376</v>
       </c>
@@ -18297,7 +18299,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="375" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>377</v>
       </c>
@@ -18338,7 +18340,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="376" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>378</v>
       </c>
@@ -18367,7 +18369,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="377" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>379</v>
       </c>
@@ -18414,7 +18416,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="378" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>380</v>
       </c>
@@ -18464,7 +18466,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="379" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>381</v>
       </c>
@@ -18511,7 +18513,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="380" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>382</v>
       </c>
@@ -18564,7 +18566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>383</v>
       </c>
@@ -18596,7 +18598,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="382" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>384</v>
       </c>
@@ -18637,7 +18639,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="383" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>385</v>
       </c>
@@ -18684,7 +18686,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="384" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>386</v>
       </c>
@@ -18734,7 +18736,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="385" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>387</v>
       </c>
@@ -18784,7 +18786,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="386" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>388</v>
       </c>
@@ -18834,7 +18836,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="387" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>389</v>
       </c>
@@ -18887,7 +18889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>390</v>
       </c>
@@ -18943,7 +18945,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="389" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>391</v>
       </c>
@@ -18987,7 +18989,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="390" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>392</v>
       </c>
@@ -19040,7 +19042,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="391" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>393</v>
       </c>
@@ -19084,7 +19086,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="392" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>394</v>
       </c>
@@ -19128,7 +19130,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="393" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>395</v>
       </c>
@@ -19169,7 +19171,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="394" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>396</v>
       </c>
@@ -19207,7 +19209,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="395" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>397</v>
       </c>
@@ -19251,7 +19253,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="396" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>398</v>
       </c>
@@ -19295,7 +19297,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="397" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>399</v>
       </c>
@@ -19345,7 +19347,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="398" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>400</v>
       </c>
@@ -19380,7 +19382,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="399" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>401</v>
       </c>
@@ -19424,7 +19426,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="400" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>402</v>
       </c>
@@ -19450,7 +19452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="401" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>403</v>
       </c>
@@ -19500,7 +19502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="402" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>404</v>
       </c>
@@ -19550,7 +19552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>405</v>
       </c>
@@ -19594,7 +19596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="404" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>406</v>
       </c>
@@ -19638,7 +19640,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="405" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>407</v>
       </c>
@@ -19685,7 +19687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="406" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>408</v>
       </c>
@@ -19726,7 +19728,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="407" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>409</v>
       </c>
@@ -19764,7 +19766,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="408" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>410</v>
       </c>
@@ -19799,7 +19801,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="409" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>411</v>
       </c>
@@ -19834,7 +19836,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="410" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>412</v>
       </c>
@@ -19878,7 +19880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>413</v>
       </c>
@@ -19910,7 +19912,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="412" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>414</v>
       </c>
@@ -19954,7 +19956,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="413" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>415</v>
       </c>
@@ -19995,7 +19997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="414" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>416</v>
       </c>
@@ -20039,7 +20041,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="415" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>417</v>
       </c>
@@ -20083,7 +20085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>418</v>
       </c>
@@ -20127,7 +20129,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="417" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>419</v>
       </c>
@@ -20177,7 +20179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="418" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>420</v>
       </c>
@@ -20230,7 +20232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="419" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>421</v>
       </c>
@@ -20283,7 +20285,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="420" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>422</v>
       </c>
@@ -20327,7 +20329,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="421" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>423</v>
       </c>
@@ -20374,7 +20376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="422" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>424</v>
       </c>
@@ -20418,7 +20420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="423" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>425</v>
       </c>
@@ -20459,7 +20461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="424" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>426</v>
       </c>
@@ -20509,7 +20511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="425" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>427</v>
       </c>
@@ -20556,7 +20558,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="426" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>428</v>
       </c>
@@ -20603,7 +20605,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="427" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>429</v>
       </c>
@@ -20697,7 +20699,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="429" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>431</v>
       </c>
@@ -20744,7 +20746,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="430" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>432</v>
       </c>
@@ -20788,7 +20790,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="431" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>433</v>
       </c>
@@ -20838,7 +20840,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="432" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>434</v>
       </c>
@@ -20879,7 +20881,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="433" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>435</v>
       </c>
@@ -20926,7 +20928,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="434" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>436</v>
       </c>
@@ -20961,7 +20963,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="435" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>437</v>
       </c>
@@ -20996,7 +20998,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="436" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>438</v>
       </c>
@@ -21034,7 +21036,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="437" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>439</v>
       </c>
@@ -21072,7 +21074,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="438" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>440</v>
       </c>
@@ -21104,7 +21106,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="439" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>441</v>
       </c>
@@ -21136,7 +21138,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="440" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>442</v>
       </c>
@@ -21171,7 +21173,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="441" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>443</v>
       </c>
@@ -21203,7 +21205,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="442" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>444</v>
       </c>
@@ -21253,7 +21255,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>445</v>
       </c>
@@ -21297,7 +21299,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="444" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>446</v>
       </c>
@@ -21338,7 +21340,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="445" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>447</v>
       </c>
@@ -21382,7 +21384,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="446" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>449</v>
       </c>
@@ -21411,7 +21413,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="447" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>450</v>
       </c>
@@ -21446,7 +21448,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="448" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>451</v>
       </c>
@@ -21487,7 +21489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="449" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>452</v>
       </c>
@@ -21528,7 +21530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="450" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>453</v>
       </c>
@@ -21578,7 +21580,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="451" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>454</v>
       </c>
@@ -21631,7 +21633,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="452" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>455</v>
       </c>
@@ -21672,7 +21674,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>456</v>
       </c>
@@ -21719,7 +21721,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="454" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>457</v>
       </c>
@@ -21754,7 +21756,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="455" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>458</v>
       </c>
@@ -21795,7 +21797,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="456" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>459</v>
       </c>
@@ -21842,7 +21844,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="457" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>460</v>
       </c>
@@ -21886,7 +21888,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="458" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>461</v>
       </c>
@@ -22021,7 +22023,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="461" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>465</v>
       </c>
@@ -22068,7 +22070,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="462" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>466</v>
       </c>
@@ -22165,7 +22167,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="464" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>468</v>
       </c>
@@ -22212,7 +22214,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="465" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>469</v>
       </c>
@@ -22256,7 +22258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="466" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>470</v>
       </c>
@@ -22306,7 +22308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="467" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>471</v>
       </c>
@@ -22347,7 +22349,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="468" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>472</v>
       </c>
@@ -22382,7 +22384,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="469" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>473</v>
       </c>
@@ -22429,7 +22431,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="470" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>474</v>
       </c>
@@ -22479,7 +22481,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="471" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>475</v>
       </c>
@@ -22529,7 +22531,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="472" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>476</v>
       </c>
@@ -22579,7 +22581,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="473" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>477</v>
       </c>
@@ -22626,7 +22628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="474" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>478</v>
       </c>
@@ -22682,7 +22684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="475" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>479</v>
       </c>
@@ -22732,7 +22734,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="476" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>480</v>
       </c>
@@ -22770,7 +22772,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="477" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>481</v>
       </c>
@@ -22817,7 +22819,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="478" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>482</v>
       </c>
@@ -22852,7 +22854,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="479" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>483</v>
       </c>
@@ -22890,7 +22892,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="480" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>484</v>
       </c>
@@ -22940,7 +22942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="481" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>485</v>
       </c>
@@ -22975,7 +22977,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="482" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>486</v>
       </c>
@@ -23019,7 +23021,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="483" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>487</v>
       </c>
@@ -23069,7 +23071,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="484" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>488</v>
       </c>
@@ -23104,7 +23106,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="485" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>489</v>
       </c>
@@ -23148,7 +23150,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="486" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>490</v>
       </c>
@@ -23195,7 +23197,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="487" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>491</v>
       </c>
@@ -23245,7 +23247,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="488" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>492</v>
       </c>
@@ -23289,7 +23291,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="489" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>493</v>
       </c>
@@ -23339,7 +23341,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="490" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>494</v>
       </c>
@@ -23368,7 +23370,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="491" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>495</v>
       </c>
@@ -23400,7 +23402,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="492" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>496</v>
       </c>
@@ -23426,7 +23428,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="493" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>497</v>
       </c>
@@ -23458,7 +23460,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="494" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>498</v>
       </c>
@@ -23487,7 +23489,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="495" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>499</v>
       </c>
@@ -23516,7 +23518,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="496" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>500</v>
       </c>
@@ -23545,7 +23547,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="497" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>501</v>
       </c>
@@ -23574,7 +23576,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="498" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>502</v>
       </c>
@@ -23624,7 +23626,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="499" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>503</v>
       </c>
@@ -23671,7 +23673,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="500" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>504</v>
       </c>
@@ -23721,7 +23723,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="501" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>505</v>
       </c>
@@ -23750,7 +23752,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="502" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>506</v>
       </c>
@@ -23791,7 +23793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="503" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>507</v>
       </c>
@@ -23841,7 +23843,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="504" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>508</v>
       </c>
@@ -23885,7 +23887,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="505" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>509</v>
       </c>
@@ -23938,7 +23940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="506" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>510</v>
       </c>
@@ -23979,7 +23981,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="507" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>511</v>
       </c>
@@ -24011,7 +24013,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="508" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>512</v>
       </c>
@@ -24043,7 +24045,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="509" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>513</v>
       </c>
@@ -24069,7 +24071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>514</v>
       </c>
@@ -24104,7 +24106,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="511" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>515</v>
       </c>
@@ -24142,7 +24144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="512" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>516</v>
       </c>
@@ -24186,7 +24188,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="513" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>517</v>
       </c>
@@ -24224,7 +24226,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="514" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>518</v>
       </c>
@@ -24271,7 +24273,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="515" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>519</v>
       </c>
@@ -24309,7 +24311,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="516" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516">
         <v>520</v>
       </c>
@@ -24356,7 +24358,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="517" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>521</v>
       </c>
@@ -24400,7 +24402,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="518" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>522</v>
       </c>
@@ -24447,7 +24449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="519" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>523</v>
       </c>
@@ -24544,7 +24546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>525</v>
       </c>
@@ -24582,7 +24584,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="522" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>526</v>
       </c>
@@ -24623,7 +24625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="523" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>527</v>
       </c>
@@ -24664,7 +24666,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="524" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>528</v>
       </c>
@@ -24711,7 +24713,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="525" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>529</v>
       </c>
@@ -24761,7 +24763,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="526" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>530</v>
       </c>
@@ -24808,7 +24810,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="527" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>531</v>
       </c>
@@ -24837,7 +24839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>532</v>
       </c>
@@ -24863,7 +24865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>533</v>
       </c>
@@ -24913,7 +24915,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="530" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>534</v>
       </c>
@@ -24960,7 +24962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="531" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>535</v>
       </c>
@@ -25004,7 +25006,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="532" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>536</v>
       </c>
@@ -25051,7 +25053,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="533" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>537</v>
       </c>
@@ -25095,7 +25097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="534" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>538</v>
       </c>
@@ -25142,7 +25144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="535" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>539</v>
       </c>
@@ -25189,7 +25191,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="536" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>540</v>
       </c>
@@ -25233,7 +25235,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="537" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>541</v>
       </c>
@@ -25283,7 +25285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="538" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>542</v>
       </c>
@@ -25324,7 +25326,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="539" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>543</v>
       </c>
@@ -25374,7 +25376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="540" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>544</v>
       </c>
@@ -25427,7 +25429,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="541" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>545</v>
       </c>
@@ -25477,7 +25479,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="542" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542">
         <v>546</v>
       </c>
@@ -25512,7 +25514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="543" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>549</v>
       </c>
@@ -25556,7 +25558,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="544" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544">
         <v>550</v>
       </c>
@@ -25594,7 +25596,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="545" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545">
         <v>551</v>
       </c>
@@ -25632,7 +25634,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="546" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546">
         <v>552</v>
       </c>
@@ -25679,7 +25681,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="547" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547">
         <v>553</v>
       </c>
@@ -25729,7 +25731,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="548" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548">
         <v>554</v>
       </c>
@@ -25767,7 +25769,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="549" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549">
         <v>555</v>
       </c>
@@ -25864,7 +25866,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="551" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>557</v>
       </c>
@@ -25911,7 +25913,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="552" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>558</v>
       </c>
@@ -25958,7 +25960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="553" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553">
         <v>559</v>
       </c>
@@ -26008,7 +26010,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="554" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>560</v>
       </c>
@@ -26049,7 +26051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="555" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>561</v>
       </c>
@@ -26099,7 +26101,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="556" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>4097</v>
       </c>
@@ -26134,7 +26136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="557" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557">
         <v>4098</v>
       </c>
@@ -26160,7 +26162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="558" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>4099</v>
       </c>
@@ -26201,7 +26203,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="559" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>4100</v>
       </c>
@@ -26242,7 +26244,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="560" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>4101</v>
       </c>
@@ -26339,7 +26341,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="562" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>4103</v>
       </c>
@@ -26368,7 +26370,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="563" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563">
         <v>16384</v>
       </c>
@@ -26382,7 +26384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564">
         <v>16385</v>
       </c>
@@ -26399,7 +26401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="565" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565">
         <v>16386</v>
       </c>
@@ -26417,7 +26419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="566" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566">
         <v>16389</v>
       </c>
@@ -26434,7 +26436,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="567" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567">
         <v>16390</v>
       </c>
@@ -26451,7 +26453,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="568" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>16391</v>
       </c>
@@ -26468,7 +26470,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="569" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>16392</v>
       </c>
@@ -26485,7 +26487,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="570" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>16393</v>
       </c>
@@ -26502,7 +26504,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="571" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571">
         <v>16394</v>
       </c>
@@ -26519,7 +26521,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="572" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572">
         <v>16396</v>
       </c>
@@ -26536,7 +26538,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="573" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>16401</v>
       </c>
@@ -26550,7 +26552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574">
         <v>16402</v>
       </c>
@@ -26564,7 +26566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575">
         <v>16404</v>
       </c>
@@ -26581,7 +26583,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="576" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>16415</v>
       </c>
@@ -26595,7 +26597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577">
         <v>16427</v>
       </c>
@@ -26609,7 +26611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>16438</v>
       </c>
@@ -26623,7 +26625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>16439</v>
       </c>
@@ -26637,7 +26639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580">
         <v>16440</v>
       </c>
@@ -26651,7 +26653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>16445</v>
       </c>
@@ -26665,7 +26667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>16446</v>
       </c>
@@ -26679,7 +26681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583">
         <v>16461</v>
       </c>
@@ -26693,7 +26695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584">
         <v>16469</v>
       </c>
@@ -26710,7 +26712,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="585" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585">
         <v>16470</v>
       </c>
@@ -26725,7 +26727,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AH585" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:AH585" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="副砲"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/doc/equip/Equip.xlsx
+++ b/doc/equip/Equip.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuoMuoRuoProject\doc\equip\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mj\GuoMuoRuoProject\doc\equip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA28B86-6079-468A-BA09-6DBBD9798F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACE5B53-C22B-4FCE-916F-66C7CE89A676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,18 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Equip!$A$2:$AH$585</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -4047,7 +4058,9 @@
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
+      <c r="P18" s="2">
+        <v>48</v>
+      </c>
       <c r="Q18" s="2"/>
       <c r="R18">
         <v>6</v>
@@ -4105,7 +4118,9 @@
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
+      <c r="P19" s="2">
+        <v>48</v>
+      </c>
       <c r="Q19" s="2"/>
       <c r="R19">
         <v>7</v>
@@ -4163,7 +4178,9 @@
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
+      <c r="P20" s="2">
+        <v>48</v>
+      </c>
       <c r="Q20" s="2"/>
       <c r="R20">
         <v>8</v>
@@ -4623,7 +4640,7 @@
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P28" s="2"/>
       <c r="Q28" s="2"/>
@@ -5242,7 +5259,7 @@
       <c r="X39" s="2"/>
       <c r="Y39" s="2"/>
       <c r="Z39">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="AA39" s="2"/>
       <c r="AB39" s="2"/>
@@ -5294,7 +5311,7 @@
       <c r="X40" s="2"/>
       <c r="Y40" s="2"/>
       <c r="Z40">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="AA40" s="2"/>
       <c r="AB40" s="2"/>
@@ -5346,7 +5363,7 @@
       <c r="X41" s="2"/>
       <c r="Y41" s="2"/>
       <c r="Z41">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="AA41" s="2"/>
       <c r="AB41" s="2"/>
@@ -5398,7 +5415,7 @@
       <c r="X42" s="2"/>
       <c r="Y42" s="2"/>
       <c r="Z42">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="AA42" s="2"/>
       <c r="AB42" s="2"/>
@@ -5439,7 +5456,9 @@
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
-      <c r="P43" s="2"/>
+      <c r="P43" s="2">
+        <v>10</v>
+      </c>
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
       <c r="S43" s="2"/>
@@ -5878,7 +5897,7 @@
       <c r="X51" s="2"/>
       <c r="Y51" s="2"/>
       <c r="Z51">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="AA51" s="2"/>
       <c r="AB51" s="2"/>
@@ -5992,7 +6011,7 @@
       <c r="X53" s="2"/>
       <c r="Y53" s="2"/>
       <c r="Z53">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="AA53" s="2"/>
       <c r="AB53" s="2"/>
@@ -6033,7 +6052,9 @@
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
-      <c r="P54" s="2"/>
+      <c r="P54" s="2">
+        <v>48</v>
+      </c>
       <c r="Q54" s="2"/>
       <c r="R54">
         <v>10</v>
@@ -6092,7 +6113,9 @@
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" s="2"/>
-      <c r="Q55" s="2"/>
+      <c r="Q55" s="2">
+        <v>7</v>
+      </c>
       <c r="R55" s="2"/>
       <c r="S55" s="2"/>
       <c r="T55" s="2"/>
@@ -6147,7 +6170,7 @@
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
       <c r="O56">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="P56" s="2"/>
       <c r="Q56" s="2"/>
@@ -6545,7 +6568,7 @@
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="O63">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" s="2"/>
@@ -6605,7 +6628,7 @@
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
       <c r="O64">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P64" s="2"/>
       <c r="Q64">
@@ -6735,7 +6758,7 @@
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
       <c r="O66">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P66" s="2"/>
       <c r="Q66" s="2"/>
@@ -7553,7 +7576,7 @@
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
       <c r="O80">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P80" s="2"/>
       <c r="Q80" s="2"/>
@@ -7615,7 +7638,7 @@
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
       <c r="O81">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P81" s="2"/>
       <c r="Q81" s="2"/>
@@ -7679,7 +7702,7 @@
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
       <c r="O82">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P82" s="2"/>
       <c r="Q82" s="2"/>
@@ -7743,7 +7766,9 @@
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
-      <c r="P83" s="2"/>
+      <c r="P83" s="2">
+        <v>60</v>
+      </c>
       <c r="Q83" s="2"/>
       <c r="R83">
         <v>12</v>
@@ -7803,7 +7828,9 @@
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
-      <c r="P84" s="2"/>
+      <c r="P84" s="2">
+        <v>60</v>
+      </c>
       <c r="Q84" s="2"/>
       <c r="R84">
         <v>12</v>
@@ -7876,7 +7903,7 @@
       <c r="X85" s="2"/>
       <c r="Y85" s="2"/>
       <c r="Z85">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="AA85" s="2"/>
       <c r="AB85" s="2"/>
@@ -7930,7 +7957,7 @@
       <c r="X86" s="2"/>
       <c r="Y86" s="2"/>
       <c r="Z86">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="AA86" s="2"/>
       <c r="AB86" s="2"/>
@@ -8322,7 +8349,7 @@
       <c r="X93" s="2"/>
       <c r="Y93" s="2"/>
       <c r="Z93">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="AA93" s="2"/>
       <c r="AB93" s="2"/>
@@ -8365,9 +8392,11 @@
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
       <c r="O94">
-        <v>30</v>
-      </c>
-      <c r="P94" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="P94" s="2">
+        <v>96</v>
+      </c>
       <c r="Q94">
         <v>10</v>
       </c>
@@ -8431,9 +8460,11 @@
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
       <c r="O95">
-        <v>30</v>
-      </c>
-      <c r="P95" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="P95" s="2">
+        <v>108</v>
+      </c>
       <c r="Q95">
         <v>10</v>
       </c>
@@ -8553,7 +8584,7 @@
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
       <c r="O97">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="P97" s="2"/>
       <c r="Q97">
@@ -8615,7 +8646,7 @@
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
       <c r="O98">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="P98" s="2"/>
       <c r="Q98">
@@ -8681,9 +8712,11 @@
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
       <c r="O99">
-        <v>20</v>
-      </c>
-      <c r="P99" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="P99" s="2">
+        <v>72</v>
+      </c>
       <c r="Q99" s="2"/>
       <c r="R99">
         <v>12</v>
@@ -8743,7 +8776,7 @@
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
       <c r="O100">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="P100" s="2"/>
       <c r="Q100">
@@ -8807,7 +8840,7 @@
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
       <c r="O101">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="P101" s="2"/>
       <c r="Q101">
@@ -9222,7 +9255,7 @@
         <v>1</v>
       </c>
       <c r="R108">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="S108" s="2"/>
       <c r="T108" s="2"/>
@@ -9286,7 +9319,9 @@
       <c r="T109">
         <v>40</v>
       </c>
-      <c r="U109" s="2"/>
+      <c r="U109" s="2">
+        <v>3</v>
+      </c>
       <c r="V109" s="2"/>
       <c r="W109" s="2"/>
       <c r="X109" s="2"/>
@@ -9335,7 +9370,7 @@
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
       <c r="O110">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P110" s="2"/>
       <c r="Q110">
@@ -9393,7 +9428,7 @@
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
       <c r="O111">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P111" s="2"/>
       <c r="Q111">
@@ -9453,7 +9488,7 @@
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
       <c r="O112">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="P112" s="2"/>
       <c r="Q112" s="2"/>
@@ -9515,9 +9550,11 @@
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
       <c r="O113">
-        <v>10</v>
-      </c>
-      <c r="P113" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="P113" s="2">
+        <v>72</v>
+      </c>
       <c r="Q113" s="2"/>
       <c r="R113">
         <v>12</v>
@@ -9577,9 +9614,11 @@
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
       <c r="O114">
-        <v>10</v>
-      </c>
-      <c r="P114" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="P114" s="2">
+        <v>84</v>
+      </c>
       <c r="Q114" s="2"/>
       <c r="R114">
         <v>15</v>
@@ -10662,7 +10701,7 @@
       <c r="X132" s="2"/>
       <c r="Y132" s="2"/>
       <c r="Z132">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="AA132" s="2"/>
       <c r="AB132" s="2"/>
@@ -11073,7 +11112,7 @@
       <c r="M139" s="2"/>
       <c r="N139" s="2"/>
       <c r="O139">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P139" s="2"/>
       <c r="Q139" s="2"/>
@@ -11357,9 +11396,11 @@
       <c r="M144" s="2"/>
       <c r="N144" s="2"/>
       <c r="O144">
-        <v>20</v>
-      </c>
-      <c r="P144" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="P144" s="2">
+        <v>84</v>
+      </c>
       <c r="Q144">
         <v>10</v>
       </c>
@@ -11423,9 +11464,11 @@
       <c r="M145" s="2"/>
       <c r="N145" s="2"/>
       <c r="O145">
-        <v>20</v>
-      </c>
-      <c r="P145" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="P145" s="2">
+        <v>96</v>
+      </c>
       <c r="Q145">
         <v>10</v>
       </c>
@@ -11777,7 +11820,7 @@
       <c r="M152" s="2"/>
       <c r="N152" s="2"/>
       <c r="O152">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="P152" s="2"/>
       <c r="Q152" s="2"/>
@@ -11835,7 +11878,7 @@
       <c r="M153" s="2"/>
       <c r="N153" s="2"/>
       <c r="O153">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="P153" s="2"/>
       <c r="Q153">
@@ -11897,7 +11940,7 @@
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
       <c r="O154">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="P154" s="2"/>
       <c r="Q154">
@@ -11959,7 +12002,7 @@
       <c r="M155" s="2"/>
       <c r="N155" s="2"/>
       <c r="O155">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="P155" s="2"/>
       <c r="Q155">
@@ -12025,7 +12068,7 @@
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
       <c r="O156">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="P156" s="2"/>
       <c r="Q156">
@@ -12087,7 +12130,7 @@
       <c r="M157" s="2"/>
       <c r="N157" s="2"/>
       <c r="O157">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="P157" s="2"/>
       <c r="Q157">
@@ -12149,11 +12192,11 @@
       <c r="M158" s="2"/>
       <c r="N158" s="2"/>
       <c r="O158">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="P158" s="2"/>
       <c r="Q158">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="R158">
         <v>32</v>
@@ -13148,7 +13191,7 @@
       <c r="X174" s="2"/>
       <c r="Y174" s="2"/>
       <c r="Z174">
-        <v>11</v>
+        <v>127</v>
       </c>
       <c r="AA174" s="2"/>
       <c r="AB174" s="2"/>
@@ -13421,7 +13464,7 @@
       <c r="M179" s="2"/>
       <c r="N179" s="2"/>
       <c r="O179">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="P179" s="2"/>
       <c r="Q179" s="2"/>
@@ -13651,7 +13694,7 @@
       <c r="M183" s="2"/>
       <c r="N183" s="2"/>
       <c r="O183">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="P183" s="2"/>
       <c r="Q183">
@@ -14031,7 +14074,9 @@
       <c r="M189" s="2"/>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
-      <c r="P189" s="2"/>
+      <c r="P189" s="2">
+        <v>40</v>
+      </c>
       <c r="Q189">
         <v>2</v>
       </c>
@@ -14226,7 +14271,7 @@
       <c r="X192" s="2"/>
       <c r="Y192" s="2"/>
       <c r="Z192">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="AA192" s="2"/>
       <c r="AB192" s="2"/>
@@ -14453,7 +14498,7 @@
       <c r="M196" s="2"/>
       <c r="N196" s="2"/>
       <c r="O196">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P196" s="2"/>
       <c r="Q196">
@@ -14521,7 +14566,9 @@
       <c r="M197" s="2"/>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
-      <c r="P197" s="2"/>
+      <c r="P197" s="2">
+        <v>45</v>
+      </c>
       <c r="Q197" s="2"/>
       <c r="R197">
         <v>10</v>
@@ -14701,7 +14748,7 @@
       <c r="M200" s="2"/>
       <c r="N200" s="2"/>
       <c r="O200">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P200" s="2"/>
       <c r="Q200" s="2"/>
@@ -15055,7 +15102,7 @@
       <c r="M206" s="2"/>
       <c r="N206" s="2"/>
       <c r="O206">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P206" s="2"/>
       <c r="Q206">
@@ -15117,7 +15164,7 @@
       <c r="M207" s="2"/>
       <c r="N207" s="2"/>
       <c r="O207">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P207" s="2"/>
       <c r="Q207">
@@ -15179,7 +15226,7 @@
       <c r="M208" s="2"/>
       <c r="N208" s="2"/>
       <c r="O208">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P208" s="2"/>
       <c r="Q208" s="2"/>
@@ -15243,7 +15290,7 @@
       <c r="M209" s="2"/>
       <c r="N209" s="2"/>
       <c r="O209">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="P209" s="2"/>
       <c r="Q209">
@@ -15477,7 +15524,7 @@
       <c r="M213" s="2"/>
       <c r="N213" s="2"/>
       <c r="O213">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="P213" s="2"/>
       <c r="Q213" s="2"/>
@@ -16977,7 +17024,7 @@
       <c r="M238" s="2"/>
       <c r="N238" s="2"/>
       <c r="O238">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P238" s="2"/>
       <c r="Q238">
@@ -17254,9 +17301,11 @@
       <c r="M243" s="2"/>
       <c r="N243" s="2"/>
       <c r="O243">
-        <v>10</v>
-      </c>
-      <c r="P243" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="P243" s="2">
+        <v>45</v>
+      </c>
       <c r="Q243" s="2"/>
       <c r="R243">
         <v>6</v>
@@ -17316,9 +17365,11 @@
       <c r="M244" s="2"/>
       <c r="N244" s="2"/>
       <c r="O244">
-        <v>30</v>
-      </c>
-      <c r="P244" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="P244" s="2">
+        <v>60</v>
+      </c>
       <c r="Q244" s="2"/>
       <c r="R244">
         <v>12</v>
@@ -17380,9 +17431,11 @@
       <c r="M245" s="2"/>
       <c r="N245" s="2"/>
       <c r="O245">
-        <v>40</v>
-      </c>
-      <c r="P245" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="P245" s="2">
+        <v>80</v>
+      </c>
       <c r="Q245" s="2"/>
       <c r="R245">
         <v>28</v>
@@ -17696,7 +17749,7 @@
       <c r="M250" s="2"/>
       <c r="N250" s="2"/>
       <c r="O250">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="P250" s="2"/>
       <c r="Q250">
@@ -17886,7 +17939,7 @@
       </c>
       <c r="N253" s="2"/>
       <c r="O253">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P253" s="2"/>
       <c r="Q253">
@@ -18008,7 +18061,7 @@
       <c r="M255" s="2"/>
       <c r="N255" s="2"/>
       <c r="O255">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="P255" s="2"/>
       <c r="Q255">
@@ -18072,7 +18125,7 @@
       <c r="M256" s="2"/>
       <c r="N256" s="2"/>
       <c r="O256">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P256" s="2"/>
       <c r="Q256">
@@ -18136,7 +18189,9 @@
       <c r="M257" s="2"/>
       <c r="N257" s="2"/>
       <c r="O257" s="2"/>
-      <c r="P257" s="2"/>
+      <c r="P257" s="2">
+        <v>56</v>
+      </c>
       <c r="Q257" s="2"/>
       <c r="R257">
         <v>10</v>
@@ -18200,9 +18255,11 @@
       <c r="M258" s="2"/>
       <c r="N258" s="2"/>
       <c r="O258">
-        <v>20</v>
-      </c>
-      <c r="P258" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="P258" s="2">
+        <v>70</v>
+      </c>
       <c r="Q258" s="2"/>
       <c r="R258">
         <v>20</v>
@@ -18335,7 +18392,9 @@
       <c r="T260">
         <v>36</v>
       </c>
-      <c r="U260" s="2"/>
+      <c r="U260" s="2">
+        <v>1</v>
+      </c>
       <c r="V260" s="2"/>
       <c r="W260" s="2"/>
       <c r="X260" s="2"/>
@@ -19034,7 +19093,7 @@
       </c>
       <c r="N272" s="2"/>
       <c r="O272">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P272" s="2"/>
       <c r="Q272">
@@ -19099,7 +19158,7 @@
         <v>1</v>
       </c>
       <c r="R273">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="S273" s="2"/>
       <c r="T273" s="2"/>
@@ -19146,7 +19205,7 @@
       <c r="M274" s="2"/>
       <c r="N274" s="2"/>
       <c r="O274">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="P274" s="2"/>
       <c r="Q274" s="2"/>
@@ -19219,7 +19278,7 @@
       <c r="X275" s="2"/>
       <c r="Y275" s="2"/>
       <c r="Z275">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="AA275" s="2"/>
       <c r="AB275" s="2"/>
@@ -19390,7 +19449,7 @@
       <c r="M278" s="2"/>
       <c r="N278" s="2"/>
       <c r="O278">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="P278" s="2"/>
       <c r="Q278">
@@ -20228,7 +20287,7 @@
       <c r="M292" s="2"/>
       <c r="N292" s="2"/>
       <c r="O292">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="P292" s="2"/>
       <c r="Q292" s="2"/>
@@ -20290,7 +20349,7 @@
       <c r="M293" s="2"/>
       <c r="N293" s="2"/>
       <c r="O293">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="P293" s="2"/>
       <c r="Q293">
@@ -20507,7 +20566,7 @@
       <c r="X296" s="2"/>
       <c r="Y296" s="2"/>
       <c r="Z296">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="AA296" s="2"/>
       <c r="AB296" s="2"/>
@@ -20573,7 +20632,7 @@
       <c r="X297" s="2"/>
       <c r="Y297" s="2"/>
       <c r="Z297">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="AA297" s="2"/>
       <c r="AB297" s="2"/>
@@ -20875,7 +20934,7 @@
       <c r="X302" s="2"/>
       <c r="Y302" s="2"/>
       <c r="Z302">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="AA302" s="2"/>
       <c r="AB302" s="2"/>
@@ -20916,9 +20975,11 @@
       <c r="M303" s="2"/>
       <c r="N303" s="2"/>
       <c r="O303">
-        <v>20</v>
-      </c>
-      <c r="P303" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="P303" s="2">
+        <v>72</v>
+      </c>
       <c r="Q303">
         <v>1</v>
       </c>
@@ -21100,7 +21161,7 @@
       <c r="M306" s="2"/>
       <c r="N306" s="2"/>
       <c r="O306">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="P306" s="2"/>
       <c r="Q306">
@@ -21164,7 +21225,7 @@
       <c r="M307" s="2"/>
       <c r="N307" s="2"/>
       <c r="O307">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="P307" s="2"/>
       <c r="Q307">
@@ -21359,7 +21420,7 @@
       <c r="N310" s="2"/>
       <c r="O310" s="2"/>
       <c r="P310">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q310">
         <v>6</v>
@@ -21478,7 +21539,7 @@
       <c r="M312" s="2"/>
       <c r="N312" s="2"/>
       <c r="O312">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="P312" s="2"/>
       <c r="Q312" s="2"/>
@@ -21538,7 +21599,7 @@
       </c>
       <c r="N313" s="2"/>
       <c r="O313">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="P313" s="2"/>
       <c r="Q313" s="2"/>
@@ -21782,7 +21843,7 @@
       <c r="M317" s="2"/>
       <c r="N317" s="2"/>
       <c r="O317">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P317" s="2"/>
       <c r="Q317">
@@ -21964,7 +22025,7 @@
       <c r="M320" s="2"/>
       <c r="N320" s="2"/>
       <c r="O320">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P320" s="2"/>
       <c r="Q320">
@@ -22028,7 +22089,7 @@
       <c r="M321" s="2"/>
       <c r="N321" s="2"/>
       <c r="O321">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="P321" s="2"/>
       <c r="Q321" s="2"/>
@@ -22090,7 +22151,7 @@
       <c r="M322" s="2"/>
       <c r="N322" s="2"/>
       <c r="O322">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P322" s="2"/>
       <c r="Q322">
@@ -22156,7 +22217,7 @@
       <c r="M323" s="2"/>
       <c r="N323" s="2"/>
       <c r="O323">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="P323" s="2"/>
       <c r="Q323">
@@ -22888,7 +22949,7 @@
       <c r="M335" s="2"/>
       <c r="N335" s="2"/>
       <c r="O335">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="P335" s="2"/>
       <c r="Q335">
@@ -22948,7 +23009,7 @@
       <c r="M336" s="2"/>
       <c r="N336" s="2"/>
       <c r="O336">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="P336" s="2"/>
       <c r="Q336">
@@ -23012,7 +23073,7 @@
       <c r="M337" s="2"/>
       <c r="N337" s="2"/>
       <c r="O337">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="P337" s="2"/>
       <c r="Q337">
@@ -23204,9 +23265,11 @@
       <c r="M340" s="2"/>
       <c r="N340" s="2"/>
       <c r="O340">
-        <v>10</v>
-      </c>
-      <c r="P340" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="P340" s="2">
+        <v>96</v>
+      </c>
       <c r="Q340" s="2"/>
       <c r="R340">
         <v>20</v>
@@ -23268,9 +23331,11 @@
       <c r="M341" s="2"/>
       <c r="N341" s="2"/>
       <c r="O341">
-        <v>20</v>
-      </c>
-      <c r="P341" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="P341" s="2">
+        <v>108</v>
+      </c>
       <c r="Q341">
         <v>10</v>
       </c>
@@ -23334,9 +23399,11 @@
       <c r="M342" s="2"/>
       <c r="N342" s="2"/>
       <c r="O342">
-        <v>10</v>
-      </c>
-      <c r="P342" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="P342" s="2">
+        <v>80</v>
+      </c>
       <c r="Q342" s="2"/>
       <c r="R342">
         <v>20</v>
@@ -23396,9 +23463,11 @@
       <c r="M343" s="2"/>
       <c r="N343" s="2"/>
       <c r="O343">
-        <v>20</v>
-      </c>
-      <c r="P343" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="P343" s="2">
+        <v>88</v>
+      </c>
       <c r="Q343" s="2"/>
       <c r="R343">
         <v>24</v>
@@ -23846,7 +23915,7 @@
       <c r="M351" s="2"/>
       <c r="N351" s="2"/>
       <c r="O351">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="P351" s="2"/>
       <c r="Q351">
@@ -24551,7 +24620,7 @@
       <c r="N362" s="2"/>
       <c r="O362" s="2"/>
       <c r="P362">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Q362" s="2"/>
       <c r="R362">
@@ -24730,7 +24799,7 @@
       <c r="M365" s="2"/>
       <c r="N365" s="2"/>
       <c r="O365">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P365" s="2"/>
       <c r="Q365" s="2"/>
@@ -24794,7 +24863,7 @@
       <c r="M366" s="2"/>
       <c r="N366" s="2"/>
       <c r="O366">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="P366" s="2"/>
       <c r="Q366" s="2"/>
@@ -24860,7 +24929,7 @@
       <c r="M367" s="2"/>
       <c r="N367" s="2"/>
       <c r="O367">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="P367" s="2"/>
       <c r="Q367" s="2"/>
@@ -25046,7 +25115,9 @@
       <c r="M370" s="2"/>
       <c r="N370" s="2"/>
       <c r="O370" s="2"/>
-      <c r="P370" s="2"/>
+      <c r="P370" s="2">
+        <v>48</v>
+      </c>
       <c r="Q370" s="2"/>
       <c r="R370">
         <v>10</v>
@@ -25108,9 +25179,11 @@
       <c r="M371" s="2"/>
       <c r="N371" s="2"/>
       <c r="O371">
-        <v>10</v>
-      </c>
-      <c r="P371" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="P371" s="2">
+        <v>60</v>
+      </c>
       <c r="Q371" s="2"/>
       <c r="R371">
         <v>24</v>
@@ -25172,9 +25245,11 @@
       <c r="M372" s="2"/>
       <c r="N372" s="2"/>
       <c r="O372">
-        <v>20</v>
-      </c>
-      <c r="P372" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="P372" s="2">
+        <v>84</v>
+      </c>
       <c r="Q372">
         <v>10</v>
       </c>
@@ -26106,9 +26181,11 @@
       <c r="M387" s="2"/>
       <c r="N387" s="2"/>
       <c r="O387">
-        <v>30</v>
-      </c>
-      <c r="P387" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="P387" s="2">
+        <v>60</v>
+      </c>
       <c r="Q387" s="2"/>
       <c r="R387">
         <v>50</v>
@@ -26240,7 +26317,7 @@
       <c r="M389" s="2"/>
       <c r="N389" s="2"/>
       <c r="O389">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P389" s="2"/>
       <c r="Q389" s="2"/>
@@ -26304,7 +26381,7 @@
       <c r="M390" s="2"/>
       <c r="N390" s="2"/>
       <c r="O390">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="P390" s="2"/>
       <c r="Q390">
@@ -27585,7 +27662,7 @@
       <c r="P411" s="2"/>
       <c r="Q411" s="2"/>
       <c r="R411">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="S411" s="2"/>
       <c r="T411" s="2"/>
@@ -27946,7 +28023,7 @@
       <c r="M417" s="2"/>
       <c r="N417" s="2"/>
       <c r="O417">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="P417" s="2"/>
       <c r="Q417">
@@ -28012,7 +28089,7 @@
       <c r="M418" s="2"/>
       <c r="N418" s="2"/>
       <c r="O418">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P418" s="2"/>
       <c r="Q418">
@@ -28080,7 +28157,7 @@
       <c r="M419" s="2"/>
       <c r="N419" s="2"/>
       <c r="O419">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="P419" s="2"/>
       <c r="Q419">
@@ -28150,7 +28227,7 @@
       <c r="M420" s="2"/>
       <c r="N420" s="2"/>
       <c r="O420">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P420" s="2"/>
       <c r="Q420">
@@ -28210,7 +28287,7 @@
       <c r="M421" s="2"/>
       <c r="N421" s="2"/>
       <c r="O421">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="P421" s="2"/>
       <c r="Q421">
@@ -28274,9 +28351,11 @@
       <c r="M422" s="2"/>
       <c r="N422" s="2"/>
       <c r="O422">
-        <v>10</v>
-      </c>
-      <c r="P422" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="P422" s="2">
+        <v>60</v>
+      </c>
       <c r="Q422" s="2"/>
       <c r="R422">
         <v>10</v>
@@ -28334,9 +28413,11 @@
       <c r="M423" s="2"/>
       <c r="N423" s="2"/>
       <c r="O423">
-        <v>10</v>
-      </c>
-      <c r="P423" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="P423" s="2">
+        <v>70</v>
+      </c>
       <c r="Q423" s="2"/>
       <c r="R423">
         <v>16</v>
@@ -28972,7 +29053,7 @@
       <c r="M433" s="2"/>
       <c r="N433" s="2"/>
       <c r="O433">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="P433" s="2"/>
       <c r="Q433">
@@ -29086,7 +29167,7 @@
       <c r="M435" s="2"/>
       <c r="N435" s="2"/>
       <c r="O435">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="P435" s="2"/>
       <c r="Q435">
@@ -30710,9 +30791,11 @@
       <c r="M462" s="2"/>
       <c r="N462" s="2"/>
       <c r="O462">
-        <v>10</v>
-      </c>
-      <c r="P462" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="P462" s="2">
+        <v>100</v>
+      </c>
       <c r="Q462">
         <v>10</v>
       </c>
@@ -31148,7 +31231,7 @@
       <c r="M469" s="2"/>
       <c r="N469" s="2"/>
       <c r="O469">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="P469" s="2"/>
       <c r="Q469">
@@ -31278,7 +31361,9 @@
       <c r="M471" s="2"/>
       <c r="N471" s="2"/>
       <c r="O471" s="2"/>
-      <c r="P471" s="2"/>
+      <c r="P471">
+        <v>60</v>
+      </c>
       <c r="Q471">
         <v>10</v>
       </c>
@@ -31344,7 +31429,9 @@
       <c r="M472" s="2"/>
       <c r="N472" s="2"/>
       <c r="O472" s="2"/>
-      <c r="P472" s="2"/>
+      <c r="P472">
+        <v>60</v>
+      </c>
       <c r="Q472">
         <v>20</v>
       </c>
@@ -31425,7 +31512,9 @@
       <c r="T473">
         <v>6</v>
       </c>
-      <c r="U473" s="2"/>
+      <c r="U473" s="2">
+        <v>1</v>
+      </c>
       <c r="V473" s="2"/>
       <c r="W473" s="2"/>
       <c r="X473" s="2"/>
@@ -31489,7 +31578,9 @@
       <c r="T474">
         <v>60</v>
       </c>
-      <c r="U474" s="2"/>
+      <c r="U474" s="2">
+        <v>2</v>
+      </c>
       <c r="V474" s="2"/>
       <c r="W474" s="2"/>
       <c r="X474">
@@ -31610,7 +31701,7 @@
       </c>
       <c r="N476" s="2"/>
       <c r="O476">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="P476" s="2"/>
       <c r="Q476" s="2"/>
@@ -31666,9 +31757,11 @@
       <c r="M477" s="2"/>
       <c r="N477" s="2"/>
       <c r="O477">
-        <v>10</v>
-      </c>
-      <c r="P477" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="P477" s="2">
+        <v>60</v>
+      </c>
       <c r="Q477">
         <v>10</v>
       </c>
@@ -31968,7 +32061,7 @@
       <c r="M482" s="2"/>
       <c r="N482" s="2"/>
       <c r="O482">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P482" s="2"/>
       <c r="Q482">
@@ -32032,7 +32125,7 @@
       <c r="M483" s="2"/>
       <c r="N483" s="2"/>
       <c r="O483">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="P483" s="2"/>
       <c r="Q483" s="2"/>
@@ -32214,7 +32307,7 @@
       <c r="M486" s="2"/>
       <c r="N486" s="2"/>
       <c r="O486">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P486" s="2"/>
       <c r="Q486" s="2"/>
@@ -32346,7 +32439,7 @@
       <c r="M488" s="2"/>
       <c r="N488" s="2"/>
       <c r="O488">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="P488" s="2"/>
       <c r="Q488">
@@ -33095,7 +33188,7 @@
       <c r="X501" s="2"/>
       <c r="Y501" s="2"/>
       <c r="Z501">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="AA501" s="2"/>
       <c r="AB501" s="2"/>
@@ -34661,7 +34754,7 @@
       <c r="P527" s="2"/>
       <c r="Q527" s="2"/>
       <c r="R527">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="S527" s="2"/>
       <c r="T527" s="2"/>
@@ -34711,7 +34804,7 @@
       <c r="P528" s="2"/>
       <c r="Q528" s="2"/>
       <c r="R528">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="S528" s="2"/>
       <c r="T528" s="2"/>
@@ -35270,7 +35363,7 @@
       <c r="M537" s="2"/>
       <c r="N537" s="2"/>
       <c r="O537">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P537" s="2"/>
       <c r="Q537">
@@ -35336,7 +35429,9 @@
       <c r="M538" s="2"/>
       <c r="N538" s="2"/>
       <c r="O538" s="2"/>
-      <c r="P538" s="2"/>
+      <c r="P538" s="2">
+        <v>50</v>
+      </c>
       <c r="Q538" s="2"/>
       <c r="R538">
         <v>10</v>
@@ -35396,7 +35491,7 @@
       <c r="M539" s="2"/>
       <c r="N539" s="2"/>
       <c r="O539">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="P539" s="2"/>
       <c r="Q539">
@@ -35462,7 +35557,7 @@
       <c r="M540" s="2"/>
       <c r="N540" s="2"/>
       <c r="O540">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="P540" s="2"/>
       <c r="Q540">
@@ -35530,9 +35625,11 @@
       <c r="M541" s="2"/>
       <c r="N541" s="2"/>
       <c r="O541">
-        <v>30</v>
-      </c>
-      <c r="P541" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="P541" s="2">
+        <v>108</v>
+      </c>
       <c r="Q541">
         <v>10</v>
       </c>
@@ -35828,7 +35925,7 @@
       <c r="M546" s="2"/>
       <c r="N546" s="2"/>
       <c r="O546">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P546" s="2"/>
       <c r="Q546">
@@ -35958,7 +36055,9 @@
       <c r="M548" s="2"/>
       <c r="N548" s="2"/>
       <c r="O548" s="2"/>
-      <c r="P548" s="2"/>
+      <c r="P548" s="2">
+        <v>66</v>
+      </c>
       <c r="Q548" s="2"/>
       <c r="R548">
         <v>12</v>
@@ -36146,7 +36245,7 @@
       <c r="M551" s="2"/>
       <c r="N551" s="2"/>
       <c r="O551">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="P551" s="2"/>
       <c r="Q551">
@@ -36210,7 +36309,7 @@
       <c r="M552" s="2"/>
       <c r="N552" s="2"/>
       <c r="O552">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="P552" s="2"/>
       <c r="Q552">
@@ -36276,9 +36375,11 @@
       <c r="M553" s="2"/>
       <c r="N553" s="2"/>
       <c r="O553">
-        <v>30</v>
-      </c>
-      <c r="P553" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="P553" s="2">
+        <v>78</v>
+      </c>
       <c r="Q553">
         <v>10</v>
       </c>
@@ -36342,7 +36443,7 @@
       <c r="M554" s="2"/>
       <c r="N554" s="2"/>
       <c r="O554">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="P554" s="2"/>
       <c r="Q554">
@@ -36466,7 +36567,7 @@
       <c r="M556" s="2"/>
       <c r="N556" s="2"/>
       <c r="O556">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P556" s="2"/>
       <c r="Q556" s="2"/>
@@ -36523,7 +36624,7 @@
       <c r="P557" s="2"/>
       <c r="Q557" s="2"/>
       <c r="R557">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="S557" s="2"/>
       <c r="T557" s="2"/>
@@ -37842,7 +37943,11 @@
       <c r="AF585" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AH585" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:AH585" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AH585">
+      <sortCondition ref="A2:A585"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/doc/equip/Equip.xlsx
+++ b/doc/equip/Equip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mj\GuoMuoRuoProject\doc\equip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACE5B53-C22B-4FCE-916F-66C7CE89A676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCC8E7F-531B-4084-BCC2-2B677912A92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Equip!$A$2:$AH$585</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -9317,7 +9317,7 @@
       </c>
       <c r="S109" s="2"/>
       <c r="T109">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="U109" s="2">
         <v>3</v>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="S259" s="2"/>
       <c r="T259">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="U259" s="2"/>
       <c r="V259" s="2"/>
@@ -18390,7 +18390,7 @@
       <c r="R260" s="2"/>
       <c r="S260" s="2"/>
       <c r="T260">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="U260" s="2">
         <v>1</v>
@@ -31510,7 +31510,7 @@
       </c>
       <c r="S473" s="2"/>
       <c r="T473">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U473" s="2">
         <v>1</v>
@@ -31576,7 +31576,7 @@
       </c>
       <c r="S474" s="2"/>
       <c r="T474">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="U474" s="2">
         <v>2</v>

--- a/doc/equip/Equip.xlsx
+++ b/doc/equip/Equip.xlsx
@@ -2723,31 +2723,31 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2962,14 +2962,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AH585"/>
-  <sheetFormatPr defaultColWidth="5.54296875" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="5.453125" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.69"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="5.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.9"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="32" min="6" style="1" width="5.54"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="33" style="2" width="5.54"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.39"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="5.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="32" min="6" style="1" width="5.45"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="33" style="2" width="5.45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/doc/equip/Equip.xlsx
+++ b/doc/equip/Equip.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -2651,7 +2651,7 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="0"/>
-      <charset val="134"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2673,7 +2673,7 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
-      <charset val="134"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2827,14 +2827,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -2842,67 +2842,25 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -2921,35 +2879,11 @@
           <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
@@ -2962,14 +2896,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AH585"/>
-  <sheetFormatPr defaultColWidth="5.453125" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="5.27734375" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.39"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="5.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="32" min="6" style="1" width="5.45"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="33" style="2" width="5.45"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.81"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="5.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.81"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="32" min="6" style="1" width="5.28"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="33" style="2" width="5.28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4076,7 +4010,7 @@
       <c r="AE17" s="6"/>
       <c r="AF17" s="6"/>
     </row>
-    <row r="18" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
         <v>16</v>
       </c>
@@ -4138,7 +4072,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="n">
         <v>17</v>
       </c>
@@ -4198,7 +4132,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="n">
         <v>18</v>
       </c>
@@ -4260,7 +4194,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="n">
         <v>19</v>
       </c>
@@ -4426,7 +4360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="n">
         <v>22</v>
       </c>
@@ -4480,7 +4414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="n">
         <v>23</v>
       </c>
@@ -4538,7 +4472,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
         <v>24</v>
       </c>
@@ -4594,7 +4528,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="n">
         <v>25</v>
       </c>
@@ -5048,7 +4982,7 @@
       <c r="AE34" s="6"/>
       <c r="AF34" s="6"/>
     </row>
-    <row r="35" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="n">
         <v>33</v>
       </c>
@@ -5102,7 +5036,7 @@
       <c r="AE35" s="6"/>
       <c r="AF35" s="6"/>
     </row>
-    <row r="36" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="n">
         <v>34</v>
       </c>
@@ -5156,7 +5090,7 @@
       <c r="AE36" s="6"/>
       <c r="AF36" s="6"/>
     </row>
-    <row r="37" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="n">
         <v>35</v>
       </c>
@@ -5210,7 +5144,7 @@
       <c r="AE37" s="6"/>
       <c r="AF37" s="6"/>
     </row>
-    <row r="38" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="n">
         <v>36</v>
       </c>
@@ -5476,7 +5410,7 @@
       <c r="AE42" s="6"/>
       <c r="AF42" s="6"/>
     </row>
-    <row r="43" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="n">
         <v>41</v>
       </c>
@@ -5530,7 +5464,7 @@
       <c r="AE43" s="6"/>
       <c r="AF43" s="6"/>
     </row>
-    <row r="44" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="n">
         <v>42</v>
       </c>
@@ -5581,7 +5515,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="45" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="n">
         <v>43</v>
       </c>
@@ -5632,7 +5566,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="46" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="n">
         <v>44</v>
       </c>
@@ -5684,7 +5618,7 @@
       <c r="AE46" s="6"/>
       <c r="AF46" s="6"/>
     </row>
-    <row r="47" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="n">
         <v>45</v>
       </c>
@@ -5734,7 +5668,7 @@
       <c r="AE47" s="6"/>
       <c r="AF47" s="6"/>
     </row>
-    <row r="48" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="n">
         <v>46</v>
       </c>
@@ -5790,7 +5724,7 @@
       <c r="AE48" s="6"/>
       <c r="AF48" s="6"/>
     </row>
-    <row r="49" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="n">
         <v>47</v>
       </c>
@@ -6072,7 +6006,7 @@
       <c r="AE53" s="6"/>
       <c r="AF53" s="6"/>
     </row>
-    <row r="54" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="n">
         <v>52</v>
       </c>
@@ -6134,7 +6068,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="n">
         <v>53</v>
       </c>
@@ -6188,7 +6122,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="n">
         <v>54</v>
       </c>
@@ -6246,7 +6180,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="n">
         <v>55</v>
       </c>
@@ -6302,7 +6236,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="n">
         <v>56</v>
       </c>
@@ -6354,7 +6288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="n">
         <v>57</v>
       </c>
@@ -6466,7 +6400,7 @@
       <c r="AE60" s="6"/>
       <c r="AF60" s="6"/>
     </row>
-    <row r="61" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="n">
         <v>59</v>
       </c>
@@ -6586,7 +6520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="n">
         <v>61</v>
       </c>
@@ -6960,7 +6894,7 @@
       <c r="AE68" s="6"/>
       <c r="AF68" s="6"/>
     </row>
-    <row r="69" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="n">
         <v>68</v>
       </c>
@@ -7014,7 +6948,7 @@
       </c>
       <c r="AF69" s="6"/>
     </row>
-    <row r="70" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="n">
         <v>69</v>
       </c>
@@ -7302,7 +7236,7 @@
       <c r="AE74" s="6"/>
       <c r="AF74" s="6"/>
     </row>
-    <row r="75" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="n">
         <v>74</v>
       </c>
@@ -7964,7 +7898,7 @@
       <c r="AE85" s="6"/>
       <c r="AF85" s="6"/>
     </row>
-    <row r="86" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="n">
         <v>85</v>
       </c>
@@ -8018,7 +7952,7 @@
       <c r="AE86" s="6"/>
       <c r="AF86" s="6"/>
     </row>
-    <row r="87" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="n">
         <v>86</v>
       </c>
@@ -8068,7 +8002,7 @@
       <c r="AE87" s="6"/>
       <c r="AF87" s="6"/>
     </row>
-    <row r="88" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="n">
         <v>87</v>
       </c>
@@ -8924,7 +8858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="5" t="n">
         <v>101</v>
       </c>
@@ -9272,7 +9206,7 @@
       <c r="AE107" s="6"/>
       <c r="AF107" s="6"/>
     </row>
-    <row r="108" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="5" t="n">
         <v>107</v>
       </c>
@@ -9328,7 +9262,7 @@
       <c r="AE108" s="6"/>
       <c r="AF108" s="6"/>
     </row>
-    <row r="109" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="5" t="n">
         <v>108</v>
       </c>
@@ -9824,7 +9758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="5" t="n">
         <v>116</v>
       </c>
@@ -9940,7 +9874,7 @@
       <c r="AE118" s="6"/>
       <c r="AF118" s="6"/>
     </row>
-    <row r="119" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="n">
         <v>118</v>
       </c>
@@ -10414,7 +10348,7 @@
       <c r="AE126" s="6"/>
       <c r="AF126" s="6"/>
     </row>
-    <row r="127" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="5" t="n">
         <v>126</v>
       </c>
@@ -10588,7 +10522,7 @@
       <c r="AE129" s="6"/>
       <c r="AF129" s="6"/>
     </row>
-    <row r="130" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="5" t="n">
         <v>129</v>
       </c>
@@ -10764,7 +10698,7 @@
       <c r="AE132" s="6"/>
       <c r="AF132" s="6"/>
     </row>
-    <row r="133" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="5" t="n">
         <v>132</v>
       </c>
@@ -11132,7 +11066,7 @@
       <c r="AE138" s="6"/>
       <c r="AF138" s="6"/>
     </row>
-    <row r="139" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="5" t="n">
         <v>138</v>
       </c>
@@ -11552,7 +11486,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="n">
         <v>145</v>
       </c>
@@ -11581,7 +11515,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="147" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="5" t="n">
         <v>146</v>
       </c>
@@ -11693,7 +11627,7 @@
       <c r="AE148" s="6"/>
       <c r="AF148" s="6"/>
     </row>
-    <row r="149" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="5" t="n">
         <v>148</v>
       </c>
@@ -11755,7 +11689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="5" t="n">
         <v>149</v>
       </c>
@@ -11811,7 +11745,7 @@
       <c r="AE150" s="6"/>
       <c r="AF150" s="6"/>
     </row>
-    <row r="151" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="n">
         <v>150</v>
       </c>
@@ -12706,7 +12640,7 @@
       <c r="AE165" s="6"/>
       <c r="AF165" s="6"/>
     </row>
-    <row r="166" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="5" t="n">
         <v>165</v>
       </c>
@@ -12816,7 +12750,7 @@
       </c>
       <c r="AF167" s="6"/>
     </row>
-    <row r="168" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="5" t="n">
         <v>167</v>
       </c>
@@ -12870,7 +12804,7 @@
       </c>
       <c r="AF168" s="6"/>
     </row>
-    <row r="169" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="5" t="n">
         <v>168</v>
       </c>
@@ -12934,7 +12868,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="170" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="5" t="n">
         <v>169</v>
       </c>
@@ -13062,7 +12996,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="172" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="5" t="n">
         <v>171</v>
       </c>
@@ -13308,7 +13242,7 @@
       <c r="AE175" s="6"/>
       <c r="AF175" s="6"/>
     </row>
-    <row r="176" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="5" t="n">
         <v>175</v>
       </c>
@@ -13366,7 +13300,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="5" t="n">
         <v>176</v>
       </c>
@@ -13484,7 +13418,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="5" t="n">
         <v>178</v>
       </c>
@@ -13596,7 +13530,7 @@
       <c r="AE180" s="6"/>
       <c r="AF180" s="6"/>
     </row>
-    <row r="181" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="5" t="n">
         <v>180</v>
       </c>
@@ -13906,7 +13840,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="5" t="n">
         <v>185</v>
       </c>
@@ -13964,7 +13898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="5" t="n">
         <v>186</v>
       </c>
@@ -14028,7 +13962,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="188" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="5" t="n">
         <v>187</v>
       </c>
@@ -14396,7 +14330,7 @@
       <c r="AE193" s="6"/>
       <c r="AF193" s="6"/>
     </row>
-    <row r="194" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="5" t="n">
         <v>193</v>
       </c>
@@ -14516,7 +14450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="5" t="n">
         <v>195</v>
       </c>
@@ -14584,7 +14518,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="5" t="n">
         <v>196</v>
       </c>
@@ -14648,7 +14582,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="5" t="n">
         <v>197</v>
       </c>
@@ -14708,7 +14642,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="5" t="n">
         <v>198</v>
       </c>
@@ -14770,7 +14704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="5" t="n">
         <v>199</v>
       </c>
@@ -14832,7 +14766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="5" t="n">
         <v>200</v>
       </c>
@@ -14892,7 +14826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="5" t="n">
         <v>201</v>
       </c>
@@ -14954,7 +14888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="203" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="5" t="n">
         <v>202</v>
       </c>
@@ -15122,7 +15056,7 @@
       <c r="AE205" s="6"/>
       <c r="AF205" s="6"/>
     </row>
-    <row r="206" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="5" t="n">
         <v>205</v>
       </c>
@@ -15184,7 +15118,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="5" t="n">
         <v>206</v>
       </c>
@@ -15426,7 +15360,7 @@
       <c r="AE210" s="6"/>
       <c r="AF210" s="6"/>
     </row>
-    <row r="211" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="5" t="n">
         <v>210</v>
       </c>
@@ -15830,7 +15764,7 @@
       <c r="AE217" s="6"/>
       <c r="AF217" s="6"/>
     </row>
-    <row r="218" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="5" t="n">
         <v>217</v>
       </c>
@@ -15886,7 +15820,7 @@
       <c r="AE218" s="6"/>
       <c r="AF218" s="6"/>
     </row>
-    <row r="219" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="5" t="n">
         <v>218</v>
       </c>
@@ -16378,7 +16312,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="227" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="5" t="n">
         <v>226</v>
       </c>
@@ -16430,7 +16364,7 @@
       <c r="AE227" s="6"/>
       <c r="AF227" s="6"/>
     </row>
-    <row r="228" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="5" t="n">
         <v>227</v>
       </c>
@@ -16480,7 +16414,7 @@
       <c r="AE228" s="6"/>
       <c r="AF228" s="6"/>
     </row>
-    <row r="229" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="5" t="n">
         <v>228</v>
       </c>
@@ -16784,7 +16718,7 @@
       <c r="AE233" s="6"/>
       <c r="AF233" s="6"/>
     </row>
-    <row r="234" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="5" t="n">
         <v>233</v>
       </c>
@@ -17321,7 +17255,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="243" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="5" t="n">
         <v>242</v>
       </c>
@@ -17705,7 +17639,7 @@
       <c r="AE248" s="6"/>
       <c r="AF248" s="6"/>
     </row>
-    <row r="249" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="5" t="n">
         <v>248</v>
       </c>
@@ -17767,7 +17701,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="250" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="5" t="n">
         <v>249</v>
       </c>
@@ -17833,7 +17767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="251" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="5" t="n">
         <v>250</v>
       </c>
@@ -17895,7 +17829,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="5" t="n">
         <v>251</v>
       </c>
@@ -18081,7 +18015,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="5" t="n">
         <v>254</v>
       </c>
@@ -18145,7 +18079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="5" t="n">
         <v>255</v>
       </c>
@@ -18209,7 +18143,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="5" t="n">
         <v>256</v>
       </c>
@@ -18273,7 +18207,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="258" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="5" t="n">
         <v>257</v>
       </c>
@@ -18341,7 +18275,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="259" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="5" t="n">
         <v>258</v>
       </c>
@@ -18399,7 +18333,7 @@
       <c r="AE259" s="6"/>
       <c r="AF259" s="6"/>
     </row>
-    <row r="260" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="5" t="n">
         <v>259</v>
       </c>
@@ -18461,7 +18395,7 @@
       <c r="AE260" s="6"/>
       <c r="AF260" s="6"/>
     </row>
-    <row r="261" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="5" t="n">
         <v>260</v>
       </c>
@@ -18519,7 +18453,7 @@
       <c r="AE261" s="6"/>
       <c r="AF261" s="6"/>
     </row>
-    <row r="262" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="5" t="n">
         <v>261</v>
       </c>
@@ -18575,7 +18509,7 @@
       <c r="AE262" s="6"/>
       <c r="AF262" s="6"/>
     </row>
-    <row r="263" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="5" t="n">
         <v>262</v>
       </c>
@@ -18999,7 +18933,7 @@
       <c r="AE269" s="6"/>
       <c r="AF269" s="6"/>
     </row>
-    <row r="270" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="5" t="n">
         <v>269</v>
       </c>
@@ -19115,7 +19049,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="272" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="5" t="n">
         <v>271</v>
       </c>
@@ -19173,7 +19107,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="273" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="5" t="n">
         <v>272</v>
       </c>
@@ -19469,7 +19403,7 @@
       <c r="AE277" s="6"/>
       <c r="AF277" s="6"/>
     </row>
-    <row r="278" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="5" t="n">
         <v>277</v>
       </c>
@@ -20079,7 +20013,7 @@
       <c r="AE287" s="6"/>
       <c r="AF287" s="6"/>
     </row>
-    <row r="288" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="5" t="n">
         <v>287</v>
       </c>
@@ -21125,7 +21059,7 @@
       <c r="AE304" s="6"/>
       <c r="AF304" s="6"/>
     </row>
-    <row r="305" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="5" t="n">
         <v>304</v>
       </c>
@@ -21313,7 +21247,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="308" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="5" t="n">
         <v>307</v>
       </c>
@@ -21443,7 +21377,7 @@
       <c r="AE309" s="6"/>
       <c r="AF309" s="6"/>
     </row>
-    <row r="310" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="310" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="5" t="n">
         <v>309</v>
       </c>
@@ -21561,7 +21495,7 @@
       <c r="AE311" s="6"/>
       <c r="AF311" s="6"/>
     </row>
-    <row r="312" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="5" t="n">
         <v>311</v>
       </c>
@@ -21927,7 +21861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="5" t="n">
         <v>317</v>
       </c>
@@ -22303,7 +22237,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="324" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="5" t="n">
         <v>324</v>
       </c>
@@ -22359,7 +22293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="325" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="5" t="n">
         <v>325</v>
       </c>
@@ -22417,7 +22351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="326" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="5" t="n">
         <v>326</v>
       </c>
@@ -22853,7 +22787,7 @@
       <c r="AE332" s="6"/>
       <c r="AF332" s="6"/>
     </row>
-    <row r="333" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="333" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="5" t="n">
         <v>333</v>
       </c>
@@ -22971,7 +22905,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="335" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="5" t="n">
         <v>336</v>
       </c>
@@ -23029,7 +22963,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="336" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="336" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="5" t="n">
         <v>338</v>
       </c>
@@ -23763,7 +23697,7 @@
       <c r="AE347" s="6"/>
       <c r="AF347" s="6"/>
     </row>
-    <row r="348" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="5" t="n">
         <v>350</v>
       </c>
@@ -23821,7 +23755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="349" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="5" t="n">
         <v>351</v>
       </c>
@@ -23877,7 +23811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="5" t="n">
         <v>352</v>
       </c>
@@ -23995,7 +23929,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="352" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="352" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="5" t="n">
         <v>354</v>
       </c>
@@ -24057,7 +23991,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="353" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="5" t="n">
         <v>355</v>
       </c>
@@ -24697,7 +24631,7 @@
       <c r="AE362" s="6"/>
       <c r="AF362" s="6"/>
     </row>
-    <row r="363" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="363" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="5" t="n">
         <v>365</v>
       </c>
@@ -25137,7 +25071,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="370" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="370" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="5" t="n">
         <v>372</v>
       </c>
@@ -25333,7 +25267,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="5" t="n">
         <v>375</v>
       </c>
@@ -25877,7 +25811,7 @@
       <c r="AE381" s="6"/>
       <c r="AF381" s="6"/>
     </row>
-    <row r="382" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="382" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="5" t="n">
         <v>384</v>
       </c>
@@ -26339,7 +26273,7 @@
       <c r="AE388" s="6"/>
       <c r="AF388" s="6"/>
     </row>
-    <row r="389" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="5" t="n">
         <v>391</v>
       </c>
@@ -26593,7 +26527,7 @@
       <c r="AE392" s="6"/>
       <c r="AF392" s="6"/>
     </row>
-    <row r="393" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="393" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="5" t="n">
         <v>395</v>
       </c>
@@ -26653,7 +26587,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="394" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="394" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="5" t="n">
         <v>396</v>
       </c>
@@ -26957,7 +26891,7 @@
       <c r="AE398" s="6"/>
       <c r="AF398" s="6"/>
     </row>
-    <row r="399" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="399" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="5" t="n">
         <v>401</v>
       </c>
@@ -27019,7 +26953,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="400" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="400" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="5" t="n">
         <v>402</v>
       </c>
@@ -27069,7 +27003,7 @@
       <c r="AE400" s="6"/>
       <c r="AF400" s="6"/>
     </row>
-    <row r="401" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="5" t="n">
         <v>403</v>
       </c>
@@ -27449,7 +27383,7 @@
       </c>
       <c r="AF406" s="6"/>
     </row>
-    <row r="407" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="5" t="n">
         <v>409</v>
       </c>
@@ -27619,7 +27553,7 @@
       <c r="AE409" s="6"/>
       <c r="AF409" s="6"/>
     </row>
-    <row r="410" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="410" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="5" t="n">
         <v>412</v>
       </c>
@@ -27681,7 +27615,7 @@
       <c r="AE410" s="6"/>
       <c r="AF410" s="6"/>
     </row>
-    <row r="411" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="5" t="n">
         <v>413</v>
       </c>
@@ -27735,7 +27669,7 @@
       <c r="AE411" s="6"/>
       <c r="AF411" s="6"/>
     </row>
-    <row r="412" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="412" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="5" t="n">
         <v>414</v>
       </c>
@@ -28043,7 +27977,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="417" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="417" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="5" t="n">
         <v>419</v>
       </c>
@@ -28109,7 +28043,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="418" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="418" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="5" t="n">
         <v>420</v>
       </c>
@@ -28177,7 +28111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="419" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="419" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="5" t="n">
         <v>421</v>
       </c>
@@ -28245,7 +28179,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="420" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="420" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="5" t="n">
         <v>422</v>
       </c>
@@ -28371,7 +28305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="422" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="422" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="5" t="n">
         <v>424</v>
       </c>
@@ -28435,7 +28369,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="423" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="423" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="5" t="n">
         <v>425</v>
       </c>
@@ -28819,7 +28753,7 @@
       <c r="AE428" s="6"/>
       <c r="AF428" s="6"/>
     </row>
-    <row r="429" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="5" t="n">
         <v>431</v>
       </c>
@@ -28883,7 +28817,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="430" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="5" t="n">
         <v>432</v>
       </c>
@@ -29011,7 +28945,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="432" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="432" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="5" t="n">
         <v>434</v>
       </c>
@@ -29071,7 +29005,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="433" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="5" t="n">
         <v>435</v>
       </c>
@@ -29191,7 +29125,7 @@
       <c r="AE434" s="6"/>
       <c r="AF434" s="6"/>
     </row>
-    <row r="435" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="435" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="5" t="n">
         <v>437</v>
       </c>
@@ -29247,7 +29181,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="436" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="436" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="5" t="n">
         <v>438</v>
       </c>
@@ -29581,7 +29515,7 @@
       <c r="AE441" s="6"/>
       <c r="AF441" s="6"/>
     </row>
-    <row r="442" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="5" t="n">
         <v>444</v>
       </c>
@@ -29647,7 +29581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="443" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="5" t="n">
         <v>445</v>
       </c>
@@ -29709,7 +29643,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="444" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="444" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="5" t="n">
         <v>446</v>
       </c>
@@ -29831,7 +29765,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="446" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="446" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="5" t="n">
         <v>449</v>
       </c>
@@ -29939,7 +29873,7 @@
       <c r="AE447" s="6"/>
       <c r="AF447" s="6"/>
     </row>
-    <row r="448" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="448" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="5" t="n">
         <v>451</v>
       </c>
@@ -30373,7 +30307,7 @@
       <c r="AE454" s="6"/>
       <c r="AF454" s="6"/>
     </row>
-    <row r="455" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="455" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="5" t="n">
         <v>458</v>
       </c>
@@ -30433,7 +30367,7 @@
       <c r="AE455" s="6"/>
       <c r="AF455" s="6"/>
     </row>
-    <row r="456" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="456" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="5" t="n">
         <v>459</v>
       </c>
@@ -31135,7 +31069,7 @@
       <c r="AE466" s="6"/>
       <c r="AF466" s="6"/>
     </row>
-    <row r="467" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="467" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="5" t="n">
         <v>471</v>
       </c>
@@ -31251,7 +31185,7 @@
       <c r="AE468" s="6"/>
       <c r="AF468" s="6"/>
     </row>
-    <row r="469" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="469" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="5" t="n">
         <v>473</v>
       </c>
@@ -31315,7 +31249,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="470" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="470" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="5" t="n">
         <v>474</v>
       </c>
@@ -31381,7 +31315,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="471" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="471" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="5" t="n">
         <v>475</v>
       </c>
@@ -31449,7 +31383,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="472" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="472" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="5" t="n">
         <v>476</v>
       </c>
@@ -31517,7 +31451,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="473" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="473" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="5" t="n">
         <v>477</v>
       </c>
@@ -31583,7 +31517,7 @@
       <c r="AE473" s="6"/>
       <c r="AF473" s="6"/>
     </row>
-    <row r="474" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="474" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="5" t="n">
         <v>478</v>
       </c>
@@ -31655,7 +31589,7 @@
       <c r="AE474" s="6"/>
       <c r="AF474" s="6"/>
     </row>
-    <row r="475" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="475" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="5" t="n">
         <v>479</v>
       </c>
@@ -31721,7 +31655,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="476" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="476" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="5" t="n">
         <v>480</v>
       </c>
@@ -31779,7 +31713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="477" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="477" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="5" t="n">
         <v>481</v>
       </c>
@@ -31901,7 +31835,7 @@
       <c r="AE478" s="6"/>
       <c r="AF478" s="6"/>
     </row>
-    <row r="479" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="479" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="5" t="n">
         <v>483</v>
       </c>
@@ -32025,7 +31959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="481" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="481" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="5" t="n">
         <v>485</v>
       </c>
@@ -32209,7 +32143,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="484" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="484" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="5" t="n">
         <v>488</v>
       </c>
@@ -32585,7 +32519,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="490" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="490" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="5" t="n">
         <v>494</v>
       </c>
@@ -32637,7 +32571,7 @@
       <c r="AE490" s="6"/>
       <c r="AF490" s="6"/>
     </row>
-    <row r="491" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="491" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="5" t="n">
         <v>495</v>
       </c>
@@ -32691,7 +32625,7 @@
       <c r="AE491" s="6"/>
       <c r="AF491" s="6"/>
     </row>
-    <row r="492" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="492" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="5" t="n">
         <v>496</v>
       </c>
@@ -32847,7 +32781,7 @@
       <c r="AE494" s="6"/>
       <c r="AF494" s="6"/>
     </row>
-    <row r="495" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="495" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="5" t="n">
         <v>499</v>
       </c>
@@ -33507,7 +33441,7 @@
       <c r="AE505" s="6"/>
       <c r="AF505" s="6"/>
     </row>
-    <row r="506" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="506" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="5" t="n">
         <v>510</v>
       </c>
@@ -33675,7 +33609,7 @@
       <c r="AE508" s="6"/>
       <c r="AF508" s="6"/>
     </row>
-    <row r="509" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="509" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="5" t="n">
         <v>513</v>
       </c>
@@ -33781,7 +33715,7 @@
       <c r="AE510" s="6"/>
       <c r="AF510" s="6"/>
     </row>
-    <row r="511" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="511" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="5" t="n">
         <v>515</v>
       </c>
@@ -34207,7 +34141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="518" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="518" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="5" t="n">
         <v>522</v>
       </c>
@@ -34401,7 +34335,7 @@
       <c r="AE520" s="6"/>
       <c r="AF520" s="6"/>
     </row>
-    <row r="521" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="521" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="5" t="n">
         <v>525</v>
       </c>
@@ -34459,7 +34393,7 @@
       </c>
       <c r="AF521" s="6"/>
     </row>
-    <row r="522" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="522" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="5" t="n">
         <v>526</v>
       </c>
@@ -34773,7 +34707,7 @@
       <c r="AE526" s="6"/>
       <c r="AF526" s="6"/>
     </row>
-    <row r="527" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="527" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="5" t="n">
         <v>531</v>
       </c>
@@ -34825,7 +34759,7 @@
       <c r="AE527" s="6"/>
       <c r="AF527" s="6"/>
     </row>
-    <row r="528" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="528" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="5" t="n">
         <v>532</v>
       </c>
@@ -35769,7 +35703,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="543" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="543" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="5" t="n">
         <v>549</v>
       </c>
@@ -35889,7 +35823,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="545" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="545" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="5" t="n">
         <v>551</v>
       </c>
@@ -36395,7 +36329,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="553" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="553" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="5" t="n">
         <v>559</v>
       </c>
@@ -36463,7 +36397,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="554" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="554" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A554" s="5" t="n">
         <v>560</v>
       </c>
@@ -36523,7 +36457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="555" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="555" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="5" t="n">
         <v>561</v>
       </c>
@@ -36589,7 +36523,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="556" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="556" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="5" t="n">
         <v>4097</v>
       </c>
@@ -36645,7 +36579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="557" s="5" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="557" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="5" t="n">
         <v>4098</v>
       </c>
@@ -37997,11 +37931,7 @@
       <c r="AF585" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AH585">
-    <sortState ref="A3:AH585">
-      <sortCondition ref="A3:A585"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A2:AH585"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/doc/equip/Equip.xlsx
+++ b/doc/equip/Equip.xlsx
@@ -2896,14 +2896,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AH585"/>
-  <sheetFormatPr defaultColWidth="5.27734375" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="5.1953125" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.81"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="5.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.81"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="32" min="6" style="1" width="5.28"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="33" style="2" width="5.28"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34.49"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="5.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.46"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="32" min="6" style="1" width="5.19"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="33" style="2" width="5.19"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3995,7 +3995,9 @@
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
       <c r="T17" s="6"/>
-      <c r="U17" s="6"/>
+      <c r="U17" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="V17" s="6"/>
       <c r="W17" s="5" t="n">
         <v>100</v>
@@ -6385,7 +6387,9 @@
       <c r="R60" s="6"/>
       <c r="S60" s="6"/>
       <c r="T60" s="6"/>
-      <c r="U60" s="6"/>
+      <c r="U60" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="V60" s="6"/>
       <c r="W60" s="5" t="n">
         <v>120</v>
@@ -8521,7 +8525,9 @@
       <c r="R96" s="6"/>
       <c r="S96" s="6"/>
       <c r="T96" s="6"/>
-      <c r="U96" s="6"/>
+      <c r="U96" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="V96" s="6"/>
       <c r="W96" s="5" t="n">
         <v>160</v>
@@ -10333,7 +10339,9 @@
       <c r="R126" s="6"/>
       <c r="S126" s="6"/>
       <c r="T126" s="6"/>
-      <c r="U126" s="6"/>
+      <c r="U126" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="V126" s="6"/>
       <c r="W126" s="5" t="n">
         <v>80</v>
@@ -10445,7 +10453,9 @@
       <c r="R128" s="6"/>
       <c r="S128" s="6"/>
       <c r="T128" s="6"/>
-      <c r="U128" s="6"/>
+      <c r="U128" s="6" t="n">
+        <v>16</v>
+      </c>
       <c r="V128" s="6"/>
       <c r="W128" s="5" t="n">
         <v>124</v>
@@ -13515,7 +13525,9 @@
       <c r="R180" s="6"/>
       <c r="S180" s="6"/>
       <c r="T180" s="6"/>
-      <c r="U180" s="6"/>
+      <c r="U180" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="V180" s="6"/>
       <c r="W180" s="5" t="n">
         <v>135</v>
@@ -15575,7 +15587,9 @@
       <c r="R214" s="6"/>
       <c r="S214" s="6"/>
       <c r="T214" s="6"/>
-      <c r="U214" s="6"/>
+      <c r="U214" s="6" t="n">
+        <v>16</v>
+      </c>
       <c r="V214" s="6"/>
       <c r="W214" s="5" t="n">
         <v>150</v>
@@ -15631,7 +15645,9 @@
       </c>
       <c r="S215" s="6"/>
       <c r="T215" s="6"/>
-      <c r="U215" s="6"/>
+      <c r="U215" s="6" t="n">
+        <v>20</v>
+      </c>
       <c r="V215" s="6"/>
       <c r="W215" s="5" t="n">
         <v>153</v>
@@ -19942,7 +19958,9 @@
       <c r="R286" s="6"/>
       <c r="S286" s="6"/>
       <c r="T286" s="6"/>
-      <c r="U286" s="6"/>
+      <c r="U286" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="V286" s="6"/>
       <c r="W286" s="5" t="n">
         <v>90</v>
@@ -19998,7 +20016,9 @@
       <c r="R287" s="6"/>
       <c r="S287" s="6"/>
       <c r="T287" s="6"/>
-      <c r="U287" s="6"/>
+      <c r="U287" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="V287" s="6"/>
       <c r="W287" s="5" t="n">
         <v>110</v>
@@ -25796,7 +25816,9 @@
       <c r="R381" s="6"/>
       <c r="S381" s="6"/>
       <c r="T381" s="6"/>
-      <c r="U381" s="6"/>
+      <c r="U381" s="6" t="n">
+        <v>20</v>
+      </c>
       <c r="V381" s="6"/>
       <c r="W381" s="5" t="n">
         <v>192</v>
@@ -29336,7 +29358,9 @@
       <c r="R438" s="6"/>
       <c r="S438" s="6"/>
       <c r="T438" s="6"/>
-      <c r="U438" s="6"/>
+      <c r="U438" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="V438" s="6"/>
       <c r="W438" s="5" t="n">
         <v>100</v>
@@ -29390,7 +29414,9 @@
       <c r="R439" s="6"/>
       <c r="S439" s="6"/>
       <c r="T439" s="6"/>
-      <c r="U439" s="6"/>
+      <c r="U439" s="6" t="n">
+        <v>20</v>
+      </c>
       <c r="V439" s="6"/>
       <c r="W439" s="5" t="n">
         <v>140</v>
@@ -29446,7 +29472,9 @@
       <c r="R440" s="6"/>
       <c r="S440" s="6"/>
       <c r="T440" s="6"/>
-      <c r="U440" s="6"/>
+      <c r="U440" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="V440" s="6"/>
       <c r="W440" s="5" t="n">
         <v>62</v>
@@ -29500,7 +29528,9 @@
       <c r="R441" s="6"/>
       <c r="S441" s="6"/>
       <c r="T441" s="6"/>
-      <c r="U441" s="6"/>
+      <c r="U441" s="6" t="n">
+        <v>20</v>
+      </c>
       <c r="V441" s="6"/>
       <c r="W441" s="5" t="n">
         <v>94</v>
@@ -30292,7 +30322,9 @@
       <c r="R454" s="6"/>
       <c r="S454" s="6"/>
       <c r="T454" s="6"/>
-      <c r="U454" s="6"/>
+      <c r="U454" s="6" t="n">
+        <v>20</v>
+      </c>
       <c r="V454" s="6"/>
       <c r="W454" s="5" t="n">
         <v>120</v>
@@ -30536,7 +30568,9 @@
       </c>
       <c r="S458" s="6"/>
       <c r="T458" s="6"/>
-      <c r="U458" s="6"/>
+      <c r="U458" s="6" t="n">
+        <v>24</v>
+      </c>
       <c r="V458" s="6"/>
       <c r="W458" s="5" t="n">
         <v>135</v>
@@ -33540,7 +33574,9 @@
       <c r="R507" s="6"/>
       <c r="S507" s="6"/>
       <c r="T507" s="6"/>
-      <c r="U507" s="6"/>
+      <c r="U507" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="V507" s="6"/>
       <c r="W507" s="5" t="n">
         <v>78</v>
@@ -33594,7 +33630,9 @@
       <c r="R508" s="6"/>
       <c r="S508" s="6"/>
       <c r="T508" s="6"/>
-      <c r="U508" s="6"/>
+      <c r="U508" s="6" t="n">
+        <v>20</v>
+      </c>
       <c r="V508" s="6"/>
       <c r="W508" s="5" t="n">
         <v>124</v>

--- a/doc/equip/Equip.xlsx
+++ b/doc/equip/Equip.xlsx
@@ -2896,14 +2896,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AH585"/>
-  <sheetFormatPr defaultColWidth="5.1953125" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="5.10546875" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34.49"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="5.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.46"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="32" min="6" style="1" width="5.19"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="33" style="2" width="5.19"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="33.93"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="5.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="32" min="6" style="1" width="5.11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="33" style="2" width="5.11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/doc/equip/Equip.xlsx
+++ b/doc/equip/Equip.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2399" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2399" uniqueCount="968">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -970,13 +970,16 @@
     <t xml:space="preserve">試製景雲(艦偵型)</t>
   </si>
   <si>
+    <t xml:space="preserve">Recon-jet</t>
+  </si>
+  <si>
     <t xml:space="preserve">零式艦戦52型(熟練)</t>
   </si>
   <si>
     <t xml:space="preserve">零戦52型丙(付岩井小隊)</t>
   </si>
   <si>
-    <t xml:space="preserve">零戦62型(爆戦/岩井隊)</t>
+    <t xml:space="preserve">零戦62型(爆戦／岩井隊)</t>
   </si>
   <si>
     <t xml:space="preserve">Bomb-dive-fight-n2</t>
@@ -2537,6 +2540,12 @@
   </si>
   <si>
     <t xml:space="preserve">Q734709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全翼型戦闘爆撃機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack-lb-fight-jet</t>
   </si>
   <si>
     <t xml:space="preserve">試製烈風 初期型</t>
@@ -2993,7 +3002,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3004,6 +3013,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -9214,7 +9227,7 @@
         <v>161</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>162</v>
+        <v>315</v>
       </c>
       <c r="F152" s="2" t="n">
         <v>1945</v>
@@ -9246,7 +9259,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>91</v>
@@ -9290,7 +9303,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>91</v>
@@ -9333,8 +9346,8 @@
       <c r="A155" s="2" t="n">
         <v>154</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>317</v>
+      <c r="B155" s="3" t="s">
+        <v>318</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>91</v>
@@ -9343,7 +9356,7 @@
         <v>96</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F155" s="2" t="n">
         <v>1946</v>
@@ -9384,7 +9397,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>91</v>
@@ -9428,7 +9441,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>91</v>
@@ -9472,7 +9485,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>91</v>
@@ -9516,10 +9529,10 @@
         <v>158</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>88</v>
@@ -9557,10 +9570,10 @@
         <v>159</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>88</v>
@@ -9595,7 +9608,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>66</v>
@@ -9639,10 +9652,10 @@
         <v>161</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>57</v>
@@ -9686,10 +9699,10 @@
         <v>162</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>49</v>
@@ -9733,10 +9746,10 @@
         <v>163</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>102</v>
@@ -9783,13 +9796,13 @@
         <v>164</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F165" s="2" t="n">
         <v>1937</v>
@@ -9821,13 +9834,13 @@
         <v>165</v>
       </c>
       <c r="B166" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E166" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>335</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>1942</v>
@@ -9859,7 +9872,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>182</v>
@@ -9888,16 +9901,16 @@
         <v>167</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F168" s="2" t="n">
         <v>1942</v>
@@ -9920,16 +9933,16 @@
         <v>168</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F169" s="2" t="n">
         <v>1936</v>
@@ -9967,16 +9980,16 @@
         <v>169</v>
       </c>
       <c r="B170" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E170" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="F170" s="2" t="n">
         <v>1941</v>
@@ -10011,16 +10024,16 @@
         <v>170</v>
       </c>
       <c r="B171" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C171" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C171" s="2" t="s">
-        <v>347</v>
-      </c>
       <c r="D171" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F171" s="2" t="n">
         <v>1944</v>
@@ -10061,10 +10074,10 @@
         <v>171</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>102</v>
@@ -10108,10 +10121,10 @@
         <v>172</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>66</v>
@@ -10158,10 +10171,10 @@
         <v>173</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>133</v>
@@ -10202,7 +10215,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>73</v>
@@ -10234,16 +10247,16 @@
         <v>175</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F176" s="2" t="n">
         <v>1943</v>
@@ -10272,16 +10285,16 @@
         <v>176</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F177" s="2" t="n">
         <v>1943</v>
@@ -10310,16 +10323,16 @@
         <v>177</v>
       </c>
       <c r="B178" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E178" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D178" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="E178" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="F178" s="2" t="n">
         <v>1943</v>
@@ -10351,10 +10364,10 @@
         <v>178</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>294</v>
@@ -10392,7 +10405,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>73</v>
@@ -10424,16 +10437,16 @@
         <v>180</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F181" s="2" t="n">
         <v>1943</v>
@@ -10468,7 +10481,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>91</v>
@@ -10503,7 +10516,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>91</v>
@@ -10547,10 +10560,10 @@
         <v>183</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>57</v>
@@ -10603,10 +10616,10 @@
         <v>184</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>88</v>
@@ -10644,16 +10657,16 @@
         <v>185</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F186" s="2" t="n">
         <v>1944</v>
@@ -10682,16 +10695,16 @@
         <v>186</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>1943</v>
@@ -10729,16 +10742,16 @@
         <v>187</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F188" s="2" t="n">
         <v>1944</v>
@@ -10779,16 +10792,16 @@
         <v>188</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>79</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F189" s="2" t="n">
         <v>1943</v>
@@ -10823,10 +10836,10 @@
         <v>189</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>88</v>
@@ -10861,10 +10874,10 @@
         <v>190</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>57</v>
@@ -10908,10 +10921,10 @@
         <v>191</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>133</v>
@@ -10943,10 +10956,10 @@
         <v>192</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>57</v>
@@ -10987,7 +11000,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>182</v>
@@ -11016,10 +11029,10 @@
         <v>194</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>106</v>
@@ -11069,10 +11082,10 @@
         <v>195</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>96</v>
@@ -11122,10 +11135,10 @@
         <v>196</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>79</v>
@@ -11169,10 +11182,10 @@
         <v>197</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>88</v>
@@ -11210,10 +11223,10 @@
         <v>198</v>
       </c>
       <c r="B199" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C199" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>88</v>
@@ -11254,13 +11267,13 @@
         <v>199</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F200" s="2" t="n">
         <v>1946</v>
@@ -11298,13 +11311,13 @@
         <v>200</v>
       </c>
       <c r="B201" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E201" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="F201" s="2" t="n">
         <v>1947</v>
@@ -11339,16 +11352,16 @@
         <v>201</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>164</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F202" s="2" t="n">
         <v>1943</v>
@@ -11383,16 +11396,16 @@
         <v>202</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>164</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F203" s="2" t="n">
         <v>1944</v>
@@ -11424,7 +11437,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>193</v>
@@ -11456,7 +11469,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>195</v>
@@ -11488,10 +11501,10 @@
         <v>205</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>88</v>
@@ -11532,10 +11545,10 @@
         <v>206</v>
       </c>
       <c r="B207" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C207" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>88</v>
@@ -11576,7 +11589,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>105</v>
@@ -11623,7 +11636,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>173</v>
@@ -11670,16 +11683,16 @@
         <v>209</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>160</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F210" s="2" t="n">
         <v>1944</v>
@@ -11699,13 +11712,13 @@
         <v>210</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F211" s="2" t="n">
         <v>1943</v>
@@ -11740,13 +11753,13 @@
         <v>211</v>
       </c>
       <c r="B212" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E212" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="D212" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>415</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>1944</v>
@@ -11778,7 +11791,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>160</v>
@@ -11816,7 +11829,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>228</v>
@@ -11848,7 +11861,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>228</v>
@@ -11883,13 +11896,13 @@
         <v>215</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F216" s="2" t="n">
         <v>1942</v>
@@ -11921,13 +11934,13 @@
         <v>216</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F217" s="2" t="n">
         <v>1942</v>
@@ -11962,13 +11975,13 @@
         <v>217</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F218" s="2" t="n">
         <v>1943</v>
@@ -11997,16 +12010,16 @@
         <v>218</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F219" s="2" t="n">
         <v>1944</v>
@@ -12035,7 +12048,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>91</v>
@@ -12073,7 +12086,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>180</v>
@@ -12123,16 +12136,16 @@
         <v>221</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F222" s="2" t="n">
         <v>1941</v>
@@ -12161,16 +12174,16 @@
         <v>222</v>
       </c>
       <c r="B223" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C223" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="C223" s="2" t="s">
-        <v>428</v>
-      </c>
       <c r="D223" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F223" s="2" t="n">
         <v>1944</v>
@@ -12202,16 +12215,16 @@
         <v>223</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F224" s="2" t="n">
         <v>1944</v>
@@ -12249,16 +12262,16 @@
         <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F225" s="2" t="n">
         <v>1945</v>
@@ -12296,16 +12309,16 @@
         <v>225</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F226" s="2" t="n">
         <v>1942</v>
@@ -12343,13 +12356,13 @@
         <v>226</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F227" s="2" t="n">
         <v>1937</v>
@@ -12372,13 +12385,13 @@
         <v>227</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F228" s="2" t="n">
         <v>1942</v>
@@ -12398,7 +12411,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>87</v>
@@ -12436,7 +12449,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>40</v>
@@ -12483,7 +12496,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>182</v>
@@ -12509,10 +12522,10 @@
         <v>231</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>57</v>
@@ -12559,10 +12572,10 @@
         <v>232</v>
       </c>
       <c r="B233" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C233" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>441</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>57</v>
@@ -12609,10 +12622,10 @@
         <v>233</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>96</v>
@@ -12659,7 +12672,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>52</v>
@@ -12706,7 +12719,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>52</v>
@@ -12756,7 +12769,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>60</v>
@@ -12803,7 +12816,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>105</v>
@@ -12853,7 +12866,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>101</v>
@@ -12897,7 +12910,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>101</v>
@@ -12944,7 +12957,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>109</v>
@@ -12979,7 +12992,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>305</v>
@@ -13008,16 +13021,16 @@
         <v>242</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>79</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F243" s="2" t="n">
         <v>1936</v>
@@ -13055,16 +13068,16 @@
         <v>243</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>79</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F244" s="2" t="n">
         <v>1943</v>
@@ -13102,16 +13115,16 @@
         <v>244</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>79</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F245" s="2" t="n">
         <v>1944</v>
@@ -13152,10 +13165,10 @@
         <v>245</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>57</v>
@@ -13199,10 +13212,10 @@
         <v>246</v>
       </c>
       <c r="B247" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C247" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>459</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>57</v>
@@ -13246,7 +13259,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>66</v>
@@ -13290,10 +13303,10 @@
         <v>248</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>96</v>
@@ -13334,10 +13347,10 @@
         <v>249</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>88</v>
@@ -13384,16 +13397,16 @@
         <v>250</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>1938</v>
@@ -13428,16 +13441,16 @@
         <v>251</v>
       </c>
       <c r="B252" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C252" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="C252" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="D252" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F252" s="2" t="n">
         <v>1941</v>
@@ -13469,10 +13482,10 @@
         <v>252</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>88</v>
@@ -13516,16 +13529,16 @@
         <v>253</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F254" s="2" t="n">
         <v>1943</v>
@@ -13560,16 +13573,16 @@
         <v>254</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>88</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F255" s="2" t="n">
         <v>1943</v>
@@ -13607,16 +13620,16 @@
         <v>255</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>88</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F256" s="2" t="n">
         <v>1945</v>
@@ -13654,10 +13667,10 @@
         <v>256</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>79</v>
@@ -13701,16 +13714,16 @@
         <v>257</v>
       </c>
       <c r="B258" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C258" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>476</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>79</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F258" s="2" t="n">
         <v>1946</v>
@@ -13754,7 +13767,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>247</v>
@@ -13792,7 +13805,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>247</v>
@@ -13836,7 +13849,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>149</v>
@@ -13874,7 +13887,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>149</v>
@@ -13909,7 +13922,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>149</v>
@@ -13944,16 +13957,16 @@
         <v>263</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>164</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F264" s="2" t="n">
         <v>1944</v>
@@ -13988,16 +14001,16 @@
         <v>264</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>164</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F265" s="2" t="n">
         <v>1944</v>
@@ -14032,16 +14045,16 @@
         <v>265</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>164</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F266" s="2" t="n">
         <v>1944</v>
@@ -14076,7 +14089,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>40</v>
@@ -14123,7 +14136,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>40</v>
@@ -14170,7 +14183,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>193</v>
@@ -14202,13 +14215,13 @@
         <v>269</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F270" s="2" t="n">
         <v>1944</v>
@@ -14237,13 +14250,13 @@
         <v>270</v>
       </c>
       <c r="B271" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E271" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="D271" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E271" s="2" t="s">
-        <v>491</v>
       </c>
       <c r="F271" s="2" t="n">
         <v>1945</v>
@@ -14278,7 +14291,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>88</v>
@@ -14316,7 +14329,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>244</v>
@@ -14351,7 +14364,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>161</v>
@@ -14386,7 +14399,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>133</v>
@@ -14421,7 +14434,7 @@
         <v>275</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>66</v>
@@ -14471,7 +14484,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>57</v>
@@ -14515,7 +14528,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>96</v>
@@ -14565,7 +14578,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>115</v>
@@ -14603,7 +14616,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>115</v>
@@ -14647,7 +14660,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>40</v>
@@ -14697,7 +14710,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>57</v>
@@ -14744,7 +14757,7 @@
         <v>282</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>40</v>
@@ -14788,7 +14801,7 @@
         <v>283</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>73</v>
@@ -14823,7 +14836,7 @@
         <v>284</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>40</v>
@@ -14870,7 +14883,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>73</v>
@@ -14908,7 +14921,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>73</v>
@@ -14946,7 +14959,7 @@
         <v>287</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>145</v>
@@ -14972,7 +14985,7 @@
         <v>288</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>145</v>
@@ -15004,7 +15017,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>57</v>
@@ -15051,7 +15064,7 @@
         <v>290</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>57</v>
@@ -15095,7 +15108,7 @@
         <v>291</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>96</v>
@@ -15139,7 +15152,7 @@
         <v>292</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>96</v>
@@ -15189,7 +15202,7 @@
         <v>293</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>40</v>
@@ -15233,7 +15246,7 @@
         <v>294</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>40</v>
@@ -15280,7 +15293,7 @@
         <v>295</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>40</v>
@@ -15330,7 +15343,7 @@
         <v>296</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>40</v>
@@ -15380,7 +15393,7 @@
         <v>297</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>40</v>
@@ -15424,7 +15437,7 @@
         <v>298</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>57</v>
@@ -15465,7 +15478,7 @@
         <v>299</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>57</v>
@@ -15509,7 +15522,7 @@
         <v>300</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>57</v>
@@ -15559,7 +15572,7 @@
         <v>301</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>133</v>
@@ -15588,7 +15601,7 @@
         <v>302</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>79</v>
@@ -15635,7 +15648,7 @@
         <v>303</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>49</v>
@@ -15682,7 +15695,7 @@
         <v>304</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>102</v>
@@ -15723,7 +15736,7 @@
         <v>305</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D306" s="2" t="s">
         <v>96</v>
@@ -15767,7 +15780,7 @@
         <v>306</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>96</v>
@@ -15817,13 +15830,13 @@
         <v>307</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>109</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F308" s="2" t="n">
         <v>1943</v>
@@ -15864,7 +15877,7 @@
         <v>308</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>40</v>
@@ -15914,7 +15927,7 @@
         <v>309</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D310" s="2" t="s">
         <v>139</v>
@@ -15946,7 +15959,7 @@
         <v>310</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D311" s="2" t="s">
         <v>49</v>
@@ -15993,13 +16006,13 @@
         <v>311</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>1942</v>
@@ -16031,13 +16044,13 @@
         <v>312</v>
       </c>
       <c r="B313" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D313" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E313" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="D313" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="E313" s="2" t="s">
-        <v>536</v>
       </c>
       <c r="F313" s="2" t="n">
         <v>1942</v>
@@ -16072,7 +16085,7 @@
         <v>313</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D314" s="2" t="s">
         <v>40</v>
@@ -16116,7 +16129,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D315" s="2" t="s">
         <v>73</v>
@@ -16157,13 +16170,13 @@
         <v>315</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>109</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F316" s="2" t="n">
         <v>1942</v>
@@ -16204,7 +16217,7 @@
         <v>316</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D317" s="2" t="s">
         <v>96</v>
@@ -16248,7 +16261,7 @@
         <v>317</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>127</v>
@@ -16283,7 +16296,7 @@
         <v>318</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>57</v>
@@ -16330,7 +16343,7 @@
         <v>319</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>96</v>
@@ -16377,13 +16390,13 @@
         <v>320</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>96</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F321" s="2" t="n">
         <v>1945</v>
@@ -16418,7 +16431,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>106</v>
@@ -16468,7 +16481,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>106</v>
@@ -16518,7 +16531,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>186</v>
@@ -16553,7 +16566,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D325" s="2" t="s">
         <v>186</v>
@@ -16591,7 +16604,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D326" s="2" t="s">
         <v>186</v>
@@ -16632,7 +16645,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D327" s="2" t="s">
         <v>186</v>
@@ -16670,7 +16683,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>57</v>
@@ -16717,7 +16730,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D329" s="2" t="s">
         <v>57</v>
@@ -16764,7 +16777,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>57</v>
@@ -16808,7 +16821,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>57</v>
@@ -16855,7 +16868,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D332" s="2" t="s">
         <v>57</v>
@@ -16902,13 +16915,13 @@
         <v>333</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F333" s="2" t="n">
         <v>1945</v>
@@ -16940,13 +16953,13 @@
         <v>334</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F334" s="2" t="n">
         <v>1945</v>
@@ -16981,7 +16994,7 @@
         <v>336</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>88</v>
@@ -17019,13 +17032,13 @@
         <v>338</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>88</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F336" s="2" t="n">
         <v>1948</v>
@@ -17066,13 +17079,13 @@
         <v>339</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D337" s="2" t="s">
         <v>88</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F337" s="2" t="n">
         <v>1948</v>
@@ -17113,7 +17126,7 @@
         <v>340</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>49</v>
@@ -17160,7 +17173,7 @@
         <v>341</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D339" s="2" t="s">
         <v>49</v>
@@ -17207,7 +17220,7 @@
         <v>342</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>84</v>
@@ -17257,7 +17270,7 @@
         <v>343</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>84</v>
@@ -17310,7 +17323,7 @@
         <v>344</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>78</v>
@@ -17319,7 +17332,7 @@
         <v>79</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F342" s="2" t="n">
         <v>1943</v>
@@ -17357,7 +17370,7 @@
         <v>345</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>78</v>
@@ -17366,7 +17379,7 @@
         <v>79</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F343" s="2" t="n">
         <v>1944</v>
@@ -17404,7 +17417,7 @@
         <v>346</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>145</v>
@@ -17436,7 +17449,7 @@
         <v>347</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>145</v>
@@ -17468,7 +17481,7 @@
         <v>348</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>272</v>
@@ -17500,7 +17513,7 @@
         <v>349</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D347" s="2" t="s">
         <v>272</v>
@@ -17532,16 +17545,16 @@
         <v>350</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F348" s="2" t="n">
         <v>1942</v>
@@ -17570,16 +17583,16 @@
         <v>351</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F349" s="2" t="n">
         <v>1945</v>
@@ -17605,16 +17618,16 @@
         <v>352</v>
       </c>
       <c r="B350" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="C350" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="C350" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="D350" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F350" s="2" t="n">
         <v>1947</v>
@@ -17640,10 +17653,10 @@
         <v>353</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D351" s="2" t="s">
         <v>88</v>
@@ -17684,16 +17697,16 @@
         <v>354</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F352" s="2" t="n">
         <v>1944</v>
@@ -17728,10 +17741,10 @@
         <v>355</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D353" s="2" t="s">
         <v>182</v>
@@ -17766,10 +17779,10 @@
         <v>356</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D354" s="2" t="s">
         <v>49</v>
@@ -17813,10 +17826,10 @@
         <v>357</v>
       </c>
       <c r="B355" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C355" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="C355" s="2" t="s">
-        <v>583</v>
       </c>
       <c r="D355" s="2" t="s">
         <v>49</v>
@@ -17860,10 +17873,10 @@
         <v>358</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D356" s="2" t="s">
         <v>66</v>
@@ -17910,10 +17923,10 @@
         <v>359</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D357" s="2" t="s">
         <v>49</v>
@@ -17963,10 +17976,10 @@
         <v>360</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D358" s="2" t="s">
         <v>49</v>
@@ -18013,10 +18026,10 @@
         <v>361</v>
       </c>
       <c r="B359" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="C359" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="C359" s="2" t="s">
-        <v>589</v>
       </c>
       <c r="D359" s="2" t="s">
         <v>49</v>
@@ -18063,16 +18076,16 @@
         <v>362</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D360" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F360" s="2" t="n">
         <v>1934</v>
@@ -18113,16 +18126,16 @@
         <v>363</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D361" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F361" s="2" t="n">
         <v>1943</v>
@@ -18166,7 +18179,7 @@
         <v>364</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>139</v>
@@ -18198,7 +18211,7 @@
         <v>365</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D363" s="2" t="s">
         <v>130</v>
@@ -18230,7 +18243,7 @@
         <v>366</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D364" s="2" t="s">
         <v>40</v>
@@ -18280,10 +18293,10 @@
         <v>367</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D365" s="2" t="s">
         <v>106</v>
@@ -18330,10 +18343,10 @@
         <v>368</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>106</v>
@@ -18377,10 +18390,10 @@
         <v>369</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D367" s="2" t="s">
         <v>106</v>
@@ -18427,10 +18440,10 @@
         <v>370</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D368" s="2" t="s">
         <v>102</v>
@@ -18468,10 +18481,10 @@
         <v>371</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D369" s="2" t="s">
         <v>102</v>
@@ -18515,7 +18528,7 @@
         <v>372</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>82</v>
@@ -18559,7 +18572,7 @@
         <v>373</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>82</v>
@@ -18568,7 +18581,7 @@
         <v>79</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F371" s="2" t="n">
         <v>1945</v>
@@ -18609,7 +18622,7 @@
         <v>374</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>82</v>
@@ -18618,7 +18631,7 @@
         <v>79</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F372" s="2" t="n">
         <v>1945</v>
@@ -18662,10 +18675,10 @@
         <v>375</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D373" s="2" t="s">
         <v>88</v>
@@ -18700,7 +18713,7 @@
         <v>376</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D374" s="2" t="s">
         <v>73</v>
@@ -18741,10 +18754,10 @@
         <v>377</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D375" s="2" t="s">
         <v>145</v>
@@ -18782,13 +18795,13 @@
         <v>378</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D376" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F376" s="2" t="n">
         <v>1956</v>
@@ -18811,7 +18824,7 @@
         <v>379</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D377" s="2" t="s">
         <v>40</v>
@@ -18858,7 +18871,7 @@
         <v>380</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>65</v>
@@ -18908,10 +18921,10 @@
         <v>381</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D379" s="2" t="s">
         <v>57</v>
@@ -18955,7 +18968,7 @@
         <v>382</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>39</v>
@@ -19008,7 +19021,7 @@
         <v>383</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D381" s="2" t="s">
         <v>228</v>
@@ -19040,13 +19053,13 @@
         <v>384</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F382" s="2" t="n">
         <v>1945</v>
@@ -19081,10 +19094,10 @@
         <v>385</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D383" s="2" t="s">
         <v>57</v>
@@ -19128,10 +19141,10 @@
         <v>386</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D384" s="2" t="s">
         <v>49</v>
@@ -19178,10 +19191,10 @@
         <v>387</v>
       </c>
       <c r="B385" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="C385" s="2" t="s">
         <v>622</v>
-      </c>
-      <c r="C385" s="2" t="s">
-        <v>621</v>
       </c>
       <c r="D385" s="2" t="s">
         <v>49</v>
@@ -19228,16 +19241,16 @@
         <v>388</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F386" s="2" t="n">
         <v>1944</v>
@@ -19278,16 +19291,16 @@
         <v>389</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D387" s="2" t="s">
         <v>79</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F387" s="2" t="n">
         <v>1947</v>
@@ -19334,10 +19347,10 @@
         <v>390</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D388" s="2" t="s">
         <v>57</v>
@@ -19390,7 +19403,7 @@
         <v>391</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>95</v>
@@ -19434,7 +19447,7 @@
         <v>392</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>95</v>
@@ -19487,7 +19500,7 @@
         <v>393</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D391" s="2" t="s">
         <v>40</v>
@@ -19531,7 +19544,7 @@
         <v>394</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D392" s="2" t="s">
         <v>40</v>
@@ -19575,16 +19588,16 @@
         <v>395</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F393" s="2" t="n">
         <v>1943</v>
@@ -19616,16 +19629,16 @@
         <v>396</v>
       </c>
       <c r="B394" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C394" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="D394" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E394" s="2" t="s">
         <v>634</v>
-      </c>
-      <c r="C394" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="D394" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="E394" s="2" t="s">
-        <v>633</v>
       </c>
       <c r="F394" s="2" t="n">
         <v>1946</v>
@@ -19654,7 +19667,7 @@
         <v>397</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D395" s="2" t="s">
         <v>40</v>
@@ -19698,7 +19711,7 @@
         <v>398</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D396" s="2" t="s">
         <v>40</v>
@@ -19742,10 +19755,10 @@
         <v>399</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D397" s="2" t="s">
         <v>49</v>
@@ -19792,7 +19805,7 @@
         <v>400</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D398" s="2" t="s">
         <v>73</v>
@@ -19827,16 +19840,16 @@
         <v>401</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F399" s="2" t="n">
         <v>1934</v>
@@ -19871,7 +19884,7 @@
         <v>402</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D400" s="2" t="s">
         <v>247</v>
@@ -19897,16 +19910,16 @@
         <v>403</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F401" s="2" t="n">
         <v>1944</v>
@@ -19947,16 +19960,16 @@
         <v>404</v>
       </c>
       <c r="B402" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="C402" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="C402" s="2" t="s">
-        <v>643</v>
-      </c>
       <c r="D402" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F402" s="2" t="n">
         <v>1944</v>
@@ -19997,16 +20010,16 @@
         <v>405</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F403" s="2" t="n">
         <v>1940</v>
@@ -20041,16 +20054,16 @@
         <v>406</v>
       </c>
       <c r="B404" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="C404" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="C404" s="2" t="s">
-        <v>646</v>
-      </c>
       <c r="D404" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F404" s="2" t="n">
         <v>1943</v>
@@ -20085,7 +20098,7 @@
         <v>407</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D405" s="2" t="s">
         <v>49</v>
@@ -20132,7 +20145,7 @@
         <v>408</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D406" s="2" t="s">
         <v>182</v>
@@ -20173,7 +20186,7 @@
         <v>409</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D407" s="2" t="s">
         <v>182</v>
@@ -20211,7 +20224,7 @@
         <v>410</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D408" s="2" t="s">
         <v>115</v>
@@ -20246,7 +20259,7 @@
         <v>411</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D409" s="2" t="s">
         <v>115</v>
@@ -20281,7 +20294,7 @@
         <v>412</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D410" s="2" t="s">
         <v>278</v>
@@ -20325,7 +20338,7 @@
         <v>413</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D411" s="2" t="s">
         <v>244</v>
@@ -20357,10 +20370,10 @@
         <v>414</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D412" s="2" t="s">
         <v>102</v>
@@ -20401,10 +20414,10 @@
         <v>415</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D413" s="2" t="s">
         <v>102</v>
@@ -20442,16 +20455,16 @@
         <v>416</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C414" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F414" s="2" t="n">
         <v>1941</v>
@@ -20486,16 +20499,16 @@
         <v>417</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C415" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F415" s="2" t="n">
         <v>1942</v>
@@ -20530,16 +20543,16 @@
         <v>418</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C416" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F416" s="2" t="n">
         <v>1942</v>
@@ -20574,10 +20587,10 @@
         <v>419</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D417" s="2" t="s">
         <v>96</v>
@@ -20624,10 +20637,10 @@
         <v>420</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D418" s="2" t="s">
         <v>96</v>
@@ -20677,10 +20690,10 @@
         <v>421</v>
       </c>
       <c r="B419" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C419" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="C419" s="2" t="s">
-        <v>664</v>
       </c>
       <c r="D419" s="2" t="s">
         <v>96</v>
@@ -20730,10 +20743,10 @@
         <v>422</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D420" s="2" t="s">
         <v>88</v>
@@ -20774,16 +20787,16 @@
         <v>423</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D421" s="2" t="s">
         <v>161</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F421" s="2" t="n">
         <v>1940</v>
@@ -20821,10 +20834,10 @@
         <v>424</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D422" s="2" t="s">
         <v>79</v>
@@ -20868,10 +20881,10 @@
         <v>425</v>
       </c>
       <c r="B423" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="C423" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="C423" s="2" t="s">
-        <v>671</v>
       </c>
       <c r="D423" s="2" t="s">
         <v>79</v>
@@ -20912,10 +20925,10 @@
         <v>426</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D424" s="2" t="s">
         <v>57</v>
@@ -20962,10 +20975,10 @@
         <v>427</v>
       </c>
       <c r="B425" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="C425" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="C425" s="2" t="s">
-        <v>674</v>
       </c>
       <c r="D425" s="2" t="s">
         <v>57</v>
@@ -21009,10 +21022,10 @@
         <v>428</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D426" s="2" t="s">
         <v>57</v>
@@ -21056,10 +21069,10 @@
         <v>429</v>
       </c>
       <c r="B427" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="C427" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="C427" s="2" t="s">
-        <v>677</v>
       </c>
       <c r="D427" s="2" t="s">
         <v>57</v>
@@ -21103,7 +21116,7 @@
         <v>430</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D428" s="2" t="s">
         <v>66</v>
@@ -21150,16 +21163,16 @@
         <v>431</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F429" s="2" t="n">
         <v>1937</v>
@@ -21197,16 +21210,16 @@
         <v>432</v>
       </c>
       <c r="B430" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="C430" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="C430" s="2" t="s">
-        <v>681</v>
-      </c>
       <c r="D430" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F430" s="2" t="n">
         <v>1942</v>
@@ -21241,16 +21254,16 @@
         <v>433</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F431" s="2" t="n">
         <v>1942</v>
@@ -21291,10 +21304,10 @@
         <v>434</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D432" s="2" t="s">
         <v>88</v>
@@ -21332,10 +21345,10 @@
         <v>435</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D433" s="2" t="s">
         <v>88</v>
@@ -21379,7 +21392,7 @@
         <v>436</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D434" s="2" t="s">
         <v>182</v>
@@ -21414,7 +21427,7 @@
         <v>437</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D435" s="2" t="s">
         <v>88</v>
@@ -21449,7 +21462,7 @@
         <v>438</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D436" s="2" t="s">
         <v>149</v>
@@ -21487,16 +21500,16 @@
         <v>439</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D437" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E437" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F437" s="2" t="n">
         <v>1942</v>
@@ -21525,7 +21538,7 @@
         <v>440</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D438" s="2" t="s">
         <v>228</v>
@@ -21557,7 +21570,7 @@
         <v>441</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D439" s="2" t="s">
         <v>228</v>
@@ -21589,7 +21602,7 @@
         <v>442</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D440" s="2" t="s">
         <v>228</v>
@@ -21624,7 +21637,7 @@
         <v>443</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D441" s="2" t="s">
         <v>228</v>
@@ -21656,16 +21669,16 @@
         <v>444</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F442" s="2" t="n">
         <v>1946</v>
@@ -21706,16 +21719,16 @@
         <v>445</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F443" s="2" t="n">
         <v>1942</v>
@@ -21750,16 +21763,16 @@
         <v>446</v>
       </c>
       <c r="B444" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="C444" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="C444" s="2" t="s">
-        <v>697</v>
-      </c>
       <c r="D444" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F444" s="2" t="n">
         <v>1943</v>
@@ -21791,7 +21804,7 @@
         <v>447</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C445" s="2" t="s">
         <v>91</v>
@@ -21835,7 +21848,7 @@
         <v>449</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D446" s="2" t="s">
         <v>182</v>
@@ -21864,13 +21877,13 @@
         <v>450</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D447" s="2" t="s">
         <v>109</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F447" s="2" t="n">
         <v>1945</v>
@@ -21899,7 +21912,7 @@
         <v>451</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C448" s="2" t="s">
         <v>189</v>
@@ -21940,16 +21953,16 @@
         <v>452</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E449" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F449" s="2" t="n">
         <v>1944</v>
@@ -21981,16 +21994,16 @@
         <v>453</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E450" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F450" s="2" t="n">
         <v>1944</v>
@@ -22031,16 +22044,16 @@
         <v>454</v>
       </c>
       <c r="B451" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="C451" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="C451" s="2" t="s">
-        <v>706</v>
-      </c>
       <c r="D451" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E451" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F451" s="2" t="n">
         <v>1946</v>
@@ -22084,7 +22097,7 @@
         <v>455</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D452" s="2" t="s">
         <v>40</v>
@@ -22125,13 +22138,13 @@
         <v>456</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D453" s="2" t="s">
         <v>109</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F453" s="2" t="n">
         <v>1944</v>
@@ -22172,7 +22185,7 @@
         <v>457</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D454" s="2" t="s">
         <v>228</v>
@@ -22207,13 +22220,13 @@
         <v>458</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E455" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F455" s="2" t="n">
         <v>1945</v>
@@ -22248,16 +22261,16 @@
         <v>459</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F456" s="2" t="n">
         <v>1941</v>
@@ -22295,7 +22308,7 @@
         <v>460</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D457" s="2" t="s">
         <v>115</v>
@@ -22339,7 +22352,7 @@
         <v>461</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D458" s="2" t="s">
         <v>228</v>
@@ -22377,7 +22390,7 @@
         <v>463</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C459" s="2" t="s">
         <v>52</v>
@@ -22427,13 +22440,13 @@
         <v>464</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D460" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="F460" s="2" t="n">
         <v>1943</v>
@@ -22474,7 +22487,7 @@
         <v>465</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D461" s="2" t="s">
         <v>57</v>
@@ -22521,7 +22534,7 @@
         <v>466</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>84</v>
@@ -22574,16 +22587,16 @@
         <v>467</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D463" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="F463" s="2" t="n">
         <v>1940</v>
@@ -22621,10 +22634,10 @@
         <v>468</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D464" s="2" t="s">
         <v>57</v>
@@ -22668,7 +22681,7 @@
         <v>469</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C465" s="2" t="s">
         <v>101</v>
@@ -22712,7 +22725,7 @@
         <v>470</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D466" s="2" t="s">
         <v>40</v>
@@ -22762,10 +22775,10 @@
         <v>471</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D467" s="2" t="s">
         <v>102</v>
@@ -22803,7 +22816,7 @@
         <v>472</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D468" s="2" t="s">
         <v>145</v>
@@ -22838,16 +22851,16 @@
         <v>473</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D469" s="2" t="s">
         <v>88</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F469" s="2" t="n">
         <v>1944</v>
@@ -22885,10 +22898,10 @@
         <v>474</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D470" s="2" t="s">
         <v>96</v>
@@ -22935,16 +22948,16 @@
         <v>475</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D471" s="2" t="s">
         <v>96</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="F471" s="2" t="n">
         <v>1945</v>
@@ -22988,16 +23001,16 @@
         <v>476</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D472" s="2" t="s">
         <v>96</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="F472" s="2" t="n">
         <v>1945</v>
@@ -23041,7 +23054,7 @@
         <v>477</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D473" s="2" t="s">
         <v>247</v>
@@ -23091,7 +23104,7 @@
         <v>478</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D474" s="2" t="s">
         <v>247</v>
@@ -23150,16 +23163,16 @@
         <v>479</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D475" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F475" s="2" t="n">
         <v>1941</v>
@@ -23200,16 +23213,16 @@
         <v>480</v>
       </c>
       <c r="B476" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="C476" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="C476" s="2" t="s">
-        <v>736</v>
-      </c>
       <c r="D476" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F476" s="2" t="n">
         <v>1941</v>
@@ -23238,16 +23251,16 @@
         <v>481</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D477" s="2" t="s">
         <v>79</v>
       </c>
       <c r="E477" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F477" s="2" t="n">
         <v>1941</v>
@@ -23288,7 +23301,7 @@
         <v>482</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D478" s="2" t="s">
         <v>182</v>
@@ -23323,7 +23336,7 @@
         <v>483</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D479" s="2" t="s">
         <v>127</v>
@@ -23361,16 +23374,16 @@
         <v>484</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F480" s="2" t="n">
         <v>1946</v>
@@ -23411,13 +23424,13 @@
         <v>485</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F481" s="2" t="n">
         <v>1946</v>
@@ -23446,7 +23459,7 @@
         <v>486</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C482" s="2" t="s">
         <v>91</v>
@@ -23490,7 +23503,7 @@
         <v>487</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C483" s="2" t="s">
         <v>91</v>
@@ -23540,13 +23553,13 @@
         <v>488</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D484" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F484" s="2" t="n">
         <v>1944</v>
@@ -23575,16 +23588,16 @@
         <v>489</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D485" s="2" t="s">
         <v>190</v>
       </c>
       <c r="E485" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F485" s="2" t="n">
         <v>1943</v>
@@ -23619,7 +23632,7 @@
         <v>490</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C486" s="2" t="s">
         <v>105</v>
@@ -23628,7 +23641,7 @@
         <v>106</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F486" s="2" t="n">
         <v>1948</v>
@@ -23666,16 +23679,16 @@
         <v>491</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D487" s="2" t="s">
         <v>190</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F487" s="2" t="n">
         <v>1945</v>
@@ -23716,7 +23729,7 @@
         <v>492</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C488" s="2" t="s">
         <v>91</v>
@@ -23760,16 +23773,16 @@
         <v>493</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F489" s="2" t="n">
         <v>1944</v>
@@ -23810,7 +23823,7 @@
         <v>494</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D490" s="2" t="s">
         <v>182</v>
@@ -23839,7 +23852,7 @@
         <v>495</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D491" s="2" t="s">
         <v>182</v>
@@ -23871,13 +23884,13 @@
         <v>496</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="F492" s="2" t="n">
         <v>1931</v>
@@ -23897,16 +23910,16 @@
         <v>497</v>
       </c>
       <c r="B493" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="C493" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="D493" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="E493" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="C493" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="D493" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="E493" s="2" t="s">
-        <v>757</v>
       </c>
       <c r="F493" s="2" t="n">
         <v>1938</v>
@@ -23929,16 +23942,16 @@
         <v>498</v>
       </c>
       <c r="B494" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="C494" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="C494" s="2" t="s">
-        <v>759</v>
-      </c>
       <c r="D494" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="F494" s="2" t="n">
         <v>1941</v>
@@ -23958,13 +23971,13 @@
         <v>499</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="F495" s="2" t="n">
         <v>1941</v>
@@ -23987,13 +24000,13 @@
         <v>500</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F496" s="2" t="n">
         <v>1934</v>
@@ -24016,13 +24029,13 @@
         <v>501</v>
       </c>
       <c r="B497" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="D497" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="E497" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="D497" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="E497" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="F497" s="2" t="n">
         <v>1941</v>
@@ -24045,7 +24058,7 @@
         <v>502</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D498" s="2" t="s">
         <v>57</v>
@@ -24095,7 +24108,7 @@
         <v>503</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D499" s="2" t="s">
         <v>57</v>
@@ -24142,16 +24155,16 @@
         <v>504</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E500" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F500" s="2" t="n">
         <v>1945</v>
@@ -24192,7 +24205,7 @@
         <v>505</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D501" s="2" t="s">
         <v>133</v>
@@ -24221,13 +24234,13 @@
         <v>506</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D502" s="2" t="s">
         <v>109</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F502" s="2" t="n">
         <v>1945</v>
@@ -24262,10 +24275,10 @@
         <v>507</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D503" s="2" t="s">
         <v>57</v>
@@ -24312,10 +24325,10 @@
         <v>508</v>
       </c>
       <c r="B504" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="C504" s="2" t="s">
         <v>773</v>
-      </c>
-      <c r="C504" s="2" t="s">
-        <v>772</v>
       </c>
       <c r="D504" s="2" t="s">
         <v>57</v>
@@ -24356,7 +24369,7 @@
         <v>509</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>39</v>
@@ -24409,10 +24422,10 @@
         <v>510</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D506" s="2" t="s">
         <v>102</v>
@@ -24450,7 +24463,7 @@
         <v>511</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D507" s="2" t="s">
         <v>228</v>
@@ -24482,7 +24495,7 @@
         <v>512</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D508" s="2" t="s">
         <v>228</v>
@@ -24514,13 +24527,13 @@
         <v>513</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D509" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F509" s="2" t="n">
         <v>1914</v>
@@ -24540,7 +24553,7 @@
         <v>514</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D510" s="2" t="s">
         <v>182</v>
@@ -24575,10 +24588,10 @@
         <v>515</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D511" s="2" t="s">
         <v>102</v>
@@ -24613,16 +24626,16 @@
         <v>516</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D512" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F512" s="2" t="n">
         <v>1944</v>
@@ -24657,7 +24670,7 @@
         <v>517</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D513" s="2" t="s">
         <v>109</v>
@@ -24695,7 +24708,7 @@
         <v>518</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>48</v>
@@ -24742,13 +24755,13 @@
         <v>519</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D515" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F515" s="2" t="n">
         <v>1941</v>
@@ -24780,7 +24793,7 @@
         <v>520</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>54</v>
@@ -24827,7 +24840,7 @@
         <v>521</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D517" s="2" t="s">
         <v>102</v>
@@ -24871,7 +24884,7 @@
         <v>522</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>101</v>
@@ -24880,7 +24893,7 @@
         <v>102</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="F518" s="2" t="n">
         <v>1938</v>
@@ -24918,7 +24931,7 @@
         <v>523</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>101</v>
@@ -24927,7 +24940,7 @@
         <v>102</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="F519" s="2" t="n">
         <v>1938</v>
@@ -24965,7 +24978,7 @@
         <v>524</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D520" s="2" t="s">
         <v>66</v>
@@ -25015,16 +25028,16 @@
         <v>525</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C521" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D521" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F521" s="2" t="n">
         <v>1944</v>
@@ -25053,16 +25066,16 @@
         <v>526</v>
       </c>
       <c r="B522" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="C522" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="C522" s="2" t="s">
-        <v>797</v>
-      </c>
       <c r="D522" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F522" s="2" t="n">
         <v>1946</v>
@@ -25094,10 +25107,10 @@
         <v>527</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D523" s="2" t="s">
         <v>115</v>
@@ -25135,7 +25148,7 @@
         <v>528</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D524" s="2" t="s">
         <v>115</v>
@@ -25182,7 +25195,7 @@
         <v>529</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D525" s="2" t="s">
         <v>40</v>
@@ -25232,7 +25245,7 @@
         <v>530</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D526" s="2" t="s">
         <v>57</v>
@@ -25279,7 +25292,7 @@
         <v>531</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D527" s="2" t="s">
         <v>244</v>
@@ -25308,7 +25321,7 @@
         <v>532</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D528" s="2" t="s">
         <v>244</v>
@@ -25334,7 +25347,7 @@
         <v>533</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>45</v>
@@ -25384,10 +25397,10 @@
         <v>534</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D530" s="2" t="s">
         <v>40</v>
@@ -25431,10 +25444,10 @@
         <v>535</v>
       </c>
       <c r="B531" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C531" s="2" t="s">
         <v>809</v>
-      </c>
-      <c r="C531" s="2" t="s">
-        <v>808</v>
       </c>
       <c r="D531" s="2" t="s">
         <v>40</v>
@@ -25475,7 +25488,7 @@
         <v>536</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D532" s="2" t="s">
         <v>49</v>
@@ -25522,7 +25535,7 @@
         <v>537</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D533" s="2" t="s">
         <v>49</v>
@@ -25566,10 +25579,10 @@
         <v>538</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D534" s="2" t="s">
         <v>102</v>
@@ -25613,10 +25626,10 @@
         <v>539</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D535" s="2" t="s">
         <v>102</v>
@@ -25660,7 +25673,7 @@
         <v>540</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C536" s="2" t="s">
         <v>101</v>
@@ -25704,10 +25717,10 @@
         <v>541</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D537" s="2" t="s">
         <v>96</v>
@@ -25754,10 +25767,10 @@
         <v>542</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D538" s="2" t="s">
         <v>79</v>
@@ -25798,10 +25811,10 @@
         <v>543</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D539" s="2" t="s">
         <v>161</v>
@@ -25848,10 +25861,10 @@
         <v>544</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D540" s="2" t="s">
         <v>96</v>
@@ -25901,7 +25914,7 @@
         <v>545</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>82</v>
@@ -25910,7 +25923,7 @@
         <v>79</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F541" s="2" t="n">
         <v>1948</v>
@@ -25954,13 +25967,13 @@
         <v>546</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D542" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F542" s="2" t="n">
         <v>1948</v>
@@ -25989,7 +26002,7 @@
         <v>549</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>189</v>
@@ -26033,7 +26046,7 @@
         <v>550</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D544" s="2" t="s">
         <v>96</v>
@@ -26071,7 +26084,7 @@
         <v>551</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D545" s="2" t="s">
         <v>96</v>
@@ -26109,7 +26122,7 @@
         <v>552</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C546" s="2" t="s">
         <v>95</v>
@@ -26118,7 +26131,7 @@
         <v>96</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="F546" s="2" t="n">
         <v>1948</v>
@@ -26156,7 +26169,7 @@
         <v>553</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>45</v>
@@ -26206,7 +26219,7 @@
         <v>554</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C548" s="2" t="s">
         <v>78</v>
@@ -26247,10 +26260,10 @@
         <v>555</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D549" s="2" t="s">
         <v>49</v>
@@ -26297,7 +26310,7 @@
         <v>556</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D550" s="2" t="s">
         <v>66</v>
@@ -26344,7 +26357,7 @@
         <v>557</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>91</v>
@@ -26353,7 +26366,7 @@
         <v>96</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="F551" s="2" t="n">
         <v>1948</v>
@@ -26391,7 +26404,7 @@
         <v>558</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C552" s="2" t="s">
         <v>91</v>
@@ -26400,7 +26413,7 @@
         <v>96</v>
       </c>
       <c r="E552" s="2" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="F552" s="2" t="n">
         <v>1950</v>
@@ -26438,7 +26451,7 @@
         <v>559</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>177</v>
@@ -26491,10 +26504,10 @@
         <v>560</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C554" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D554" s="2" t="s">
         <v>88</v>
@@ -26532,16 +26545,16 @@
         <v>561</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C555" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="D555" s="2" t="s">
-        <v>398</v>
+        <v>838</v>
+      </c>
+      <c r="D555" s="3" t="s">
+        <v>839</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>399</v>
+        <v>840</v>
       </c>
       <c r="F555" s="2" t="n">
         <v>1945</v>
@@ -26582,7 +26595,7 @@
         <v>4097</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D556" s="2" t="s">
         <v>88</v>
@@ -26617,7 +26630,7 @@
         <v>4098</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="D557" s="2" t="s">
         <v>244</v>
@@ -26643,7 +26656,7 @@
         <v>4099</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="D558" s="2" t="s">
         <v>40</v>
@@ -26684,7 +26697,7 @@
         <v>4100</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="D559" s="2" t="s">
         <v>40</v>
@@ -26725,7 +26738,7 @@
         <v>4101</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="C560" s="2" t="s">
         <v>43</v>
@@ -26775,7 +26788,7 @@
         <v>4102</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C561" s="2" t="s">
         <v>48</v>
@@ -26822,13 +26835,13 @@
         <v>4103</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="D562" s="2" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="F562" s="2" t="n">
         <v>1941</v>
@@ -26851,7 +26864,7 @@
         <v>8192</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="D563" s="2" t="s">
         <v>40</v>
@@ -26940,7 +26953,7 @@
         <v>8193</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="D564" s="2" t="s">
         <v>40</v>
@@ -27029,7 +27042,7 @@
         <v>8194</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="D565" s="2" t="s">
         <v>40</v>
@@ -27118,7 +27131,7 @@
         <v>8195</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="D566" s="2" t="s">
         <v>40</v>
@@ -27207,7 +27220,7 @@
         <v>8196</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="D567" s="2" t="s">
         <v>40</v>
@@ -27296,7 +27309,7 @@
         <v>8197</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="D568" s="2" t="s">
         <v>40</v>
@@ -27385,7 +27398,7 @@
         <v>8198</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="D569" s="2" t="s">
         <v>40</v>
@@ -27474,7 +27487,7 @@
         <v>8199</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="D570" s="2" t="s">
         <v>40</v>
@@ -27563,7 +27576,7 @@
         <v>8200</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="D571" s="2" t="s">
         <v>40</v>
@@ -27652,7 +27665,7 @@
         <v>8201</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="D572" s="2" t="s">
         <v>40</v>
@@ -27741,7 +27754,7 @@
         <v>8202</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="D573" s="2" t="s">
         <v>40</v>
@@ -27830,7 +27843,7 @@
         <v>8203</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="D574" s="2" t="s">
         <v>40</v>
@@ -27919,7 +27932,7 @@
         <v>8204</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="D575" s="2" t="s">
         <v>49</v>
@@ -28008,7 +28021,7 @@
         <v>8205</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="D576" s="2" t="s">
         <v>49</v>
@@ -28097,7 +28110,7 @@
         <v>8206</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="D577" s="2" t="s">
         <v>49</v>
@@ -28186,7 +28199,7 @@
         <v>8207</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="D578" s="2" t="s">
         <v>49</v>
@@ -28275,7 +28288,7 @@
         <v>8208</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="D579" s="2" t="s">
         <v>49</v>
@@ -28364,7 +28377,7 @@
         <v>8209</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="D580" s="2" t="s">
         <v>49</v>
@@ -28453,7 +28466,7 @@
         <v>8210</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="D581" s="2" t="s">
         <v>49</v>
@@ -28542,7 +28555,7 @@
         <v>8211</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="D582" s="2" t="s">
         <v>49</v>
@@ -28631,7 +28644,7 @@
         <v>8212</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="D583" s="2" t="s">
         <v>49</v>
@@ -28720,7 +28733,7 @@
         <v>8213</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="D584" s="2" t="s">
         <v>49</v>
@@ -28809,7 +28822,7 @@
         <v>8214</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="D585" s="2" t="s">
         <v>57</v>
@@ -28898,7 +28911,7 @@
         <v>8215</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="D586" s="2" t="s">
         <v>57</v>
@@ -28987,7 +29000,7 @@
         <v>8216</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="D587" s="2" t="s">
         <v>57</v>
@@ -29076,7 +29089,7 @@
         <v>8217</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="D588" s="2" t="s">
         <v>57</v>
@@ -29165,7 +29178,7 @@
         <v>8218</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="D589" s="2" t="s">
         <v>57</v>
@@ -29254,7 +29267,7 @@
         <v>8219</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="D590" s="2" t="s">
         <v>57</v>
@@ -29343,7 +29356,7 @@
         <v>8220</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="D591" s="2" t="s">
         <v>66</v>
@@ -29432,7 +29445,7 @@
         <v>8221</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="D592" s="2" t="s">
         <v>66</v>
@@ -29521,7 +29534,7 @@
         <v>8222</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="D593" s="2" t="s">
         <v>66</v>
@@ -29610,7 +29623,7 @@
         <v>8223</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="D594" s="2" t="s">
         <v>66</v>
@@ -29699,7 +29712,7 @@
         <v>8224</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="D595" s="2" t="s">
         <v>66</v>
@@ -29788,7 +29801,7 @@
         <v>8225</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="D596" s="2" t="s">
         <v>66</v>
@@ -29877,7 +29890,7 @@
         <v>8226</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="D597" s="2" t="s">
         <v>66</v>
@@ -29966,7 +29979,7 @@
         <v>8227</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="D598" s="2" t="s">
         <v>66</v>
@@ -30055,7 +30068,7 @@
         <v>8228</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="D599" s="2" t="s">
         <v>66</v>
@@ -30144,7 +30157,7 @@
         <v>8229</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="D600" s="2" t="s">
         <v>66</v>
@@ -30233,7 +30246,7 @@
         <v>8230</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="D601" s="2" t="s">
         <v>73</v>
@@ -30322,7 +30335,7 @@
         <v>8231</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="D602" s="2" t="s">
         <v>73</v>
@@ -30411,7 +30424,7 @@
         <v>8232</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="D603" s="2" t="s">
         <v>73</v>
@@ -30500,7 +30513,7 @@
         <v>8233</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="D604" s="2" t="s">
         <v>73</v>
@@ -30589,7 +30602,7 @@
         <v>8234</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D605" s="2" t="s">
         <v>73</v>
@@ -30678,7 +30691,7 @@
         <v>8235</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="D606" s="2" t="s">
         <v>73</v>
@@ -30767,7 +30780,7 @@
         <v>8236</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="D607" s="2" t="s">
         <v>228</v>
@@ -30856,7 +30869,7 @@
         <v>8237</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="D608" s="2" t="s">
         <v>228</v>
@@ -30945,7 +30958,7 @@
         <v>8238</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="D609" s="2" t="s">
         <v>228</v>
@@ -31034,7 +31047,7 @@
         <v>8239</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="D610" s="2" t="s">
         <v>139</v>
@@ -31123,7 +31136,7 @@
         <v>8240</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="D611" s="2" t="s">
         <v>139</v>
@@ -31212,7 +31225,7 @@
         <v>8241</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="D612" s="2" t="s">
         <v>88</v>
@@ -31301,7 +31314,7 @@
         <v>8242</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="D613" s="2" t="s">
         <v>88</v>
@@ -31390,7 +31403,7 @@
         <v>8243</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="D614" s="2" t="s">
         <v>88</v>
@@ -31479,7 +31492,7 @@
         <v>8244</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="D615" s="2" t="s">
         <v>88</v>
@@ -31568,7 +31581,7 @@
         <v>8245</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="D616" s="2" t="s">
         <v>88</v>
@@ -31657,7 +31670,7 @@
         <v>8246</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D617" s="2" t="s">
         <v>96</v>
@@ -31746,7 +31759,7 @@
         <v>8247</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="D618" s="2" t="s">
         <v>96</v>
@@ -31835,7 +31848,7 @@
         <v>8248</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D619" s="2" t="s">
         <v>96</v>
@@ -31924,7 +31937,7 @@
         <v>8249</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="D620" s="2" t="s">
         <v>96</v>
@@ -32013,7 +32026,7 @@
         <v>8250</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="D621" s="2" t="s">
         <v>96</v>
@@ -32102,7 +32115,7 @@
         <v>8251</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="D622" s="2" t="s">
         <v>79</v>
@@ -32191,7 +32204,7 @@
         <v>8252</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="C623" s="2"/>
       <c r="D623" s="2" t="s">
@@ -32286,7 +32299,7 @@
         <v>8253</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="C624" s="2"/>
       <c r="D624" s="2" t="s">
@@ -32381,7 +32394,7 @@
         <v>8254</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="C625" s="2"/>
       <c r="D625" s="2" t="s">
@@ -32476,7 +32489,7 @@
         <v>8255</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="C626" s="2"/>
       <c r="D626" s="2" t="s">
@@ -32571,7 +32584,7 @@
         <v>8256</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="C627" s="2"/>
       <c r="D627" s="2" t="s">
@@ -32666,7 +32679,7 @@
         <v>8257</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C628" s="2"/>
       <c r="D628" s="2" t="s">
@@ -32761,7 +32774,7 @@
         <v>8258</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C629" s="2"/>
       <c r="D629" s="2" t="s">
@@ -32856,7 +32869,7 @@
         <v>8259</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="C630" s="2"/>
       <c r="D630" s="2" t="s">
@@ -32951,7 +32964,7 @@
         <v>8260</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="C631" s="2"/>
       <c r="D631" s="2" t="s">
@@ -33046,7 +33059,7 @@
         <v>8261</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C632" s="2"/>
       <c r="D632" s="2" t="s">
@@ -33141,14 +33154,14 @@
         <v>8262</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="C633" s="2"/>
       <c r="D633" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E633" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F633" s="2" t="n">
         <v>1937</v>
@@ -33236,14 +33249,14 @@
         <v>8263</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C634" s="2"/>
       <c r="D634" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E634" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F634" s="2" t="n">
         <v>1940</v>
@@ -33331,14 +33344,14 @@
         <v>8264</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="C635" s="2"/>
       <c r="D635" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E635" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F635" s="2" t="n">
         <v>1942</v>
@@ -33426,14 +33439,14 @@
         <v>8265</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C636" s="2"/>
       <c r="D636" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E636" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F636" s="2" t="n">
         <v>1944</v>
@@ -33521,14 +33534,14 @@
         <v>8266</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="C637" s="2"/>
       <c r="D637" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E637" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F637" s="2" t="n">
         <v>1948</v>
@@ -33616,7 +33629,7 @@
         <v>8267</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="C638" s="2"/>
       <c r="D638" s="2" t="s">
@@ -33711,7 +33724,7 @@
         <v>8268</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="C639" s="2"/>
       <c r="D639" s="2" t="s">
@@ -33806,7 +33819,7 @@
         <v>8269</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="C640" s="2"/>
       <c r="D640" s="2" t="s">
@@ -33901,7 +33914,7 @@
         <v>8270</v>
       </c>
       <c r="B641" s="2" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="C641" s="2"/>
       <c r="D641" s="2" t="s">
@@ -33996,7 +34009,7 @@
         <v>8271</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="C642" s="2"/>
       <c r="D642" s="2" t="s">
@@ -34091,7 +34104,7 @@
         <v>8272</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C643" s="2"/>
       <c r="D643" s="2" t="s">
@@ -34186,7 +34199,7 @@
         <v>8273</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="C644" s="2"/>
       <c r="D644" s="2" t="s">
@@ -34281,7 +34294,7 @@
         <v>8274</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="C645" s="2"/>
       <c r="D645" s="2" t="s">
@@ -34376,7 +34389,7 @@
         <v>8275</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="C646" s="2"/>
       <c r="D646" s="2" t="s">
@@ -34471,7 +34484,7 @@
         <v>8276</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="C647" s="2"/>
       <c r="D647" s="2" t="s">
@@ -34566,7 +34579,7 @@
         <v>8277</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C648" s="2"/>
       <c r="D648" s="2" t="s">
@@ -34661,7 +34674,7 @@
         <v>8278</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="C649" s="2"/>
       <c r="D649" s="2" t="s">
@@ -34756,7 +34769,7 @@
         <v>8279</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="C650" s="2"/>
       <c r="D650" s="2" t="s">
@@ -34851,7 +34864,7 @@
         <v>8280</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="C651" s="2"/>
       <c r="D651" s="2" t="s">
@@ -34946,7 +34959,7 @@
         <v>8281</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="C652" s="2"/>
       <c r="D652" s="2" t="s">
@@ -35041,7 +35054,7 @@
         <v>8282</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="C653" s="2"/>
       <c r="D653" s="2" t="s">
@@ -35136,7 +35149,7 @@
         <v>8283</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="C654" s="2"/>
       <c r="D654" s="2" t="s">
@@ -35231,7 +35244,7 @@
         <v>8284</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="C655" s="2"/>
       <c r="D655" s="2" t="s">
@@ -35326,7 +35339,7 @@
         <v>8285</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="C656" s="2"/>
       <c r="D656" s="2" t="s">
@@ -35421,7 +35434,7 @@
         <v>8286</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="C657" s="2"/>
       <c r="D657" s="2" t="s">
@@ -35516,7 +35529,7 @@
         <v>8287</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="C658" s="2"/>
       <c r="D658" s="2" t="s">
@@ -35611,7 +35624,7 @@
         <v>8288</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="D659" s="2" t="s">
         <v>145</v>
@@ -35700,13 +35713,13 @@
         <v>8289</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="D660" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E660" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F660" s="2" t="n">
         <v>1937</v>
@@ -35789,13 +35802,13 @@
         <v>8290</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="D661" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E661" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F661" s="2" t="n">
         <v>1943</v>
@@ -35878,13 +35891,13 @@
         <v>8291</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D662" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E662" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F662" s="2" t="n">
         <v>1948</v>
@@ -35967,7 +35980,7 @@
         <v>8292</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D663" s="2" t="s">
         <v>109</v>
@@ -36056,7 +36069,7 @@
         <v>8293</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="D664" s="2" t="s">
         <v>109</v>
@@ -36145,7 +36158,7 @@
         <v>8294</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D665" s="2" t="s">
         <v>109</v>
@@ -36234,7 +36247,7 @@
         <v>8295</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="D666" s="2" t="s">
         <v>109</v>
@@ -36323,13 +36336,13 @@
         <v>8296</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="D667" s="2" t="s">
         <v>109</v>
       </c>
       <c r="E667" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F667" s="2" t="n">
         <v>1943</v>
@@ -36412,13 +36425,13 @@
         <v>8297</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="D668" s="2" t="s">
         <v>109</v>
       </c>
       <c r="E668" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F668" s="2" t="n">
         <v>1948</v>
@@ -36501,7 +36514,7 @@
         <v>8298</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="D669" s="2" t="s">
         <v>115</v>
@@ -36590,7 +36603,7 @@
         <v>8299</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="D670" s="2" t="s">
         <v>115</v>
@@ -36679,7 +36692,7 @@
         <v>8300</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="D671" s="2" t="s">
         <v>115</v>
@@ -36768,7 +36781,7 @@
         <v>8301</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="D672" s="2" t="s">
         <v>115</v>
@@ -36857,7 +36870,7 @@
         <v>8302</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="D673" s="2" t="s">
         <v>200</v>
@@ -36946,7 +36959,7 @@
         <v>8303</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="D674" s="2" t="s">
         <v>200</v>
@@ -37035,7 +37048,7 @@
         <v>8304</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D675" s="2" t="s">
         <v>197</v>
@@ -37124,7 +37137,7 @@
         <v>8305</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="D676" s="2" t="s">
         <v>197</v>
@@ -37213,7 +37226,7 @@
         <v>8306</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="D677" s="2" t="s">
         <v>197</v>
@@ -37302,7 +37315,7 @@
         <v>8307</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="D678" s="2" t="s">
         <v>197</v>
@@ -37391,7 +37404,7 @@
         <v>8308</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="D679" s="2" t="s">
         <v>197</v>
@@ -37480,7 +37493,7 @@
         <v>8309</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="D680" s="2" t="s">
         <v>197</v>
